--- a/pravila bilansi.xlsx
+++ b/pravila bilansi.xlsx
@@ -8,19 +8,21 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pc1\OneDrive\Desktop\goce proekt\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC9F726E-F102-41BF-B867-D15E8D0BE105}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54908AF6-E868-4AFF-9CFC-2879EB2C270F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{093C95D7-6491-4473-A653-F40FC2BC4264}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{093C95D7-6491-4473-A653-F40FC2BC4264}"/>
   </bookViews>
   <sheets>
     <sheet name="Pravila Bilans Uspeh" sheetId="1" r:id="rId1"/>
     <sheet name="Pravila bilans Sostojba" sheetId="3" r:id="rId2"/>
-    <sheet name="Pravila CF" sheetId="5" r:id="rId3"/>
-    <sheet name="Pravila KPI" sheetId="6" r:id="rId4"/>
-    <sheet name="konta" sheetId="2" r:id="rId5"/>
+    <sheet name="Pravila Seopfatna Dobivka" sheetId="7" r:id="rId3"/>
+    <sheet name="Pravila Valuation" sheetId="8" r:id="rId4"/>
+    <sheet name="Pravila CF" sheetId="5" r:id="rId5"/>
+    <sheet name="Pravila KPI" sheetId="6" r:id="rId6"/>
+    <sheet name="konta" sheetId="2" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Pravila bilans Sostojba'!$A$1:$I$127</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Pravila bilans Sostojba'!$A$1:$I$128</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Pravila Bilans Uspeh'!$A$2:$G$75</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -44,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1408" uniqueCount="671">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1576" uniqueCount="779">
   <si>
     <r>
       <t xml:space="preserve">Биланс на успехот     </t>
@@ -2048,12 +2050,6 @@
     <t>KPI09</t>
   </si>
   <si>
-    <t>ВРАЌАЊЕ НА СРЕДСТВА</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> (РОА - Return of assets)</t>
-  </si>
-  <si>
     <t>BU255/((BS063_T+BS063_P)/2)</t>
   </si>
   <si>
@@ -2079,6 +2075,382 @@
   </si>
   <si>
     <t>Rizik_pod</t>
+  </si>
+  <si>
+    <t>13,810</t>
+  </si>
+  <si>
+    <t>ИЗВЕШТАЈ ЗА СЕОПФАТНА ДОБИВКА ЗА ПЕРИОДОТ</t>
+  </si>
+  <si>
+    <t>Останати оперативни приходи (добивка)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Промени на залихите на готови производи и производство во тек </t>
+  </si>
+  <si>
+    <t>Бруто добивка</t>
+  </si>
+  <si>
+    <t>Потрошен материјал и ситен инвентар</t>
+  </si>
+  <si>
+    <t>Набавна вредност на стоки и материјали</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Трошоци за депрецијација и амортизација </t>
+  </si>
+  <si>
+    <t>Вредносно усогласување на тековни средства</t>
+  </si>
+  <si>
+    <t>Нематеријални трошоци од работењетѕо</t>
+  </si>
+  <si>
+    <t>Останати трошоци од редовни активности</t>
+  </si>
+  <si>
+    <t>Плати и надоместоци</t>
+  </si>
+  <si>
+    <t>Вкупно оперативни трошоци</t>
+  </si>
+  <si>
+    <t>Добивка/Загуба од опертивното работење</t>
+  </si>
+  <si>
+    <t>Финансиски приходи</t>
+  </si>
+  <si>
+    <t>Финансиски расходи</t>
+  </si>
+  <si>
+    <t>Вкупно финансиски приходи/расходи</t>
+  </si>
+  <si>
+    <t>Данок на добивка</t>
+  </si>
+  <si>
+    <t>Нето добивка за периодот</t>
+  </si>
+  <si>
+    <t>Red</t>
+  </si>
+  <si>
+    <t>Stil</t>
+  </si>
+  <si>
+    <t>BU202</t>
+  </si>
+  <si>
+    <t>BU204-BU205</t>
+  </si>
+  <si>
+    <t>SD1</t>
+  </si>
+  <si>
+    <t>SD2</t>
+  </si>
+  <si>
+    <t>SD3</t>
+  </si>
+  <si>
+    <t>SD4</t>
+  </si>
+  <si>
+    <t>BU208</t>
+  </si>
+  <si>
+    <t>BU209</t>
+  </si>
+  <si>
+    <t>BU211</t>
+  </si>
+  <si>
+    <t>BU218</t>
+  </si>
+  <si>
+    <t>BU219+BU220</t>
+  </si>
+  <si>
+    <t>BU212</t>
+  </si>
+  <si>
+    <t>BU222</t>
+  </si>
+  <si>
+    <t>BU213</t>
+  </si>
+  <si>
+    <t>SD5</t>
+  </si>
+  <si>
+    <t>SD6</t>
+  </si>
+  <si>
+    <t>SD7</t>
+  </si>
+  <si>
+    <t>SD8</t>
+  </si>
+  <si>
+    <t>SD9</t>
+  </si>
+  <si>
+    <t>SD10</t>
+  </si>
+  <si>
+    <t>SD11</t>
+  </si>
+  <si>
+    <t>SD12</t>
+  </si>
+  <si>
+    <t>SD13</t>
+  </si>
+  <si>
+    <t>SD5+SD6+SD7+SD8+SD9+SD10+SD11+SD12</t>
+  </si>
+  <si>
+    <t>SD4-SD13</t>
+  </si>
+  <si>
+    <t>SD14</t>
+  </si>
+  <si>
+    <t>SD15</t>
+  </si>
+  <si>
+    <t>SD16</t>
+  </si>
+  <si>
+    <t>SD17</t>
+  </si>
+  <si>
+    <t>SD15-SD16</t>
+  </si>
+  <si>
+    <t>SD18</t>
+  </si>
+  <si>
+    <t>SD19</t>
+  </si>
+  <si>
+    <t>SD20</t>
+  </si>
+  <si>
+    <t>SD18-SD19</t>
+  </si>
+  <si>
+    <t>Добивка/Загуба пред оданочување</t>
+  </si>
+  <si>
+    <t>normal</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">total </t>
+  </si>
+  <si>
+    <t xml:space="preserve">iznos </t>
+  </si>
+  <si>
+    <t>BU203</t>
+  </si>
+  <si>
+    <t>103,100</t>
+  </si>
+  <si>
+    <t>SD1+SD2-SD3</t>
+  </si>
+  <si>
+    <t>SD14+SD17</t>
+  </si>
+  <si>
+    <t>KPI10</t>
+  </si>
+  <si>
+    <t>KPI11</t>
+  </si>
+  <si>
+    <t>ВКУПНА ЗАДОЛЖЕНОСТ</t>
+  </si>
+  <si>
+    <t>BS081_T/BS063_T</t>
+  </si>
+  <si>
+    <t>Овој показател покажува колкав дел од средствата на компанијата се финансираат со задолжување.</t>
+  </si>
+  <si>
+    <t>ФИНАНСИСКА СТАБИЛНОСТ</t>
+  </si>
+  <si>
+    <t>KPI12</t>
+  </si>
+  <si>
+    <t>ПРОФИТ ПО ВРАБОТЕН</t>
+  </si>
+  <si>
+    <t>BU255/BU257</t>
+  </si>
+  <si>
+    <t>KPI13</t>
+  </si>
+  <si>
+    <t>ПРОФИТНА МАРЖА</t>
+  </si>
+  <si>
+    <t>BU255/BS065_T</t>
+  </si>
+  <si>
+    <r>
+      <t>ВРАЌАЊЕ НА СРЕДСТВА  (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>RОА - Return of assets</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>ВРАЌАЊЕ НА КАПИТАЛ  (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>RОЕ - Return of equty</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <t>izvor</t>
+  </si>
+  <si>
+    <t>Total assets</t>
+  </si>
+  <si>
+    <t>Equty</t>
+  </si>
+  <si>
+    <t>Cash</t>
+  </si>
+  <si>
+    <t>Debt</t>
+  </si>
+  <si>
+    <t>Net profit</t>
+  </si>
+  <si>
+    <t>Depreciation</t>
+  </si>
+  <si>
+    <t>EBITDA</t>
+  </si>
+  <si>
+    <t>EBITDA multiply</t>
+  </si>
+  <si>
+    <t>BS</t>
+  </si>
+  <si>
+    <t>063_T</t>
+  </si>
+  <si>
+    <t>111_T</t>
+  </si>
+  <si>
+    <t>059_T</t>
+  </si>
+  <si>
+    <t>089_T+090_T+092_T+103_T+104_T+107_T</t>
+  </si>
+  <si>
+    <t>BU</t>
+  </si>
+  <si>
+    <t>255-256</t>
+  </si>
+  <si>
+    <t>SD</t>
+  </si>
+  <si>
+    <t>SD14+SD8</t>
+  </si>
+  <si>
+    <t>INPUT</t>
+  </si>
+  <si>
+    <t>Вкупна актива</t>
+  </si>
+  <si>
+    <t>Пари и парични средства</t>
+  </si>
+  <si>
+    <t>Кредити и финансиски обврски</t>
+  </si>
+  <si>
+    <t>Добивка по оданочување</t>
+  </si>
+  <si>
+    <t>Амортизација</t>
+  </si>
+  <si>
+    <t>пример 3x, 4x, 5x</t>
+  </si>
+  <si>
+    <t>Operating Profit + Depreciation</t>
+  </si>
+  <si>
+    <t>Total Liabilities &amp; Equity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Вкупна пасива </t>
+  </si>
+  <si>
+    <t>065_T</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Капитал </t>
+  </si>
+  <si>
+    <t>(BU255-BU256)/BU201</t>
   </si>
 </sst>
 </file>
@@ -2089,7 +2461,7 @@
     <numFmt numFmtId="42" formatCode="_-&quot;£&quot;* #,##0_-;\-&quot;£&quot;* #,##0_-;_-&quot;£&quot;* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="0.E+00"/>
   </numFmts>
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="23" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2201,8 +2573,47 @@
       <family val="2"/>
       <charset val="204"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
   </fonts>
-  <fills count="11">
+  <fills count="14">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2263,8 +2674,26 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1" tint="4.9989318521683403E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor theme="0" tint="-0.14999847407452621"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="8">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -2361,12 +2790,34 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="83">
+  <cellXfs count="101">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -2557,15 +3008,56 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="21" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="22" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="3" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment shrinkToFit="1"/>
     </xf>
@@ -2584,7 +3076,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3314,12 +3805,12 @@
       <c r="B1" s="2"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B2" s="76" t="s">
+      <c r="B2" s="95" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B3" s="77"/>
+      <c r="B3" s="96"/>
     </row>
     <row r="4" spans="1:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
@@ -5339,7 +5830,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B82CF358-6F31-4D7F-93EC-0C8D1049DBC2}">
-  <dimension ref="A1:I284"/>
+  <dimension ref="A1:I285"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="67.42578125" bestFit="1" customWidth="1"/>
@@ -5352,7 +5843,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="78" t="s">
+      <c r="A1" s="97" t="s">
         <v>308</v>
       </c>
       <c r="B1" s="38"/>
@@ -5361,18 +5852,18 @@
       <c r="E1" s="38"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="79"/>
+      <c r="A2" s="98"/>
       <c r="B2" s="38"/>
-      <c r="C2" s="80" t="s">
+      <c r="C2" s="99" t="s">
         <v>422</v>
       </c>
-      <c r="D2" s="80"/>
-      <c r="E2" s="80"/>
-      <c r="F2" s="81" t="s">
+      <c r="D2" s="99"/>
+      <c r="E2" s="99"/>
+      <c r="F2" s="100" t="s">
         <v>423</v>
       </c>
-      <c r="G2" s="81"/>
-      <c r="H2" s="81"/>
+      <c r="G2" s="100"/>
+      <c r="H2" s="100"/>
     </row>
     <row r="3" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A3" s="55" t="s">
@@ -6824,7 +7315,7 @@
         <v>357</v>
       </c>
       <c r="C61" s="37" t="s">
-        <v>448</v>
+        <v>669</v>
       </c>
       <c r="D61" s="41" t="s">
         <v>202</v>
@@ -6843,42 +7334,42 @@
       </c>
       <c r="I61" s="23"/>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A62" s="43" t="s">
+        <v>252</v>
+      </c>
+      <c r="B62" s="40" t="s">
+        <v>357</v>
+      </c>
+      <c r="C62" s="37" t="s">
+        <v>448</v>
+      </c>
+      <c r="D62" s="41" t="s">
+        <v>203</v>
+      </c>
+      <c r="E62" s="41" t="s">
+        <v>150</v>
+      </c>
+      <c r="F62" s="92">
+        <v>13</v>
+      </c>
+      <c r="G62" s="23" t="s">
+        <v>196</v>
+      </c>
+      <c r="H62" s="23" t="s">
+        <v>512</v>
+      </c>
+      <c r="I62" s="23"/>
+    </row>
+    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A63" s="43" t="s">
         <v>253</v>
       </c>
-      <c r="B62" s="40" t="s">
+      <c r="B63" s="40" t="s">
         <v>358</v>
       </c>
-      <c r="C62" s="37" t="s">
+      <c r="C63" s="37" t="s">
         <v>449</v>
-      </c>
-      <c r="D62" s="41" t="s">
-        <v>202</v>
-      </c>
-      <c r="E62" s="41" t="s">
-        <v>149</v>
-      </c>
-      <c r="F62" s="23" t="s">
-        <v>449</v>
-      </c>
-      <c r="G62" s="23" t="s">
-        <v>195</v>
-      </c>
-      <c r="H62" s="23" t="s">
-        <v>149</v>
-      </c>
-      <c r="I62" s="23"/>
-    </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A63" s="48" t="s">
-        <v>254</v>
-      </c>
-      <c r="B63" s="40" t="s">
-        <v>359</v>
-      </c>
-      <c r="C63" s="37" t="s">
-        <v>450</v>
       </c>
       <c r="D63" s="41" t="s">
         <v>202</v>
@@ -6887,7 +7378,7 @@
         <v>149</v>
       </c>
       <c r="F63" s="23" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="G63" s="23" t="s">
         <v>195</v>
@@ -6898,28 +7389,38 @@
       <c r="I63" s="23"/>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A64" s="44" t="s">
+      <c r="A64" s="48" t="s">
+        <v>254</v>
+      </c>
+      <c r="B64" s="40" t="s">
+        <v>359</v>
+      </c>
+      <c r="C64" s="37" t="s">
+        <v>450</v>
+      </c>
+      <c r="D64" s="41" t="s">
+        <v>202</v>
+      </c>
+      <c r="E64" s="41" t="s">
+        <v>149</v>
+      </c>
+      <c r="F64" s="23" t="s">
+        <v>450</v>
+      </c>
+      <c r="G64" s="23" t="s">
+        <v>195</v>
+      </c>
+      <c r="H64" s="23" t="s">
+        <v>149</v>
+      </c>
+      <c r="I64" s="23"/>
+    </row>
+    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A65" s="44" t="s">
         <v>255</v>
       </c>
-      <c r="B64" s="40" t="s">
+      <c r="B65" s="40" t="s">
         <v>360</v>
-      </c>
-      <c r="C64" s="37"/>
-      <c r="D64" s="41"/>
-      <c r="E64" s="41"/>
-      <c r="F64" s="23"/>
-      <c r="G64" s="23"/>
-      <c r="H64" s="23"/>
-      <c r="I64" s="23" t="s">
-        <v>520</v>
-      </c>
-    </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A65" s="43" t="s">
-        <v>256</v>
-      </c>
-      <c r="B65" s="40" t="s">
-        <v>361</v>
       </c>
       <c r="C65" s="37"/>
       <c r="D65" s="41"/>
@@ -6928,45 +7429,35 @@
       <c r="G65" s="23"/>
       <c r="H65" s="23"/>
       <c r="I65" s="23" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66" s="43" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B66" s="40" t="s">
-        <v>362</v>
-      </c>
-      <c r="C66" s="37" t="s">
-        <v>451</v>
-      </c>
-      <c r="D66" s="41" t="s">
-        <v>202</v>
-      </c>
-      <c r="E66" s="41" t="s">
-        <v>149</v>
-      </c>
-      <c r="F66" s="23" t="s">
-        <v>451</v>
-      </c>
-      <c r="G66" s="23" t="s">
-        <v>195</v>
-      </c>
-      <c r="H66" s="23" t="s">
-        <v>146</v>
-      </c>
-      <c r="I66" s="23"/>
+        <v>361</v>
+      </c>
+      <c r="C66" s="37"/>
+      <c r="D66" s="41"/>
+      <c r="E66" s="41"/>
+      <c r="F66" s="23"/>
+      <c r="G66" s="23"/>
+      <c r="H66" s="23"/>
+      <c r="I66" s="23" t="s">
+        <v>521</v>
+      </c>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67" s="43" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B67" s="40" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C67" s="37" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="D67" s="41" t="s">
         <v>202</v>
@@ -6975,7 +7466,7 @@
         <v>149</v>
       </c>
       <c r="F67" s="23" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="G67" s="23" t="s">
         <v>195</v>
@@ -6987,13 +7478,13 @@
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68" s="43" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B68" s="40" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C68" s="37" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="D68" s="41" t="s">
         <v>202</v>
@@ -7002,7 +7493,7 @@
         <v>149</v>
       </c>
       <c r="F68" s="23" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="G68" s="23" t="s">
         <v>195</v>
@@ -7014,13 +7505,13 @@
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A69" s="43" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B69" s="40" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C69" s="37" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="D69" s="41" t="s">
         <v>202</v>
@@ -7029,7 +7520,7 @@
         <v>149</v>
       </c>
       <c r="F69" s="23" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="G69" s="23" t="s">
         <v>195</v>
@@ -7041,13 +7532,13 @@
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70" s="43" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B70" s="40" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C70" s="37" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="D70" s="41" t="s">
         <v>202</v>
@@ -7056,7 +7547,7 @@
         <v>149</v>
       </c>
       <c r="F70" s="23" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="G70" s="23" t="s">
         <v>195</v>
@@ -7067,48 +7558,48 @@
       <c r="I70" s="23"/>
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A71" s="44" t="s">
+      <c r="A71" s="43" t="s">
+        <v>261</v>
+      </c>
+      <c r="B71" s="40" t="s">
+        <v>366</v>
+      </c>
+      <c r="C71" s="37" t="s">
+        <v>455</v>
+      </c>
+      <c r="D71" s="41" t="s">
+        <v>202</v>
+      </c>
+      <c r="E71" s="41" t="s">
+        <v>149</v>
+      </c>
+      <c r="F71" s="23" t="s">
+        <v>455</v>
+      </c>
+      <c r="G71" s="23" t="s">
+        <v>195</v>
+      </c>
+      <c r="H71" s="23" t="s">
+        <v>146</v>
+      </c>
+      <c r="I71" s="23"/>
+    </row>
+    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A72" s="44" t="s">
         <v>262</v>
       </c>
-      <c r="B71" s="40" t="s">
+      <c r="B72" s="40" t="s">
         <v>367</v>
       </c>
-      <c r="C71" s="37"/>
-      <c r="D71" s="41"/>
-      <c r="E71" s="41"/>
-      <c r="F71" s="23"/>
-      <c r="G71" s="23"/>
-      <c r="H71" s="23"/>
-      <c r="I71" s="23" t="s">
+      <c r="C72" s="37"/>
+      <c r="D72" s="41"/>
+      <c r="E72" s="41"/>
+      <c r="F72" s="23"/>
+      <c r="G72" s="23"/>
+      <c r="H72" s="23"/>
+      <c r="I72" s="23" t="s">
         <v>522</v>
       </c>
-    </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A72" s="43" t="s">
-        <v>263</v>
-      </c>
-      <c r="B72" s="40" t="s">
-        <v>368</v>
-      </c>
-      <c r="C72" s="37" t="s">
-        <v>456</v>
-      </c>
-      <c r="D72" s="41" t="s">
-        <v>202</v>
-      </c>
-      <c r="E72" s="41" t="s">
-        <v>149</v>
-      </c>
-      <c r="F72" s="23" t="s">
-        <v>456</v>
-      </c>
-      <c r="G72" s="23" t="s">
-        <v>195</v>
-      </c>
-      <c r="H72" s="23" t="s">
-        <v>149</v>
-      </c>
-      <c r="I72" s="23"/>
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A73" s="43" t="s">
@@ -7118,61 +7609,61 @@
         <v>368</v>
       </c>
       <c r="C73" s="37" t="s">
-        <v>411</v>
+        <v>456</v>
       </c>
       <c r="D73" s="41" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E73" s="41" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F73" s="23" t="s">
-        <v>411</v>
+        <v>456</v>
       </c>
       <c r="G73" s="23" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H73" s="23" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="I73" s="23"/>
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A74" s="43" t="s">
+        <v>263</v>
+      </c>
+      <c r="B74" s="40" t="s">
+        <v>368</v>
+      </c>
+      <c r="C74" s="37" t="s">
+        <v>731</v>
+      </c>
+      <c r="D74" s="41" t="s">
+        <v>203</v>
+      </c>
+      <c r="E74" s="41" t="s">
+        <v>150</v>
+      </c>
+      <c r="F74" s="91">
+        <v>103100</v>
+      </c>
+      <c r="G74" s="23" t="s">
+        <v>196</v>
+      </c>
+      <c r="H74" s="23" t="s">
+        <v>150</v>
+      </c>
+      <c r="I74" s="23"/>
+    </row>
+    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A75" s="43" t="s">
         <v>264</v>
       </c>
-      <c r="B74" s="40" t="s">
+      <c r="B75" s="40" t="s">
         <v>369</v>
       </c>
-      <c r="C74" s="37" t="s">
+      <c r="C75" s="37" t="s">
         <v>457</v>
-      </c>
-      <c r="D74" s="41" t="s">
-        <v>202</v>
-      </c>
-      <c r="E74" s="41" t="s">
-        <v>149</v>
-      </c>
-      <c r="F74" s="23" t="s">
-        <v>457</v>
-      </c>
-      <c r="G74" s="23" t="s">
-        <v>195</v>
-      </c>
-      <c r="H74" s="23" t="s">
-        <v>149</v>
-      </c>
-      <c r="I74" s="23"/>
-    </row>
-    <row r="75" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A75" s="46" t="s">
-        <v>265</v>
-      </c>
-      <c r="B75" s="40" t="s">
-        <v>370</v>
-      </c>
-      <c r="C75" s="37" t="s">
-        <v>458</v>
       </c>
       <c r="D75" s="41" t="s">
         <v>202</v>
@@ -7181,7 +7672,7 @@
         <v>149</v>
       </c>
       <c r="F75" s="23" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="G75" s="23" t="s">
         <v>195</v>
@@ -7191,103 +7682,103 @@
       </c>
       <c r="I75" s="23"/>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A76" s="49" t="s">
+    <row r="76" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A76" s="46" t="s">
+        <v>265</v>
+      </c>
+      <c r="B76" s="40" t="s">
+        <v>370</v>
+      </c>
+      <c r="C76" s="37" t="s">
+        <v>458</v>
+      </c>
+      <c r="D76" s="41" t="s">
+        <v>202</v>
+      </c>
+      <c r="E76" s="41" t="s">
+        <v>149</v>
+      </c>
+      <c r="F76" s="23" t="s">
+        <v>458</v>
+      </c>
+      <c r="G76" s="23" t="s">
+        <v>195</v>
+      </c>
+      <c r="H76" s="23" t="s">
+        <v>149</v>
+      </c>
+      <c r="I76" s="23"/>
+    </row>
+    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A77" s="49" t="s">
         <v>266</v>
       </c>
-      <c r="B76" s="40" t="s">
+      <c r="B77" s="40" t="s">
         <v>371</v>
       </c>
-      <c r="C76" s="37"/>
-      <c r="D76" s="41"/>
-      <c r="E76" s="41"/>
-      <c r="F76" s="23"/>
-      <c r="G76" s="23"/>
-      <c r="H76" s="23"/>
-      <c r="I76" s="23" t="s">
+      <c r="C77" s="37"/>
+      <c r="D77" s="41"/>
+      <c r="E77" s="41"/>
+      <c r="F77" s="23"/>
+      <c r="G77" s="23"/>
+      <c r="H77" s="23"/>
+      <c r="I77" s="23" t="s">
         <v>523</v>
       </c>
     </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A77" s="44" t="s">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A78" s="44" t="s">
         <v>267</v>
       </c>
-      <c r="B77" s="40" t="s">
+      <c r="B78" s="40" t="s">
         <v>372</v>
       </c>
-      <c r="C77" s="37" t="s">
+      <c r="C78" s="37" t="s">
         <v>459</v>
       </c>
-      <c r="D77" s="41" t="s">
+      <c r="D78" s="41" t="s">
         <v>202</v>
       </c>
-      <c r="E77" s="41" t="s">
-        <v>149</v>
-      </c>
-      <c r="F77" s="23" t="s">
+      <c r="E78" s="41" t="s">
+        <v>149</v>
+      </c>
+      <c r="F78" s="23" t="s">
         <v>459</v>
       </c>
-      <c r="G77" s="23" t="s">
+      <c r="G78" s="23" t="s">
         <v>195</v>
       </c>
-      <c r="H77" s="23" t="s">
-        <v>149</v>
-      </c>
-      <c r="I77" s="23"/>
-    </row>
-    <row r="78" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A78" s="46" t="s">
+      <c r="H78" s="23" t="s">
+        <v>149</v>
+      </c>
+      <c r="I78" s="23"/>
+    </row>
+    <row r="79" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A79" s="46" t="s">
         <v>268</v>
       </c>
-      <c r="B78" s="40" t="s">
+      <c r="B79" s="40" t="s">
         <v>373</v>
       </c>
-      <c r="C78" s="37"/>
-      <c r="D78" s="41"/>
-      <c r="E78" s="41"/>
-      <c r="F78" s="23"/>
-      <c r="G78" s="23"/>
-      <c r="H78" s="23"/>
-      <c r="I78" s="23" t="s">
+      <c r="C79" s="37"/>
+      <c r="D79" s="41"/>
+      <c r="E79" s="41"/>
+      <c r="F79" s="23"/>
+      <c r="G79" s="23"/>
+      <c r="H79" s="23"/>
+      <c r="I79" s="23" t="s">
         <v>524</v>
       </c>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A79" s="50" t="s">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A80" s="50" t="s">
         <v>269</v>
       </c>
-      <c r="B79" s="40" t="s">
+      <c r="B80" s="40" t="s">
         <v>374</v>
       </c>
-      <c r="C79" s="37" t="s">
+      <c r="C80" s="37" t="s">
         <v>460</v>
-      </c>
-      <c r="D79" s="41" t="s">
-        <v>203</v>
-      </c>
-      <c r="E79" s="41" t="s">
-        <v>149</v>
-      </c>
-      <c r="F79" s="23" t="s">
-        <v>460</v>
-      </c>
-      <c r="G79" s="23" t="s">
-        <v>196</v>
-      </c>
-      <c r="H79" s="23" t="s">
-        <v>149</v>
-      </c>
-      <c r="I79" s="23"/>
-    </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A80" s="44" t="s">
-        <v>270</v>
-      </c>
-      <c r="B80" s="40" t="s">
-        <v>375</v>
-      </c>
-      <c r="C80" s="37" t="s">
-        <v>461</v>
       </c>
       <c r="D80" s="41" t="s">
         <v>203</v>
@@ -7296,7 +7787,7 @@
         <v>149</v>
       </c>
       <c r="F80" s="23" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="G80" s="23" t="s">
         <v>196</v>
@@ -7308,13 +7799,13 @@
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A81" s="44" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B81" s="40" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C81" s="37" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="D81" s="41" t="s">
         <v>203</v>
@@ -7323,7 +7814,7 @@
         <v>149</v>
       </c>
       <c r="F81" s="23" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="G81" s="23" t="s">
         <v>196</v>
@@ -7335,13 +7826,13 @@
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A82" s="44" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B82" s="40" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C82" s="37" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D82" s="41" t="s">
         <v>203</v>
@@ -7350,7 +7841,7 @@
         <v>149</v>
       </c>
       <c r="F82" s="23" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="G82" s="23" t="s">
         <v>196</v>
@@ -7360,15 +7851,15 @@
       </c>
       <c r="I82" s="23"/>
     </row>
-    <row r="83" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A83" s="46" t="s">
-        <v>273</v>
+    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A83" s="44" t="s">
+        <v>272</v>
       </c>
       <c r="B83" s="40" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C83" s="37" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="D83" s="41" t="s">
         <v>203</v>
@@ -7377,7 +7868,7 @@
         <v>149</v>
       </c>
       <c r="F83" s="23" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="G83" s="23" t="s">
         <v>196</v>
@@ -7387,59 +7878,59 @@
       </c>
       <c r="I83" s="23"/>
     </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A84" s="44" t="s">
+    <row r="84" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A84" s="46" t="s">
+        <v>273</v>
+      </c>
+      <c r="B84" s="40" t="s">
+        <v>378</v>
+      </c>
+      <c r="C84" s="37" t="s">
+        <v>464</v>
+      </c>
+      <c r="D84" s="41" t="s">
+        <v>203</v>
+      </c>
+      <c r="E84" s="41" t="s">
+        <v>149</v>
+      </c>
+      <c r="F84" s="23" t="s">
+        <v>464</v>
+      </c>
+      <c r="G84" s="23" t="s">
+        <v>196</v>
+      </c>
+      <c r="H84" s="23" t="s">
+        <v>149</v>
+      </c>
+      <c r="I84" s="23"/>
+    </row>
+    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A85" s="44" t="s">
         <v>274</v>
       </c>
-      <c r="B84" s="40" t="s">
+      <c r="B85" s="40" t="s">
         <v>379</v>
       </c>
-      <c r="C84" s="37"/>
-      <c r="D84" s="41"/>
-      <c r="E84" s="41"/>
-      <c r="F84" s="23"/>
-      <c r="G84" s="23"/>
-      <c r="H84" s="23"/>
-      <c r="I84" s="23" t="s">
+      <c r="C85" s="37"/>
+      <c r="D85" s="41"/>
+      <c r="E85" s="41"/>
+      <c r="F85" s="23"/>
+      <c r="G85" s="23"/>
+      <c r="H85" s="23"/>
+      <c r="I85" s="23" t="s">
         <v>525</v>
       </c>
-    </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A85" s="48" t="s">
-        <v>275</v>
-      </c>
-      <c r="B85" s="40" t="s">
-        <v>380</v>
-      </c>
-      <c r="C85" s="37" t="s">
-        <v>465</v>
-      </c>
-      <c r="D85" s="41" t="s">
-        <v>203</v>
-      </c>
-      <c r="E85" s="41" t="s">
-        <v>149</v>
-      </c>
-      <c r="F85" s="23" t="s">
-        <v>465</v>
-      </c>
-      <c r="G85" s="23" t="s">
-        <v>196</v>
-      </c>
-      <c r="H85" s="23" t="s">
-        <v>149</v>
-      </c>
-      <c r="I85" s="23"/>
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A86" s="48" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B86" s="40" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C86" s="37" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="D86" s="41" t="s">
         <v>203</v>
@@ -7448,7 +7939,7 @@
         <v>149</v>
       </c>
       <c r="F86" s="23" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="G86" s="23" t="s">
         <v>196</v>
@@ -7460,13 +7951,13 @@
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A87" s="48" t="s">
-        <v>277</v>
-      </c>
-      <c r="B87" s="51" t="s">
-        <v>382</v>
+        <v>276</v>
+      </c>
+      <c r="B87" s="40" t="s">
+        <v>381</v>
       </c>
       <c r="C87" s="37" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="D87" s="41" t="s">
         <v>203</v>
@@ -7475,7 +7966,7 @@
         <v>149</v>
       </c>
       <c r="F87" s="23" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="G87" s="23" t="s">
         <v>196</v>
@@ -7486,14 +7977,14 @@
       <c r="I87" s="23"/>
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A88" s="44" t="s">
-        <v>278</v>
+      <c r="A88" s="48" t="s">
+        <v>277</v>
       </c>
       <c r="B88" s="51" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C88" s="37" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="D88" s="41" t="s">
         <v>203</v>
@@ -7502,7 +7993,7 @@
         <v>149</v>
       </c>
       <c r="F88" s="23" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="G88" s="23" t="s">
         <v>196</v>
@@ -7514,25 +8005,25 @@
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A89" s="44" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B89" s="51" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C89" s="37" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="D89" s="41" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E89" s="41" t="s">
         <v>149</v>
       </c>
       <c r="F89" s="23" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="G89" s="23" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="H89" s="23" t="s">
         <v>149</v>
@@ -7541,13 +8032,13 @@
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A90" s="44" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B90" s="51" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C90" s="37" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="D90" s="41" t="s">
         <v>202</v>
@@ -7556,7 +8047,7 @@
         <v>149</v>
       </c>
       <c r="F90" s="23" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="G90" s="23" t="s">
         <v>195</v>
@@ -7568,67 +8059,79 @@
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A91" s="44" t="s">
+        <v>280</v>
+      </c>
+      <c r="B91" s="51" t="s">
+        <v>385</v>
+      </c>
+      <c r="C91" s="37" t="s">
+        <v>470</v>
+      </c>
+      <c r="D91" s="41" t="s">
+        <v>202</v>
+      </c>
+      <c r="E91" s="41" t="s">
+        <v>149</v>
+      </c>
+      <c r="F91" s="23" t="s">
+        <v>470</v>
+      </c>
+      <c r="G91" s="23" t="s">
+        <v>195</v>
+      </c>
+      <c r="H91" s="23" t="s">
+        <v>149</v>
+      </c>
+      <c r="I91" s="23"/>
+    </row>
+    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A92" s="44" t="s">
         <v>281</v>
       </c>
-      <c r="B91" s="51" t="s">
+      <c r="B92" s="51" t="s">
         <v>386</v>
       </c>
-      <c r="C91" s="37"/>
-      <c r="D91" s="41"/>
-      <c r="E91" s="41"/>
-      <c r="F91" s="23"/>
-      <c r="G91" s="23"/>
-      <c r="H91" s="23"/>
-      <c r="I91" s="23"/>
-    </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A92" s="52" t="s">
+      <c r="C92" s="37"/>
+      <c r="D92" s="41"/>
+      <c r="E92" s="41"/>
+      <c r="F92" s="23"/>
+      <c r="G92" s="23"/>
+      <c r="H92" s="23"/>
+      <c r="I92" s="23"/>
+    </row>
+    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A93" s="52" t="s">
         <v>282</v>
       </c>
-      <c r="B92" s="51" t="s">
+      <c r="B93" s="51" t="s">
         <v>387</v>
       </c>
-      <c r="C92" s="37" t="s">
+      <c r="C93" s="37" t="s">
         <v>471</v>
       </c>
-      <c r="D92" s="41" t="s">
+      <c r="D93" s="41" t="s">
         <v>203</v>
       </c>
-      <c r="E92" s="41" t="s">
-        <v>149</v>
-      </c>
-      <c r="F92" s="23" t="s">
+      <c r="E93" s="41" t="s">
+        <v>149</v>
+      </c>
+      <c r="F93" s="23" t="s">
         <v>471</v>
       </c>
-      <c r="G92" s="23" t="s">
+      <c r="G93" s="23" t="s">
         <v>196</v>
       </c>
-      <c r="H92" s="23" t="s">
-        <v>149</v>
-      </c>
-      <c r="I92" s="23"/>
-    </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A93" s="53" t="s">
-        <v>283</v>
-      </c>
-      <c r="B93" s="51" t="s">
-        <v>388</v>
-      </c>
-      <c r="C93" s="37"/>
-      <c r="D93" s="41"/>
-      <c r="E93" s="41"/>
-      <c r="F93" s="23"/>
-      <c r="G93" s="23"/>
-      <c r="H93" s="23"/>
+      <c r="H93" s="23" t="s">
+        <v>149</v>
+      </c>
       <c r="I93" s="23"/>
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A94" s="53" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B94" s="51" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C94" s="37"/>
       <c r="D94" s="41"/>
@@ -7636,16 +8139,14 @@
       <c r="F94" s="23"/>
       <c r="G94" s="23"/>
       <c r="H94" s="23"/>
-      <c r="I94" s="23" t="s">
-        <v>526</v>
-      </c>
+      <c r="I94" s="23"/>
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A95" s="44" t="s">
-        <v>285</v>
+      <c r="A95" s="53" t="s">
+        <v>284</v>
       </c>
       <c r="B95" s="51" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C95" s="37"/>
       <c r="D95" s="41"/>
@@ -7654,45 +8155,35 @@
       <c r="G95" s="23"/>
       <c r="H95" s="23"/>
       <c r="I95" s="23" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A96" s="44" t="s">
+        <v>285</v>
+      </c>
+      <c r="B96" s="51" t="s">
+        <v>390</v>
+      </c>
+      <c r="C96" s="37"/>
+      <c r="D96" s="41"/>
+      <c r="E96" s="41"/>
+      <c r="F96" s="23"/>
+      <c r="G96" s="23"/>
+      <c r="H96" s="23"/>
+      <c r="I96" s="23" t="s">
         <v>527</v>
       </c>
     </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A96" s="48" t="s">
+    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A97" s="48" t="s">
         <v>286</v>
       </c>
-      <c r="B96" s="51" t="s">
+      <c r="B97" s="51" t="s">
         <v>391</v>
       </c>
-      <c r="C96" s="37" t="s">
+      <c r="C97" s="37" t="s">
         <v>472</v>
-      </c>
-      <c r="D96" s="41" t="s">
-        <v>203</v>
-      </c>
-      <c r="E96" s="41" t="s">
-        <v>149</v>
-      </c>
-      <c r="F96" s="23" t="s">
-        <v>472</v>
-      </c>
-      <c r="G96" s="23" t="s">
-        <v>196</v>
-      </c>
-      <c r="H96" s="23" t="s">
-        <v>149</v>
-      </c>
-      <c r="I96" s="23"/>
-    </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A97" s="54" t="s">
-        <v>287</v>
-      </c>
-      <c r="B97" s="51" t="s">
-        <v>392</v>
-      </c>
-      <c r="C97" s="37" t="s">
-        <v>473</v>
       </c>
       <c r="D97" s="41" t="s">
         <v>203</v>
@@ -7701,7 +8192,7 @@
         <v>149</v>
       </c>
       <c r="F97" s="23" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="G97" s="23" t="s">
         <v>196</v>
@@ -7712,58 +8203,58 @@
       <c r="I97" s="23"/>
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A98" s="39" t="s">
+      <c r="A98" s="54" t="s">
+        <v>287</v>
+      </c>
+      <c r="B98" s="51" t="s">
+        <v>392</v>
+      </c>
+      <c r="C98" s="37" t="s">
+        <v>473</v>
+      </c>
+      <c r="D98" s="41" t="s">
+        <v>203</v>
+      </c>
+      <c r="E98" s="41" t="s">
+        <v>149</v>
+      </c>
+      <c r="F98" s="23" t="s">
+        <v>473</v>
+      </c>
+      <c r="G98" s="23" t="s">
+        <v>196</v>
+      </c>
+      <c r="H98" s="23" t="s">
+        <v>149</v>
+      </c>
+      <c r="I98" s="23"/>
+    </row>
+    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A99" s="39" t="s">
         <v>288</v>
       </c>
-      <c r="B98" s="51" t="s">
+      <c r="B99" s="51" t="s">
         <v>393</v>
       </c>
-      <c r="C98" s="37"/>
-      <c r="D98" s="41"/>
-      <c r="E98" s="41"/>
-      <c r="F98" s="23"/>
-      <c r="G98" s="23"/>
-      <c r="H98" s="23"/>
-      <c r="I98" s="23" t="s">
+      <c r="C99" s="37"/>
+      <c r="D99" s="41"/>
+      <c r="E99" s="41"/>
+      <c r="F99" s="23"/>
+      <c r="G99" s="23"/>
+      <c r="H99" s="23"/>
+      <c r="I99" s="23" t="s">
         <v>528</v>
       </c>
-    </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A99" s="42" t="s">
-        <v>289</v>
-      </c>
-      <c r="B99" s="51" t="s">
-        <v>394</v>
-      </c>
-      <c r="C99" s="37" t="s">
-        <v>474</v>
-      </c>
-      <c r="D99" s="41" t="s">
-        <v>203</v>
-      </c>
-      <c r="E99" s="41" t="s">
-        <v>149</v>
-      </c>
-      <c r="F99" s="23" t="s">
-        <v>474</v>
-      </c>
-      <c r="G99" s="23" t="s">
-        <v>196</v>
-      </c>
-      <c r="H99" s="23" t="s">
-        <v>149</v>
-      </c>
-      <c r="I99" s="23"/>
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A100" s="42" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B100" s="51" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C100" s="37" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D100" s="41" t="s">
         <v>203</v>
@@ -7772,7 +8263,7 @@
         <v>149</v>
       </c>
       <c r="F100" s="23" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="G100" s="23" t="s">
         <v>196</v>
@@ -7784,13 +8275,13 @@
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A101" s="42" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B101" s="51" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C101" s="37" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D101" s="41" t="s">
         <v>203</v>
@@ -7799,7 +8290,7 @@
         <v>149</v>
       </c>
       <c r="F101" s="23" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="G101" s="23" t="s">
         <v>196</v>
@@ -7811,13 +8302,13 @@
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A102" s="42" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B102" s="51" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C102" s="37" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D102" s="41" t="s">
         <v>203</v>
@@ -7826,7 +8317,7 @@
         <v>149</v>
       </c>
       <c r="F102" s="23" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="G102" s="23" t="s">
         <v>196</v>
@@ -7838,13 +8329,13 @@
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A103" s="42" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B103" s="51" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C103" s="37" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="D103" s="41" t="s">
         <v>203</v>
@@ -7853,7 +8344,7 @@
         <v>149</v>
       </c>
       <c r="F103" s="23" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="G103" s="23" t="s">
         <v>196</v>
@@ -7865,13 +8356,13 @@
     </row>
     <row r="104" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A104" s="42" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B104" s="51" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C104" s="37" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="D104" s="41" t="s">
         <v>203</v>
@@ -7880,7 +8371,7 @@
         <v>149</v>
       </c>
       <c r="F104" s="23" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="G104" s="23" t="s">
         <v>196</v>
@@ -7892,13 +8383,13 @@
     </row>
     <row r="105" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A105" s="42" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B105" s="51" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C105" s="37" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D105" s="41" t="s">
         <v>203</v>
@@ -7907,7 +8398,7 @@
         <v>149</v>
       </c>
       <c r="F105" s="23" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="G105" s="23" t="s">
         <v>196</v>
@@ -7919,99 +8410,99 @@
     </row>
     <row r="106" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A106" s="42" t="s">
+        <v>295</v>
+      </c>
+      <c r="B106" s="51" t="s">
+        <v>400</v>
+      </c>
+      <c r="C106" s="37" t="s">
+        <v>480</v>
+      </c>
+      <c r="D106" s="41" t="s">
+        <v>203</v>
+      </c>
+      <c r="E106" s="41" t="s">
+        <v>149</v>
+      </c>
+      <c r="F106" s="23" t="s">
+        <v>480</v>
+      </c>
+      <c r="G106" s="23" t="s">
+        <v>196</v>
+      </c>
+      <c r="H106" s="23" t="s">
+        <v>149</v>
+      </c>
+      <c r="I106" s="23"/>
+    </row>
+    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A107" s="42" t="s">
         <v>296</v>
       </c>
-      <c r="B106" s="51" t="s">
+      <c r="B107" s="51" t="s">
         <v>401</v>
       </c>
-      <c r="C106" s="37"/>
-      <c r="D106" s="41"/>
-      <c r="E106" s="41"/>
-      <c r="F106" s="23"/>
-      <c r="G106" s="23"/>
-      <c r="H106" s="23"/>
-      <c r="I106" s="23"/>
-    </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A107" s="39" t="s">
-        <v>297</v>
-      </c>
-      <c r="B107" s="51" t="s">
-        <v>402</v>
-      </c>
-      <c r="C107" s="37" t="s">
-        <v>481</v>
-      </c>
-      <c r="D107" s="41" t="s">
-        <v>203</v>
-      </c>
-      <c r="E107" s="41" t="s">
-        <v>149</v>
-      </c>
-      <c r="F107" s="23" t="s">
-        <v>481</v>
-      </c>
-      <c r="G107" s="23" t="s">
-        <v>196</v>
-      </c>
-      <c r="H107" s="23" t="s">
-        <v>149</v>
-      </c>
+      <c r="C107" s="37"/>
+      <c r="D107" s="41"/>
+      <c r="E107" s="41"/>
+      <c r="F107" s="23"/>
+      <c r="G107" s="23"/>
+      <c r="H107" s="23"/>
       <c r="I107" s="23"/>
     </row>
     <row r="108" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A108" s="39" t="s">
+        <v>297</v>
+      </c>
+      <c r="B108" s="51" t="s">
+        <v>402</v>
+      </c>
+      <c r="C108" s="37" t="s">
+        <v>481</v>
+      </c>
+      <c r="D108" s="41" t="s">
+        <v>203</v>
+      </c>
+      <c r="E108" s="41" t="s">
+        <v>149</v>
+      </c>
+      <c r="F108" s="23" t="s">
+        <v>481</v>
+      </c>
+      <c r="G108" s="23" t="s">
+        <v>196</v>
+      </c>
+      <c r="H108" s="23" t="s">
+        <v>149</v>
+      </c>
+      <c r="I108" s="23"/>
+    </row>
+    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A109" s="39" t="s">
         <v>298</v>
       </c>
-      <c r="B108" s="51" t="s">
+      <c r="B109" s="51" t="s">
         <v>403</v>
       </c>
-      <c r="C108" s="37"/>
-      <c r="D108" s="41"/>
-      <c r="E108" s="41"/>
-      <c r="F108" s="23"/>
-      <c r="G108" s="23"/>
-      <c r="H108" s="23"/>
-      <c r="I108" s="23" t="s">
+      <c r="C109" s="37"/>
+      <c r="D109" s="41"/>
+      <c r="E109" s="41"/>
+      <c r="F109" s="23"/>
+      <c r="G109" s="23"/>
+      <c r="H109" s="23"/>
+      <c r="I109" s="23" t="s">
         <v>529</v>
       </c>
-    </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A109" s="42" t="s">
-        <v>289</v>
-      </c>
-      <c r="B109" s="51" t="s">
-        <v>404</v>
-      </c>
-      <c r="C109" s="37" t="s">
-        <v>482</v>
-      </c>
-      <c r="D109" s="41" t="s">
-        <v>203</v>
-      </c>
-      <c r="E109" s="41" t="s">
-        <v>149</v>
-      </c>
-      <c r="F109" s="23" t="s">
-        <v>482</v>
-      </c>
-      <c r="G109" s="23" t="s">
-        <v>196</v>
-      </c>
-      <c r="H109" s="23" t="s">
-        <v>149</v>
-      </c>
-      <c r="I109" s="23"/>
     </row>
     <row r="110" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A110" s="42" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B110" s="51" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C110" s="37" t="s">
-        <v>635</v>
+        <v>482</v>
       </c>
       <c r="D110" s="41" t="s">
         <v>203</v>
@@ -8019,8 +8510,8 @@
       <c r="E110" s="41" t="s">
         <v>149</v>
       </c>
-      <c r="F110" s="24" t="s">
-        <v>635</v>
+      <c r="F110" s="23" t="s">
+        <v>482</v>
       </c>
       <c r="G110" s="23" t="s">
         <v>196</v>
@@ -8038,49 +8529,49 @@
         <v>405</v>
       </c>
       <c r="C111" s="37" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="D111" s="41" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E111" s="41" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F111" s="24" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="G111" s="23" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="H111" s="23" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="I111" s="23"/>
     </row>
     <row r="112" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A112" s="42" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B112" s="51" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C112" s="37" t="s">
-        <v>483</v>
+        <v>636</v>
       </c>
       <c r="D112" s="41" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E112" s="41" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F112" s="24" t="s">
-        <v>483</v>
+        <v>636</v>
       </c>
       <c r="G112" s="23" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H112" s="23" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I112" s="23"/>
     </row>
@@ -8092,61 +8583,61 @@
         <v>406</v>
       </c>
       <c r="C113" s="37" t="s">
+        <v>483</v>
+      </c>
+      <c r="D113" s="41" t="s">
+        <v>203</v>
+      </c>
+      <c r="E113" s="41" t="s">
+        <v>149</v>
+      </c>
+      <c r="F113" s="24" t="s">
+        <v>483</v>
+      </c>
+      <c r="G113" s="23" t="s">
+        <v>196</v>
+      </c>
+      <c r="H113" s="23" t="s">
+        <v>149</v>
+      </c>
+      <c r="I113" s="23"/>
+    </row>
+    <row r="114" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A114" s="42" t="s">
+        <v>291</v>
+      </c>
+      <c r="B114" s="51" t="s">
+        <v>406</v>
+      </c>
+      <c r="C114" s="37" t="s">
         <v>484</v>
       </c>
-      <c r="D113" s="41" t="s">
+      <c r="D114" s="41" t="s">
         <v>202</v>
       </c>
-      <c r="E113" s="41" t="s">
+      <c r="E114" s="41" t="s">
         <v>150</v>
       </c>
-      <c r="F113" s="24" t="s">
+      <c r="F114" s="24" t="s">
         <v>484</v>
       </c>
-      <c r="G113" s="23" t="s">
+      <c r="G114" s="23" t="s">
         <v>195</v>
       </c>
-      <c r="H113" s="23" t="s">
+      <c r="H114" s="23" t="s">
         <v>150</v>
       </c>
-      <c r="I113" s="23"/>
-    </row>
-    <row r="114" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A114" s="30" t="s">
+      <c r="I114" s="23"/>
+    </row>
+    <row r="115" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A115" s="30" t="s">
         <v>299</v>
       </c>
-      <c r="B114" s="51" t="s">
+      <c r="B115" s="51" t="s">
         <v>407</v>
       </c>
-      <c r="C114" s="37" t="s">
+      <c r="C115" s="37" t="s">
         <v>485</v>
-      </c>
-      <c r="D114" s="41" t="s">
-        <v>203</v>
-      </c>
-      <c r="E114" s="41" t="s">
-        <v>149</v>
-      </c>
-      <c r="F114" s="24" t="s">
-        <v>485</v>
-      </c>
-      <c r="G114" s="23" t="s">
-        <v>196</v>
-      </c>
-      <c r="H114" s="23" t="s">
-        <v>149</v>
-      </c>
-      <c r="I114" s="23"/>
-    </row>
-    <row r="115" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A115" s="42" t="s">
-        <v>300</v>
-      </c>
-      <c r="B115" s="51" t="s">
-        <v>408</v>
-      </c>
-      <c r="C115" s="37" t="s">
-        <v>486</v>
       </c>
       <c r="D115" s="41" t="s">
         <v>203</v>
@@ -8155,7 +8646,7 @@
         <v>149</v>
       </c>
       <c r="F115" s="24" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="G115" s="23" t="s">
         <v>196</v>
@@ -8167,13 +8658,13 @@
     </row>
     <row r="116" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A116" s="42" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B116" s="51" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C116" s="37" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="D116" s="41" t="s">
         <v>203</v>
@@ -8182,7 +8673,7 @@
         <v>149</v>
       </c>
       <c r="F116" s="24" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="G116" s="23" t="s">
         <v>196</v>
@@ -8194,13 +8685,13 @@
     </row>
     <row r="117" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A117" s="42" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B117" s="51" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C117" s="37" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="D117" s="41" t="s">
         <v>203</v>
@@ -8209,7 +8700,7 @@
         <v>149</v>
       </c>
       <c r="F117" s="24" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="G117" s="23" t="s">
         <v>196</v>
@@ -8221,13 +8712,13 @@
     </row>
     <row r="118" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A118" s="42" t="s">
-        <v>292</v>
+        <v>302</v>
       </c>
       <c r="B118" s="51" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C118" s="37" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="D118" s="41" t="s">
         <v>203</v>
@@ -8236,7 +8727,7 @@
         <v>149</v>
       </c>
       <c r="F118" s="24" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="G118" s="23" t="s">
         <v>196</v>
@@ -8248,13 +8739,13 @@
     </row>
     <row r="119" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A119" s="42" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B119" s="51" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C119" s="37" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="D119" s="41" t="s">
         <v>203</v>
@@ -8263,7 +8754,7 @@
         <v>149</v>
       </c>
       <c r="F119" s="24" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="G119" s="23" t="s">
         <v>196</v>
@@ -8275,13 +8766,13 @@
     </row>
     <row r="120" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A120" s="42" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B120" s="51" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C120" s="37" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="D120" s="41" t="s">
         <v>203</v>
@@ -8290,7 +8781,7 @@
         <v>149</v>
       </c>
       <c r="F120" s="24" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="G120" s="23" t="s">
         <v>196</v>
@@ -8302,13 +8793,13 @@
     </row>
     <row r="121" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A121" s="42" t="s">
-        <v>303</v>
+        <v>294</v>
       </c>
       <c r="B121" s="51" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C121" s="37" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="D121" s="41" t="s">
         <v>203</v>
@@ -8317,7 +8808,7 @@
         <v>149</v>
       </c>
       <c r="F121" s="24" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="G121" s="23" t="s">
         <v>196</v>
@@ -8329,13 +8820,13 @@
     </row>
     <row r="122" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A122" s="42" t="s">
-        <v>295</v>
+        <v>303</v>
       </c>
       <c r="B122" s="51" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C122" s="37" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="D122" s="41" t="s">
         <v>203</v>
@@ -8344,7 +8835,7 @@
         <v>149</v>
       </c>
       <c r="F122" s="24" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="G122" s="23" t="s">
         <v>196</v>
@@ -8356,13 +8847,13 @@
     </row>
     <row r="123" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A123" s="42" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B123" s="51" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C123" s="37" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="D123" s="41" t="s">
         <v>203</v>
@@ -8371,7 +8862,7 @@
         <v>149</v>
       </c>
       <c r="F123" s="24" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="G123" s="23" t="s">
         <v>196</v>
@@ -8381,15 +8872,15 @@
       </c>
       <c r="I123" s="23"/>
     </row>
-    <row r="124" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A124" s="44" t="s">
-        <v>304</v>
+    <row r="124" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A124" s="42" t="s">
+        <v>296</v>
       </c>
       <c r="B124" s="51" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C124" s="37" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="D124" s="41" t="s">
         <v>203</v>
@@ -8397,8 +8888,8 @@
       <c r="E124" s="41" t="s">
         <v>149</v>
       </c>
-      <c r="F124" s="23" t="s">
-        <v>495</v>
+      <c r="F124" s="24" t="s">
+        <v>494</v>
       </c>
       <c r="G124" s="23" t="s">
         <v>196</v>
@@ -8408,15 +8899,15 @@
       </c>
       <c r="I124" s="23"/>
     </row>
-    <row r="125" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A125" s="39" t="s">
-        <v>305</v>
+    <row r="125" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A125" s="44" t="s">
+        <v>304</v>
       </c>
       <c r="B125" s="51" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C125" s="37" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="D125" s="41" t="s">
         <v>203</v>
@@ -8425,7 +8916,7 @@
         <v>149</v>
       </c>
       <c r="F125" s="23" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="G125" s="23" t="s">
         <v>196</v>
@@ -8435,52 +8926,76 @@
       </c>
       <c r="I125" s="23"/>
     </row>
-    <row r="126" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A126" s="39" t="s">
+        <v>305</v>
+      </c>
+      <c r="B126" s="51" t="s">
+        <v>418</v>
+      </c>
+      <c r="C126" s="37" t="s">
+        <v>496</v>
+      </c>
+      <c r="D126" s="41" t="s">
+        <v>203</v>
+      </c>
+      <c r="E126" s="41" t="s">
+        <v>149</v>
+      </c>
+      <c r="F126" s="23" t="s">
+        <v>496</v>
+      </c>
+      <c r="G126" s="23" t="s">
+        <v>196</v>
+      </c>
+      <c r="H126" s="23" t="s">
+        <v>149</v>
+      </c>
+      <c r="I126" s="23"/>
+    </row>
+    <row r="127" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A127" s="39" t="s">
         <v>306</v>
       </c>
-      <c r="B126" s="51" t="s">
+      <c r="B127" s="51" t="s">
         <v>419</v>
       </c>
-      <c r="C126" s="37"/>
-      <c r="D126" s="41"/>
-      <c r="E126" s="41"/>
-      <c r="F126" s="23"/>
-      <c r="G126" s="23"/>
-      <c r="H126" s="23"/>
-      <c r="I126" s="23" t="s">
+      <c r="C127" s="37"/>
+      <c r="D127" s="41"/>
+      <c r="E127" s="41"/>
+      <c r="F127" s="23"/>
+      <c r="G127" s="23"/>
+      <c r="H127" s="23"/>
+      <c r="I127" s="23" t="s">
         <v>530</v>
       </c>
     </row>
-    <row r="127" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A127" s="44" t="s">
+    <row r="128" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A128" s="44" t="s">
         <v>307</v>
       </c>
-      <c r="B127" s="51" t="s">
+      <c r="B128" s="51" t="s">
         <v>420</v>
       </c>
-      <c r="C127" s="37" t="s">
+      <c r="C128" s="37" t="s">
         <v>497</v>
       </c>
-      <c r="D127" s="41" t="s">
+      <c r="D128" s="41" t="s">
         <v>203</v>
       </c>
-      <c r="E127" s="41" t="s">
-        <v>149</v>
-      </c>
-      <c r="F127" s="23" t="s">
+      <c r="E128" s="41" t="s">
+        <v>149</v>
+      </c>
+      <c r="F128" s="23" t="s">
         <v>497</v>
       </c>
-      <c r="G127" s="23" t="s">
+      <c r="G128" s="23" t="s">
         <v>196</v>
       </c>
-      <c r="H127" s="23" t="s">
-        <v>149</v>
-      </c>
-      <c r="I127" s="23"/>
-    </row>
-    <row r="128" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="C128" s="16"/>
+      <c r="H128" s="23" t="s">
+        <v>149</v>
+      </c>
+      <c r="I128" s="23"/>
     </row>
     <row r="129" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C129" s="16"/>
@@ -8950,8 +9465,11 @@
     <row r="284" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C284" s="16"/>
     </row>
+    <row r="285" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C285" s="16"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I127" xr:uid="{B82CF358-6F31-4D7F-93EC-0C8D1049DBC2}"/>
+  <autoFilter ref="A1:I128" xr:uid="{B82CF358-6F31-4D7F-93EC-0C8D1049DBC2}"/>
   <mergeCells count="3">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="C2:E2"/>
@@ -8965,19 +9483,19 @@
           <x14:formula1>
             <xm:f>konta!$A$2:$A$19</xm:f>
           </x14:formula1>
-          <xm:sqref>D4:D214</xm:sqref>
+          <xm:sqref>D4:D215</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{6EAF70CE-009F-4A5D-8C05-5D472733BCFB}">
           <x14:formula1>
             <xm:f>konta!$B$2:$B$12</xm:f>
           </x14:formula1>
-          <xm:sqref>E4:E179</xm:sqref>
+          <xm:sqref>E4:E180</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{53D34262-83A1-4432-9E7C-4EBDCF8A37C7}">
           <x14:formula1>
             <xm:f>konta!$A$2:$A$11</xm:f>
           </x14:formula1>
-          <xm:sqref>G4:G251</xm:sqref>
+          <xm:sqref>G4:G252</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -8986,6 +9504,575 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3005DBEC-DB6D-4E65-ACFC-943A10618A89}">
+  <dimension ref="A1:E28"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="63.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="43.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="B1" s="76" t="s">
+        <v>670</v>
+      </c>
+      <c r="C1" s="77"/>
+    </row>
+    <row r="2" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="89" t="s">
+        <v>688</v>
+      </c>
+      <c r="B2" s="90" t="s">
+        <v>614</v>
+      </c>
+      <c r="C2" s="90" t="s">
+        <v>499</v>
+      </c>
+      <c r="D2" s="89" t="s">
+        <v>628</v>
+      </c>
+      <c r="E2" s="89" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A3" s="23" t="s">
+        <v>692</v>
+      </c>
+      <c r="B3" s="79" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="84" t="s">
+        <v>690</v>
+      </c>
+      <c r="D3" s="23" t="s">
+        <v>632</v>
+      </c>
+      <c r="E3" s="23" t="s">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A4" s="23" t="s">
+        <v>693</v>
+      </c>
+      <c r="B4" s="78" t="s">
+        <v>671</v>
+      </c>
+      <c r="C4" s="85" t="s">
+        <v>730</v>
+      </c>
+      <c r="D4" s="23" t="s">
+        <v>632</v>
+      </c>
+      <c r="E4" s="23" t="s">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A5" s="23" t="s">
+        <v>694</v>
+      </c>
+      <c r="B5" s="80" t="s">
+        <v>672</v>
+      </c>
+      <c r="C5" s="86" t="s">
+        <v>691</v>
+      </c>
+      <c r="D5" s="23" t="s">
+        <v>632</v>
+      </c>
+      <c r="E5" s="23" t="s">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A6" s="23" t="s">
+        <v>695</v>
+      </c>
+      <c r="B6" s="81" t="s">
+        <v>673</v>
+      </c>
+      <c r="C6" s="87" t="s">
+        <v>732</v>
+      </c>
+      <c r="D6" s="23" t="s">
+        <v>632</v>
+      </c>
+      <c r="E6" s="23" t="s">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A7" s="23"/>
+      <c r="B7" s="82"/>
+      <c r="C7" s="83"/>
+      <c r="D7" s="23"/>
+      <c r="E7" s="23"/>
+    </row>
+    <row r="8" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A8" s="23"/>
+      <c r="B8" s="82"/>
+      <c r="C8" s="83"/>
+      <c r="D8" s="23"/>
+      <c r="E8" s="23"/>
+    </row>
+    <row r="9" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A9" s="23" t="s">
+        <v>704</v>
+      </c>
+      <c r="B9" s="80" t="s">
+        <v>674</v>
+      </c>
+      <c r="C9" s="86" t="s">
+        <v>696</v>
+      </c>
+      <c r="D9" s="23" t="s">
+        <v>632</v>
+      </c>
+      <c r="E9" s="23" t="s">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A10" s="23" t="s">
+        <v>705</v>
+      </c>
+      <c r="B10" s="78" t="s">
+        <v>675</v>
+      </c>
+      <c r="C10" s="88" t="s">
+        <v>697</v>
+      </c>
+      <c r="D10" s="23" t="s">
+        <v>632</v>
+      </c>
+      <c r="E10" s="23" t="s">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A11" s="23" t="s">
+        <v>706</v>
+      </c>
+      <c r="B11" s="80" t="s">
+        <v>26</v>
+      </c>
+      <c r="C11" s="86" t="s">
+        <v>698</v>
+      </c>
+      <c r="D11" s="23" t="s">
+        <v>632</v>
+      </c>
+      <c r="E11" s="23" t="s">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A12" s="23" t="s">
+        <v>707</v>
+      </c>
+      <c r="B12" s="78" t="s">
+        <v>676</v>
+      </c>
+      <c r="C12" s="88" t="s">
+        <v>699</v>
+      </c>
+      <c r="D12" s="23" t="s">
+        <v>632</v>
+      </c>
+      <c r="E12" s="23" t="s">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A13" s="23" t="s">
+        <v>708</v>
+      </c>
+      <c r="B13" s="80" t="s">
+        <v>677</v>
+      </c>
+      <c r="C13" s="86" t="s">
+        <v>700</v>
+      </c>
+      <c r="D13" s="23" t="s">
+        <v>632</v>
+      </c>
+      <c r="E13" s="23" t="s">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A14" s="23" t="s">
+        <v>709</v>
+      </c>
+      <c r="B14" s="78" t="s">
+        <v>678</v>
+      </c>
+      <c r="C14" s="88" t="s">
+        <v>701</v>
+      </c>
+      <c r="D14" s="23" t="s">
+        <v>632</v>
+      </c>
+      <c r="E14" s="23" t="s">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A15" s="23" t="s">
+        <v>710</v>
+      </c>
+      <c r="B15" s="80" t="s">
+        <v>679</v>
+      </c>
+      <c r="C15" s="86" t="s">
+        <v>702</v>
+      </c>
+      <c r="D15" s="23" t="s">
+        <v>632</v>
+      </c>
+      <c r="E15" s="23" t="s">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A16" s="23" t="s">
+        <v>711</v>
+      </c>
+      <c r="B16" s="78" t="s">
+        <v>680</v>
+      </c>
+      <c r="C16" s="88" t="s">
+        <v>703</v>
+      </c>
+      <c r="D16" s="23" t="s">
+        <v>632</v>
+      </c>
+      <c r="E16" s="23" t="s">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A17" s="23" t="s">
+        <v>712</v>
+      </c>
+      <c r="B17" s="81" t="s">
+        <v>681</v>
+      </c>
+      <c r="C17" s="87" t="s">
+        <v>713</v>
+      </c>
+      <c r="D17" s="23" t="s">
+        <v>632</v>
+      </c>
+      <c r="E17" s="23" t="s">
+        <v>727</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A18" s="23"/>
+      <c r="B18" s="78"/>
+      <c r="C18" s="88"/>
+      <c r="D18" s="23"/>
+      <c r="E18" s="23"/>
+    </row>
+    <row r="19" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A19" s="23" t="s">
+        <v>715</v>
+      </c>
+      <c r="B19" s="81" t="s">
+        <v>682</v>
+      </c>
+      <c r="C19" s="87" t="s">
+        <v>714</v>
+      </c>
+      <c r="D19" s="23" t="s">
+        <v>632</v>
+      </c>
+      <c r="E19" s="23" t="s">
+        <v>727</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A20" s="23"/>
+      <c r="B20" s="78"/>
+      <c r="C20" s="88"/>
+      <c r="D20" s="23"/>
+      <c r="E20" s="23"/>
+    </row>
+    <row r="21" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A21" s="23" t="s">
+        <v>716</v>
+      </c>
+      <c r="B21" s="80" t="s">
+        <v>683</v>
+      </c>
+      <c r="C21" s="86" t="s">
+        <v>595</v>
+      </c>
+      <c r="D21" s="23" t="s">
+        <v>632</v>
+      </c>
+      <c r="E21" s="23" t="s">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A22" s="23" t="s">
+        <v>717</v>
+      </c>
+      <c r="B22" s="78" t="s">
+        <v>684</v>
+      </c>
+      <c r="C22" s="88" t="s">
+        <v>596</v>
+      </c>
+      <c r="D22" s="23" t="s">
+        <v>632</v>
+      </c>
+      <c r="E22" s="23" t="s">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A23" s="23" t="s">
+        <v>718</v>
+      </c>
+      <c r="B23" s="81" t="s">
+        <v>685</v>
+      </c>
+      <c r="C23" s="87" t="s">
+        <v>719</v>
+      </c>
+      <c r="D23" s="23"/>
+      <c r="E23" s="23"/>
+    </row>
+    <row r="24" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A24" s="23"/>
+      <c r="B24" s="78"/>
+      <c r="C24" s="88"/>
+      <c r="D24" s="23"/>
+      <c r="E24" s="23"/>
+    </row>
+    <row r="25" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A25" s="23"/>
+      <c r="B25" s="80"/>
+      <c r="C25" s="86"/>
+      <c r="D25" s="23"/>
+      <c r="E25" s="23"/>
+    </row>
+    <row r="26" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A26" s="23" t="s">
+        <v>720</v>
+      </c>
+      <c r="B26" s="78" t="s">
+        <v>724</v>
+      </c>
+      <c r="C26" s="88" t="s">
+        <v>733</v>
+      </c>
+      <c r="D26" s="23" t="s">
+        <v>632</v>
+      </c>
+      <c r="E26" s="23" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A27" s="23" t="s">
+        <v>721</v>
+      </c>
+      <c r="B27" s="80" t="s">
+        <v>686</v>
+      </c>
+      <c r="C27" s="86" t="s">
+        <v>598</v>
+      </c>
+      <c r="D27" s="23" t="s">
+        <v>729</v>
+      </c>
+      <c r="E27" s="23" t="s">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A28" s="23" t="s">
+        <v>722</v>
+      </c>
+      <c r="B28" s="81" t="s">
+        <v>687</v>
+      </c>
+      <c r="C28" s="87" t="s">
+        <v>723</v>
+      </c>
+      <c r="D28" s="23" t="s">
+        <v>729</v>
+      </c>
+      <c r="E28" s="23" t="s">
+        <v>728</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36172DA7-1A23-4E20-A464-303F5DEDB9DB}">
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="36" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="36.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" s="23" t="s">
+        <v>573</v>
+      </c>
+      <c r="B1" s="23" t="s">
+        <v>748</v>
+      </c>
+      <c r="C1" s="23" t="s">
+        <v>535</v>
+      </c>
+      <c r="D1" s="23" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="23" t="s">
+        <v>749</v>
+      </c>
+      <c r="B2" s="23" t="s">
+        <v>757</v>
+      </c>
+      <c r="C2" s="23" t="s">
+        <v>758</v>
+      </c>
+      <c r="D2" s="23" t="s">
+        <v>767</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="23" t="s">
+        <v>774</v>
+      </c>
+      <c r="B3" s="23" t="s">
+        <v>757</v>
+      </c>
+      <c r="C3" s="23" t="s">
+        <v>759</v>
+      </c>
+      <c r="D3" s="23" t="s">
+        <v>775</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="23" t="s">
+        <v>750</v>
+      </c>
+      <c r="B4" s="23" t="s">
+        <v>757</v>
+      </c>
+      <c r="C4" s="23" t="s">
+        <v>776</v>
+      </c>
+      <c r="D4" s="23" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="23" t="s">
+        <v>751</v>
+      </c>
+      <c r="B5" s="23" t="s">
+        <v>757</v>
+      </c>
+      <c r="C5" s="23" t="s">
+        <v>760</v>
+      </c>
+      <c r="D5" s="23" t="s">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="23" t="s">
+        <v>752</v>
+      </c>
+      <c r="B6" s="23" t="s">
+        <v>757</v>
+      </c>
+      <c r="C6" s="23" t="s">
+        <v>761</v>
+      </c>
+      <c r="D6" s="23" t="s">
+        <v>769</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="23" t="s">
+        <v>753</v>
+      </c>
+      <c r="B7" s="23" t="s">
+        <v>762</v>
+      </c>
+      <c r="C7" s="23" t="s">
+        <v>763</v>
+      </c>
+      <c r="D7" s="23" t="s">
+        <v>770</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="23" t="s">
+        <v>754</v>
+      </c>
+      <c r="B8" s="23" t="s">
+        <v>762</v>
+      </c>
+      <c r="C8" s="92">
+        <v>218</v>
+      </c>
+      <c r="D8" s="23" t="s">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="23" t="s">
+        <v>755</v>
+      </c>
+      <c r="B9" s="23" t="s">
+        <v>764</v>
+      </c>
+      <c r="C9" s="23" t="s">
+        <v>765</v>
+      </c>
+      <c r="D9" s="23" t="s">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="23" t="s">
+        <v>756</v>
+      </c>
+      <c r="B10" s="23" t="s">
+        <v>766</v>
+      </c>
+      <c r="C10" s="23"/>
+      <c r="D10" s="23" t="s">
+        <v>772</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{880F8430-BA4F-490D-BC3E-D695AFB7258C}">
   <dimension ref="A1:E71"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -9717,9 +10804,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2EDE38E9-5973-4784-887D-0B6E302E32A9}">
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="48" customWidth="1"/>
@@ -9751,20 +10838,20 @@
         <v>658</v>
       </c>
       <c r="G1" s="18" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="H1" s="18" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="I1" s="18" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A2" s="33" t="s">
         <v>616</v>
       </c>
-      <c r="B2" s="74" t="s">
+      <c r="B2" s="73" t="s">
         <v>620</v>
       </c>
       <c r="C2" s="33" t="s">
@@ -9777,7 +10864,7 @@
         <v>633</v>
       </c>
       <c r="F2" s="33" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="G2">
         <v>1.75</v>
@@ -9785,15 +10872,15 @@
       <c r="H2">
         <v>1.5</v>
       </c>
-      <c r="I2" s="82" t="s">
-        <v>668</v>
+      <c r="I2" s="75" t="s">
+        <v>666</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="135" x14ac:dyDescent="0.25">
       <c r="A3" s="33" t="s">
         <v>617</v>
       </c>
-      <c r="B3" s="74" t="s">
+      <c r="B3" s="73" t="s">
         <v>621</v>
       </c>
       <c r="C3" s="33" t="s">
@@ -9806,7 +10893,7 @@
         <v>633</v>
       </c>
       <c r="F3" s="33" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="G3">
         <v>1</v>
@@ -9814,15 +10901,15 @@
       <c r="H3">
         <v>1</v>
       </c>
-      <c r="I3" s="82" t="s">
-        <v>669</v>
+      <c r="I3" s="75" t="s">
+        <v>667</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="40.5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>618</v>
       </c>
-      <c r="B4" s="75" t="s">
+      <c r="B4" s="74" t="s">
         <v>624</v>
       </c>
       <c r="C4" t="s">
@@ -9835,15 +10922,15 @@
         <v>632</v>
       </c>
       <c r="F4" t="s">
-        <v>665</v>
-      </c>
-      <c r="I4" s="82"/>
+        <v>663</v>
+      </c>
+      <c r="I4" s="75"/>
     </row>
     <row r="5" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>619</v>
       </c>
-      <c r="B5" s="75" t="s">
+      <c r="B5" s="74" t="s">
         <v>629</v>
       </c>
       <c r="C5" t="s">
@@ -9856,30 +10943,30 @@
         <v>633</v>
       </c>
       <c r="F5" t="s">
-        <v>665</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="40.5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>643</v>
       </c>
-      <c r="B6" s="75" t="s">
+      <c r="B6" s="74" t="s">
         <v>639</v>
       </c>
       <c r="C6" t="s">
         <v>640</v>
       </c>
-      <c r="D6" s="73" t="s">
+      <c r="D6" s="93" t="s">
         <v>641</v>
       </c>
       <c r="E6" t="s">
         <v>642</v>
       </c>
       <c r="F6" t="s">
-        <v>663</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" ht="120" x14ac:dyDescent="0.25">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="81" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>647</v>
       </c>
@@ -9889,54 +10976,54 @@
       <c r="C7" t="s">
         <v>645</v>
       </c>
-      <c r="D7" s="75" t="s">
+      <c r="D7" s="72" t="s">
         <v>646</v>
       </c>
       <c r="E7" t="s">
         <v>642</v>
       </c>
       <c r="F7" t="s">
-        <v>663</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" ht="150" x14ac:dyDescent="0.25">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="121.5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>648</v>
       </c>
-      <c r="B8" s="75" t="s">
+      <c r="B8" s="74" t="s">
         <v>649</v>
       </c>
       <c r="C8" t="s">
         <v>654</v>
       </c>
-      <c r="D8" s="75" t="s">
+      <c r="D8" s="72" t="s">
         <v>650</v>
       </c>
       <c r="E8" t="s">
         <v>633</v>
       </c>
-      <c r="F8" s="75" t="s">
-        <v>663</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+      <c r="F8" s="74" t="s">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="54" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>651</v>
       </c>
-      <c r="B9" s="75" t="s">
+      <c r="B9" s="74" t="s">
         <v>652</v>
       </c>
       <c r="C9" t="s">
         <v>655</v>
       </c>
-      <c r="D9" s="75" t="s">
+      <c r="D9" s="72" t="s">
         <v>653</v>
       </c>
       <c r="E9" t="s">
         <v>633</v>
       </c>
       <c r="F9" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
@@ -9944,21 +11031,91 @@
         <v>659</v>
       </c>
       <c r="B10" t="s">
+        <v>746</v>
+      </c>
+      <c r="C10" t="s">
         <v>660</v>
       </c>
-      <c r="C10" t="s">
-        <v>662</v>
-      </c>
+      <c r="D10" s="94"/>
       <c r="E10" t="s">
         <v>642</v>
       </c>
       <c r="F10" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>734</v>
+      </c>
       <c r="B11" t="s">
-        <v>661</v>
+        <v>747</v>
+      </c>
+      <c r="C11" t="s">
+        <v>745</v>
+      </c>
+      <c r="D11" s="94"/>
+      <c r="E11" t="s">
+        <v>642</v>
+      </c>
+      <c r="F11" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>735</v>
+      </c>
+      <c r="B12" t="s">
+        <v>736</v>
+      </c>
+      <c r="C12" t="s">
+        <v>737</v>
+      </c>
+      <c r="D12" s="70" t="s">
+        <v>738</v>
+      </c>
+      <c r="E12" t="s">
+        <v>642</v>
+      </c>
+      <c r="F12" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>740</v>
+      </c>
+      <c r="B13" t="s">
+        <v>741</v>
+      </c>
+      <c r="C13" t="s">
+        <v>742</v>
+      </c>
+      <c r="D13" s="94"/>
+      <c r="E13" t="s">
+        <v>632</v>
+      </c>
+      <c r="F13" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>743</v>
+      </c>
+      <c r="B14" t="s">
+        <v>744</v>
+      </c>
+      <c r="C14" t="s">
+        <v>778</v>
+      </c>
+      <c r="D14" s="94"/>
+      <c r="E14" t="s">
+        <v>642</v>
+      </c>
+      <c r="F14" t="s">
+        <v>662</v>
       </c>
     </row>
   </sheetData>
@@ -9967,7 +11124,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9ABD1E2F-37D3-428C-9617-FAA26DCBEEA2}">
   <dimension ref="A1:B14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>

--- a/pravila bilansi.xlsx
+++ b/pravila bilansi.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pc1\OneDrive\Desktop\goce proekt\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54908AF6-E868-4AFF-9CFC-2879EB2C270F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{275E9ACC-A850-4637-A815-BF382BD5B252}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{093C95D7-6491-4473-A653-F40FC2BC4264}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{093C95D7-6491-4473-A653-F40FC2BC4264}"/>
   </bookViews>
   <sheets>
     <sheet name="Pravila Bilans Uspeh" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
     <sheet name="konta" sheetId="2" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Pravila bilans Sostojba'!$A$1:$I$128</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Pravila bilans Sostojba'!$A$1:$I$130</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Pravila Bilans Uspeh'!$A$2:$G$75</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1576" uniqueCount="779">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1616" uniqueCount="780">
   <si>
     <r>
       <t xml:space="preserve">Биланс на успехот     </t>
@@ -512,12 +512,6 @@
     <t xml:space="preserve"> -</t>
   </si>
   <si>
-    <t>639,634</t>
-  </si>
-  <si>
-    <t>600,630,633,634,639</t>
-  </si>
-  <si>
     <t>745</t>
   </si>
   <si>
@@ -669,9 +663,6 @@
   </si>
   <si>
     <t>krajno_pobaruva</t>
-  </si>
-  <si>
-    <t>634,639</t>
   </si>
   <si>
     <t>Konto</t>
@@ -1333,9 +1324,6 @@
     <t>112</t>
   </si>
   <si>
-    <t xml:space="preserve">600,630,633,639 </t>
-  </si>
-  <si>
     <t xml:space="preserve">tekovna godina </t>
   </si>
   <si>
@@ -1381,15 +1369,9 @@
     <t>32,35</t>
   </si>
   <si>
-    <t>630</t>
-  </si>
-  <si>
     <t>600</t>
   </si>
   <si>
-    <t>660</t>
-  </si>
-  <si>
     <t>61</t>
   </si>
   <si>
@@ -1402,18 +1384,12 @@
     <t>119</t>
   </si>
   <si>
-    <t>121,129</t>
-  </si>
-  <si>
     <t>120,121,124,125,126,127,129</t>
   </si>
   <si>
     <t>122,123</t>
   </si>
   <si>
-    <t>123</t>
-  </si>
-  <si>
     <t>13</t>
   </si>
   <si>
@@ -1480,9 +1456,6 @@
     <t>960</t>
   </si>
   <si>
-    <t>961</t>
-  </si>
-  <si>
     <t>97</t>
   </si>
   <si>
@@ -1522,9 +1495,6 @@
     <t>222,223</t>
   </si>
   <si>
-    <t>223</t>
-  </si>
-  <si>
     <t>234</t>
   </si>
   <si>
@@ -1738,9 +1708,6 @@
     <t>Нето паричен тек од финансиски активности</t>
   </si>
   <si>
-    <t>Нето намалување на парите во периодот</t>
-  </si>
-  <si>
     <t>Салдо на парите на почетокот на периодот</t>
   </si>
   <si>
@@ -1756,9 +1723,6 @@
     <t>CF03</t>
   </si>
   <si>
-    <t>CF04</t>
-  </si>
-  <si>
     <t>CF05</t>
   </si>
   <si>
@@ -1801,9 +1765,6 @@
     <t>CF08+CF12+CF16</t>
   </si>
   <si>
-    <t>Крајно салдо на периодот</t>
-  </si>
-  <si>
     <t>CF20</t>
   </si>
   <si>
@@ -1976,9 +1937,6 @@
   </si>
   <si>
     <t>220,221,224,225,229,2202</t>
-  </si>
-  <si>
-    <t>221,2202</t>
   </si>
   <si>
     <t>BS004_R</t>
@@ -2451,6 +2409,52 @@
   </si>
   <si>
     <t>(BU255-BU256)/BU201</t>
+  </si>
+  <si>
+    <t>BU255</t>
+  </si>
+  <si>
+    <t>BU256</t>
+  </si>
+  <si>
+    <t>BS085_R</t>
+  </si>
+  <si>
+    <t>100,103</t>
+  </si>
+  <si>
+    <t>600,630,633,639</t>
+  </si>
+  <si>
+    <t>634,639</t>
+  </si>
+  <si>
+    <t>630,633,639</t>
+  </si>
+  <si>
+    <t>Нето зголемување / намалување на парите во периодот</t>
+  </si>
+  <si>
+    <t>Контрола 
+(Нето зголемување/намалување + почетно салдо = крајно салдо)</t>
+  </si>
+  <si>
+    <t>660,663,661</t>
+  </si>
+  <si>
+    <t>664,669</t>
+  </si>
+  <si>
+    <t>BS020_R</t>
+  </si>
+  <si>
+    <t>BS044_R</t>
+  </si>
+  <si>
+    <t>120,121,129</t>
+  </si>
+  <si>
+    <t>220,221,2202</t>
   </si>
 </sst>
 </file>
@@ -2817,7 +2821,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="101">
+  <cellXfs count="103">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -3048,9 +3052,6 @@
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -3058,6 +3059,12 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment shrinkToFit="1"/>
     </xf>
@@ -3075,6 +3082,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3805,12 +3815,12 @@
       <c r="B1" s="2"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B2" s="95" t="s">
+      <c r="B2" s="96" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B3" s="96"/>
+      <c r="B3" s="97"/>
     </row>
     <row r="4" spans="1:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
@@ -3820,7 +3830,7 @@
         <v>2</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>535</v>
+        <v>525</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>142</v>
@@ -3832,10 +3842,10 @@
         <v>144</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>499</v>
+        <v>489</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>532</v>
+        <v>522</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
@@ -3851,8 +3861,8 @@
       <c r="D5" s="7"/>
       <c r="E5" s="23"/>
       <c r="F5" s="23"/>
-      <c r="G5" s="23" t="s">
-        <v>500</v>
+      <c r="G5" s="24" t="s">
+        <v>490</v>
       </c>
       <c r="H5" s="23"/>
     </row>
@@ -3870,7 +3880,7 @@
         <v>145</v>
       </c>
       <c r="E6" s="23" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="F6" s="23" t="s">
         <v>146</v>
@@ -3892,7 +3902,7 @@
         <v>141</v>
       </c>
       <c r="E7" s="23" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="F7" s="23" t="s">
         <v>146</v>
@@ -3925,10 +3935,10 @@
         <v>204</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>421</v>
+        <v>769</v>
       </c>
       <c r="E9" s="23" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="F9" s="23" t="s">
         <v>149</v>
@@ -3936,17 +3946,21 @@
       <c r="G9" s="24"/>
       <c r="H9" s="23"/>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="4"/>
-      <c r="B10" s="8"/>
+    <row r="10" spans="1:8" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A10" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>12</v>
+      </c>
       <c r="C10" s="6">
         <v>204</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>151</v>
+        <v>770</v>
       </c>
       <c r="E10" s="23" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="F10" s="23" t="s">
         <v>150</v>
@@ -3965,10 +3979,10 @@
         <v>205</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>152</v>
+        <v>769</v>
       </c>
       <c r="E11" s="23" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="F11" s="23" t="s">
         <v>149</v>
@@ -3977,16 +3991,20 @@
       <c r="H11" s="23"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="4"/>
-      <c r="B12" s="8"/>
+      <c r="A12" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>14</v>
+      </c>
       <c r="C12" s="6">
         <v>205</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>204</v>
+        <v>770</v>
       </c>
       <c r="E12" s="23" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="F12" s="23" t="s">
         <v>150</v>
@@ -4005,10 +4023,10 @@
         <v>206</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="E13" s="23" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="F13" s="23" t="s">
         <v>149</v>
@@ -4030,7 +4048,7 @@
       <c r="E14" s="23"/>
       <c r="F14" s="23"/>
       <c r="G14" s="24" t="s">
-        <v>501</v>
+        <v>491</v>
       </c>
       <c r="H14" s="23"/>
     </row>
@@ -4045,10 +4063,10 @@
         <v>208</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="E15" s="23" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="F15" s="23" t="s">
         <v>149</v>
@@ -4067,10 +4085,10 @@
         <v>209</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="E16" s="23" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="F16" s="23" t="s">
         <v>149</v>
@@ -4089,10 +4107,10 @@
         <v>210</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="E17" s="23" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="F17" s="23" t="s">
         <v>149</v>
@@ -4111,10 +4129,10 @@
         <v>211</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E18" s="23" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="F18" s="23" t="s">
         <v>149</v>
@@ -4133,10 +4151,10 @@
         <v>212</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="E19" s="23" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="F19" s="23"/>
       <c r="G19" s="24"/>
@@ -4156,7 +4174,7 @@
       <c r="E20" s="23"/>
       <c r="F20" s="23"/>
       <c r="G20" s="24" t="s">
-        <v>502</v>
+        <v>492</v>
       </c>
       <c r="H20" s="23"/>
     </row>
@@ -4171,10 +4189,10 @@
         <v>214</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="E21" s="23" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="F21" s="23" t="s">
         <v>149</v>
@@ -4193,10 +4211,10 @@
         <v>215</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="E22" s="23" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="F22" s="23" t="s">
         <v>149</v>
@@ -4215,10 +4233,10 @@
         <v>216</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="E23" s="23" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="F23" s="23" t="s">
         <v>149</v>
@@ -4237,10 +4255,10 @@
         <v>217</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>498</v>
+        <v>488</v>
       </c>
       <c r="E24" s="23" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="F24" s="23" t="s">
         <v>149</v>
@@ -4259,10 +4277,10 @@
         <v>218</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="E25" s="23" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="F25" s="23" t="s">
         <v>149</v>
@@ -4281,10 +4299,10 @@
         <v>219</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="E26" s="23" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="F26" s="23" t="s">
         <v>149</v>
@@ -4303,10 +4321,10 @@
         <v>220</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="E27" s="23" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="F27" s="23" t="s">
         <v>149</v>
@@ -4325,10 +4343,10 @@
         <v>221</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="E28" s="23" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="F28" s="23" t="s">
         <v>149</v>
@@ -4347,10 +4365,10 @@
         <v>222</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="E29" s="23" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="F29" s="23" t="s">
         <v>149</v>
@@ -4372,7 +4390,7 @@
       <c r="E30" s="23"/>
       <c r="F30" s="23"/>
       <c r="G30" s="24" t="s">
-        <v>503</v>
+        <v>493</v>
       </c>
       <c r="H30" s="23"/>
     </row>
@@ -4390,7 +4408,7 @@
       <c r="E31" s="23"/>
       <c r="F31" s="23"/>
       <c r="G31" s="24" t="s">
-        <v>504</v>
+        <v>494</v>
       </c>
       <c r="H31" s="23"/>
     </row>
@@ -4405,10 +4423,10 @@
         <v>225</v>
       </c>
       <c r="D32" s="7" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="E32" s="23" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="F32" s="23" t="s">
         <v>149</v>
@@ -4427,10 +4445,10 @@
         <v>226</v>
       </c>
       <c r="D33" s="7" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="E33" s="23" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="F33" s="23" t="s">
         <v>149</v>
@@ -4449,10 +4467,10 @@
         <v>227</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="E34" s="23" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="F34" s="23" t="s">
         <v>149</v>
@@ -4471,10 +4489,10 @@
         <v>228</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="E35" s="23" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="F35" s="23" t="s">
         <v>149</v>
@@ -4493,10 +4511,10 @@
         <v>229</v>
       </c>
       <c r="D36" s="7" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="E36" s="23" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="F36" s="23" t="s">
         <v>149</v>
@@ -4515,10 +4533,10 @@
         <v>230</v>
       </c>
       <c r="D37" s="7" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="E37" s="23" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="F37" s="23" t="s">
         <v>149</v>
@@ -4537,10 +4555,10 @@
         <v>231</v>
       </c>
       <c r="D38" s="7" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E38" s="23" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="F38" s="23" t="s">
         <v>149</v>
@@ -4559,10 +4577,10 @@
         <v>232</v>
       </c>
       <c r="D39" s="7" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="E39" s="23" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="F39" s="23" t="s">
         <v>149</v>
@@ -4581,10 +4599,10 @@
         <v>233</v>
       </c>
       <c r="D40" s="7" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="E40" s="23" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="F40" s="23" t="s">
         <v>149</v>
@@ -4606,7 +4624,7 @@
       <c r="E41" s="23"/>
       <c r="F41" s="23"/>
       <c r="G41" s="24" t="s">
-        <v>505</v>
+        <v>495</v>
       </c>
       <c r="H41" s="23"/>
     </row>
@@ -4624,7 +4642,7 @@
       <c r="E42" s="23"/>
       <c r="F42" s="23"/>
       <c r="G42" s="24" t="s">
-        <v>506</v>
+        <v>496</v>
       </c>
       <c r="H42" s="23"/>
     </row>
@@ -4639,10 +4657,10 @@
         <v>236</v>
       </c>
       <c r="D43" s="7" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E43" s="23" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="F43" s="23" t="s">
         <v>149</v>
@@ -4661,10 +4679,10 @@
         <v>237</v>
       </c>
       <c r="D44" s="7" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="E44" s="23" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="F44" s="23" t="s">
         <v>149</v>
@@ -4683,10 +4701,10 @@
         <v>238</v>
       </c>
       <c r="D45" s="7" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="E45" s="23" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="F45" s="23" t="s">
         <v>149</v>
@@ -4705,10 +4723,10 @@
         <v>239</v>
       </c>
       <c r="D46" s="7" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="E46" s="23" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="F46" s="23" t="s">
         <v>149</v>
@@ -4727,10 +4745,10 @@
         <v>240</v>
       </c>
       <c r="D47" s="7" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="E47" s="23" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="F47" s="23" t="s">
         <v>149</v>
@@ -4749,10 +4767,10 @@
         <v>241</v>
       </c>
       <c r="D48" s="7" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="E48" s="23" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="F48" s="23" t="s">
         <v>149</v>
@@ -4771,10 +4789,10 @@
         <v>242</v>
       </c>
       <c r="D49" s="7" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="E49" s="23" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="F49" s="23" t="s">
         <v>149</v>
@@ -4793,10 +4811,10 @@
         <v>243</v>
       </c>
       <c r="D50" s="7" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="E50" s="23" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="F50" s="23" t="s">
         <v>149</v>
@@ -4815,10 +4833,10 @@
         <v>244</v>
       </c>
       <c r="D51" s="7" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="E51" s="23" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="F51" s="23" t="s">
         <v>149</v>
@@ -4837,10 +4855,10 @@
         <v>245</v>
       </c>
       <c r="D52" s="7" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="E52" s="23" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="F52" s="23" t="s">
         <v>149</v>
@@ -4862,10 +4880,10 @@
       <c r="E53" s="23"/>
       <c r="F53" s="23"/>
       <c r="G53" s="24" t="s">
-        <v>531</v>
+        <v>521</v>
       </c>
       <c r="H53" s="23" t="s">
-        <v>533</v>
+        <v>523</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
@@ -4882,10 +4900,10 @@
       <c r="E54" s="23"/>
       <c r="F54" s="23"/>
       <c r="G54" s="24" t="s">
-        <v>531</v>
+        <v>521</v>
       </c>
       <c r="H54" s="23" t="s">
-        <v>534</v>
+        <v>524</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
@@ -4899,10 +4917,10 @@
         <v>248</v>
       </c>
       <c r="D55" s="7" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="E55" s="23" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="F55" s="23" t="s">
         <v>149</v>
@@ -4921,10 +4939,10 @@
         <v>249</v>
       </c>
       <c r="D56" s="7" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="E56" s="23" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="F56" s="23" t="s">
         <v>149</v>
@@ -4946,10 +4964,10 @@
       <c r="E57" s="23"/>
       <c r="F57" s="23"/>
       <c r="G57" s="24" t="s">
-        <v>507</v>
+        <v>497</v>
       </c>
       <c r="H57" s="23" t="s">
-        <v>533</v>
+        <v>523</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
@@ -4966,10 +4984,10 @@
       <c r="E58" s="23"/>
       <c r="F58" s="23"/>
       <c r="G58" s="24" t="s">
-        <v>508</v>
+        <v>498</v>
       </c>
       <c r="H58" s="23" t="s">
-        <v>534</v>
+        <v>524</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
@@ -4983,10 +5001,10 @@
         <v>252</v>
       </c>
       <c r="D59" s="7" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="E59" s="23" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="F59" s="23" t="s">
         <v>149</v>
@@ -5005,10 +5023,10 @@
         <v>253</v>
       </c>
       <c r="D60" s="7" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="E60" s="23" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="F60" s="23" t="s">
         <v>149</v>
@@ -5027,10 +5045,10 @@
         <v>254</v>
       </c>
       <c r="D61" s="7" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="E61" s="23" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="F61" s="23" t="s">
         <v>149</v>
@@ -5052,10 +5070,10 @@
       <c r="E62" s="23"/>
       <c r="F62" s="23"/>
       <c r="G62" s="24" t="s">
-        <v>656</v>
+        <v>642</v>
       </c>
       <c r="H62" s="23" t="s">
-        <v>533</v>
+        <v>523</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
@@ -5072,10 +5090,10 @@
       <c r="E63" s="23"/>
       <c r="F63" s="23"/>
       <c r="G63" s="24" t="s">
-        <v>657</v>
+        <v>643</v>
       </c>
       <c r="H63" s="23" t="s">
-        <v>534</v>
+        <v>524</v>
       </c>
     </row>
     <row r="64" spans="1:8" ht="25.5" x14ac:dyDescent="0.25">
@@ -5137,10 +5155,10 @@
         <v>260</v>
       </c>
       <c r="D67" s="7" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="E67" s="23" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="F67" s="23" t="s">
         <v>149</v>
@@ -5159,10 +5177,10 @@
         <v>261</v>
       </c>
       <c r="D68" s="7" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="E68" s="23" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="F68" s="23" t="s">
         <v>149</v>
@@ -5181,10 +5199,10 @@
         <v>262</v>
       </c>
       <c r="D69" s="7" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="E69" s="23" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="F69" s="23" t="s">
         <v>149</v>
@@ -5203,10 +5221,10 @@
         <v>263</v>
       </c>
       <c r="D70" s="7" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="E70" s="23" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="F70" s="23" t="s">
         <v>149</v>
@@ -5830,7 +5848,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B82CF358-6F31-4D7F-93EC-0C8D1049DBC2}">
-  <dimension ref="A1:I285"/>
+  <dimension ref="A1:I287"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="67.42578125" bestFit="1" customWidth="1"/>
@@ -5838,13 +5856,13 @@
     <col min="3" max="3" width="33.28515625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="16.5703125" customWidth="1"/>
     <col min="5" max="5" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.140625" customWidth="1"/>
+    <col min="6" max="6" width="33.28515625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="19.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="97" t="s">
-        <v>308</v>
+      <c r="A1" s="98" t="s">
+        <v>305</v>
       </c>
       <c r="B1" s="38"/>
       <c r="C1" s="38"/>
@@ -5852,28 +5870,28 @@
       <c r="E1" s="38"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="98"/>
+      <c r="A2" s="99"/>
       <c r="B2" s="38"/>
-      <c r="C2" s="99" t="s">
-        <v>422</v>
-      </c>
-      <c r="D2" s="99"/>
-      <c r="E2" s="99"/>
-      <c r="F2" s="100" t="s">
-        <v>423</v>
-      </c>
-      <c r="G2" s="100"/>
-      <c r="H2" s="100"/>
+      <c r="C2" s="100" t="s">
+        <v>418</v>
+      </c>
+      <c r="D2" s="100"/>
+      <c r="E2" s="100"/>
+      <c r="F2" s="101" t="s">
+        <v>419</v>
+      </c>
+      <c r="G2" s="101"/>
+      <c r="H2" s="101"/>
     </row>
     <row r="3" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A3" s="55" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="57" t="s">
-        <v>535</v>
+        <v>525</v>
       </c>
       <c r="C3" s="56" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="D3" s="56" t="s">
         <v>143</v>
@@ -5882,7 +5900,7 @@
         <v>144</v>
       </c>
       <c r="F3" s="23" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="G3" s="23" t="s">
         <v>143</v>
@@ -5891,64 +5909,64 @@
         <v>144</v>
       </c>
       <c r="I3" s="23" t="s">
-        <v>499</v>
+        <v>489</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="39" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="B4" s="40" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="C4" s="37"/>
       <c r="D4" s="41"/>
       <c r="E4" s="41"/>
-      <c r="F4" s="23"/>
+      <c r="F4" s="24"/>
       <c r="G4" s="23"/>
       <c r="H4" s="23"/>
       <c r="I4" s="23" t="s">
-        <v>509</v>
+        <v>499</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="39" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B5" s="40" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="C5" s="37"/>
       <c r="D5" s="41"/>
       <c r="E5" s="41"/>
-      <c r="F5" s="23"/>
+      <c r="F5" s="24"/>
       <c r="G5" s="23"/>
       <c r="H5" s="23"/>
       <c r="I5" s="23" t="s">
-        <v>510</v>
+        <v>500</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="42" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="B6" s="40" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="C6" s="37" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
       <c r="D6" s="41" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="E6" s="41" t="s">
         <v>149</v>
       </c>
       <c r="F6" s="37" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
       <c r="G6" s="23" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="H6" s="23" t="s">
         <v>149</v>
@@ -5957,25 +5975,25 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="43" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="B7" s="40" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="C7" s="37" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="D7" s="41" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="E7" s="41" t="s">
         <v>149</v>
       </c>
       <c r="F7" s="37" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="G7" s="23" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="H7" s="23" t="s">
         <v>149</v>
@@ -5984,25 +6002,25 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="43" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="B8" s="40" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="C8" s="37" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="D8" s="41" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="E8" s="41" t="s">
         <v>150</v>
       </c>
       <c r="F8" s="37" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="G8" s="23" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="H8" s="23" t="s">
         <v>150</v>
@@ -6011,25 +6029,25 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="43" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="B9" s="40" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="C9" s="37" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="D9" s="41" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="E9" s="41" t="s">
         <v>149</v>
       </c>
-      <c r="F9" s="23" t="s">
-        <v>309</v>
+      <c r="F9" s="24" t="s">
+        <v>306</v>
       </c>
       <c r="G9" s="23" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="H9" s="23" t="s">
         <v>149</v>
@@ -6038,25 +6056,25 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="43" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="B10" s="40" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="C10" s="37" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="D10" s="41" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="E10" s="41" t="s">
         <v>149</v>
       </c>
-      <c r="F10" s="23" t="s">
-        <v>313</v>
+      <c r="F10" s="24" t="s">
+        <v>310</v>
       </c>
       <c r="G10" s="23" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="H10" s="23" t="s">
         <v>149</v>
@@ -6065,25 +6083,25 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="43" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="B11" s="40" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="C11" s="37" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="D11" s="41" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="E11" s="41" t="s">
         <v>149</v>
       </c>
-      <c r="F11" s="23" t="s">
-        <v>314</v>
+      <c r="F11" s="24" t="s">
+        <v>311</v>
       </c>
       <c r="G11" s="23" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="H11" s="23" t="s">
         <v>149</v>
@@ -6092,25 +6110,25 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="43" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="B12" s="40" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="C12" s="37" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="D12" s="41" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="E12" s="41" t="s">
         <v>149</v>
       </c>
-      <c r="F12" s="23" t="s">
-        <v>315</v>
+      <c r="F12" s="24" t="s">
+        <v>312</v>
       </c>
       <c r="G12" s="23" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="H12" s="23" t="s">
         <v>149</v>
@@ -6119,59 +6137,59 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="44" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="B13" s="40" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="C13" s="37"/>
       <c r="D13" s="41"/>
       <c r="E13" s="41"/>
-      <c r="F13" s="23"/>
+      <c r="F13" s="24"/>
       <c r="G13" s="23"/>
       <c r="H13" s="23"/>
       <c r="I13" s="23" t="s">
-        <v>511</v>
+        <v>501</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="43" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="B14" s="40" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="C14" s="37"/>
       <c r="D14" s="41"/>
       <c r="E14" s="41"/>
-      <c r="F14" s="23"/>
+      <c r="F14" s="24"/>
       <c r="G14" s="23"/>
       <c r="H14" s="23"/>
       <c r="I14" s="23" t="s">
-        <v>513</v>
+        <v>503</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="43" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="B15" s="40" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="C15" s="37" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="D15" s="41" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="E15" s="41" t="s">
         <v>149</v>
       </c>
-      <c r="F15" s="23" t="s">
-        <v>318</v>
+      <c r="F15" s="24" t="s">
+        <v>315</v>
       </c>
       <c r="G15" s="23" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="H15" s="23" t="s">
         <v>146</v>
@@ -6180,25 +6198,25 @@
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="43" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="B16" s="40" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="C16" s="37" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="D16" s="41" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="E16" s="41" t="s">
         <v>149</v>
       </c>
-      <c r="F16" s="23" t="s">
-        <v>319</v>
+      <c r="F16" s="24" t="s">
+        <v>316</v>
       </c>
       <c r="G16" s="23" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="H16" s="23" t="s">
         <v>146</v>
@@ -6207,106 +6225,106 @@
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="43" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="B17" s="40" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="C17" s="37" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="D17" s="41" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="E17" s="41" t="s">
         <v>150</v>
       </c>
-      <c r="F17" s="23" t="s">
-        <v>427</v>
+      <c r="F17" s="24" t="s">
+        <v>423</v>
       </c>
       <c r="G17" s="23" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="H17" s="23" t="s">
-        <v>512</v>
+        <v>502</v>
       </c>
       <c r="I17" s="23"/>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="43" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="B18" s="40" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="C18" s="37" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="D18" s="41" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="E18" s="41" t="s">
         <v>149</v>
       </c>
-      <c r="F18" s="23" t="s">
-        <v>320</v>
+      <c r="F18" s="24" t="s">
+        <v>317</v>
       </c>
       <c r="G18" s="23" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="H18" s="23" t="s">
-        <v>512</v>
+        <v>502</v>
       </c>
       <c r="I18" s="23"/>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="43" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="B19" s="40" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="C19" s="37" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="D19" s="41" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="E19" s="41" t="s">
         <v>150</v>
       </c>
-      <c r="F19" s="23" t="s">
-        <v>428</v>
+      <c r="F19" s="24" t="s">
+        <v>424</v>
       </c>
       <c r="G19" s="23" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="H19" s="23" t="s">
-        <v>512</v>
+        <v>502</v>
       </c>
       <c r="I19" s="23"/>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="43" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="B20" s="40" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="C20" s="37" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="D20" s="41" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="E20" s="41" t="s">
         <v>149</v>
       </c>
-      <c r="F20" s="23" t="s">
-        <v>321</v>
+      <c r="F20" s="24" t="s">
+        <v>318</v>
       </c>
       <c r="G20" s="23" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="H20" s="23" t="s">
         <v>146</v>
@@ -6315,67 +6333,79 @@
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" s="43" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="B21" s="40" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="C21" s="37" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="D21" s="41" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="E21" s="41" t="s">
         <v>150</v>
       </c>
-      <c r="F21" s="23" t="s">
-        <v>429</v>
+      <c r="F21" s="24" t="s">
+        <v>425</v>
       </c>
       <c r="G21" s="23" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="H21" s="23" t="s">
-        <v>512</v>
+        <v>502</v>
       </c>
       <c r="I21" s="23"/>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="43" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="B22" s="40" t="s">
-        <v>323</v>
-      </c>
-      <c r="C22" s="37"/>
-      <c r="D22" s="41"/>
-      <c r="E22" s="41"/>
-      <c r="F22" s="23"/>
-      <c r="G22" s="23"/>
-      <c r="H22" s="23"/>
+        <v>320</v>
+      </c>
+      <c r="C22" s="102" t="s">
+        <v>324</v>
+      </c>
+      <c r="D22" s="41" t="s">
+        <v>201</v>
+      </c>
+      <c r="E22" s="41" t="s">
+        <v>150</v>
+      </c>
+      <c r="F22" s="24" t="s">
+        <v>324</v>
+      </c>
+      <c r="G22" s="23" t="s">
+        <v>194</v>
+      </c>
+      <c r="H22" s="23" t="s">
+        <v>502</v>
+      </c>
       <c r="I22" s="23"/>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="43" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="B23" s="40" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="C23" s="37" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="D23" s="41" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="E23" s="41" t="s">
         <v>149</v>
       </c>
-      <c r="F23" s="23" t="s">
-        <v>322</v>
+      <c r="F23" s="24" t="s">
+        <v>319</v>
       </c>
       <c r="G23" s="23" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="H23" s="23" t="s">
         <v>149</v>
@@ -6384,25 +6414,25 @@
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" s="43" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="B24" s="40" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="C24" s="37" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="D24" s="41" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="E24" s="41" t="s">
         <v>149</v>
       </c>
-      <c r="F24" s="23" t="s">
-        <v>325</v>
+      <c r="F24" s="24" t="s">
+        <v>322</v>
       </c>
       <c r="G24" s="23" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="H24" s="23" t="s">
         <v>149</v>
@@ -6411,25 +6441,25 @@
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" s="45" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="B25" s="40" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="C25" s="37" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="D25" s="41" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="E25" s="41" t="s">
         <v>149</v>
       </c>
-      <c r="F25" s="23" t="s">
-        <v>326</v>
+      <c r="F25" s="24" t="s">
+        <v>323</v>
       </c>
       <c r="G25" s="23" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="H25" s="23" t="s">
         <v>149</v>
@@ -6438,25 +6468,25 @@
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" s="43" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="B26" s="40" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="C26" s="37" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="D26" s="41" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="E26" s="41" t="s">
         <v>149</v>
       </c>
-      <c r="F26" s="23" t="s">
-        <v>323</v>
+      <c r="F26" s="24" t="s">
+        <v>320</v>
       </c>
       <c r="G26" s="23" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="H26" s="23" t="s">
         <v>149</v>
@@ -6466,22 +6496,22 @@
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="43"/>
       <c r="B27" s="40" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="C27" s="37" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="D27" s="41" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="E27" s="41" t="s">
         <v>150</v>
       </c>
-      <c r="F27" s="23" t="s">
-        <v>430</v>
+      <c r="F27" s="24" t="s">
+        <v>426</v>
       </c>
       <c r="G27" s="23" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="H27" s="23" t="s">
         <v>150</v>
@@ -6490,57 +6520,69 @@
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" s="46" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="B28" s="40" t="s">
-        <v>328</v>
-      </c>
-      <c r="C28" s="37"/>
-      <c r="D28" s="41"/>
-      <c r="E28" s="41"/>
-      <c r="F28" s="23"/>
-      <c r="G28" s="23"/>
-      <c r="H28" s="23"/>
+        <v>325</v>
+      </c>
+      <c r="C28" s="37" t="s">
+        <v>331</v>
+      </c>
+      <c r="D28" s="41" t="s">
+        <v>200</v>
+      </c>
+      <c r="E28" s="41" t="s">
+        <v>149</v>
+      </c>
+      <c r="F28" s="24" t="s">
+        <v>331</v>
+      </c>
+      <c r="G28" s="23" t="s">
+        <v>193</v>
+      </c>
+      <c r="H28" s="23" t="s">
+        <v>146</v>
+      </c>
       <c r="I28" s="23"/>
     </row>
     <row r="29" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A29" s="46" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="B29" s="40" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="C29" s="37"/>
       <c r="D29" s="41"/>
       <c r="E29" s="41"/>
-      <c r="F29" s="23"/>
+      <c r="F29" s="24"/>
       <c r="G29" s="23"/>
       <c r="H29" s="23"/>
       <c r="I29" s="23" t="s">
-        <v>514</v>
+        <v>504</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" s="43" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="B30" s="40" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="C30" s="37" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="D30" s="41" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="E30" s="41" t="s">
         <v>149</v>
       </c>
-      <c r="F30" s="23" t="s">
-        <v>338</v>
+      <c r="F30" s="24" t="s">
+        <v>335</v>
       </c>
       <c r="G30" s="23" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="H30" s="23" t="s">
         <v>146</v>
@@ -6549,25 +6591,25 @@
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" s="43" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="B31" s="40" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="C31" s="37" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="D31" s="41" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="E31" s="41" t="s">
         <v>149</v>
       </c>
-      <c r="F31" s="23" t="s">
-        <v>339</v>
+      <c r="F31" s="24" t="s">
+        <v>336</v>
       </c>
       <c r="G31" s="23" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="H31" s="23" t="s">
         <v>146</v>
@@ -6576,25 +6618,25 @@
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" s="43" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="B32" s="40" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="C32" s="37" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="D32" s="41" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="E32" s="41" t="s">
         <v>149</v>
       </c>
-      <c r="F32" s="23" t="s">
-        <v>340</v>
+      <c r="F32" s="24" t="s">
+        <v>337</v>
       </c>
       <c r="G32" s="23" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="H32" s="23" t="s">
         <v>146</v>
@@ -6603,25 +6645,25 @@
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" s="43" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="B33" s="40" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="C33" s="37" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="D33" s="41" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="E33" s="41" t="s">
         <v>149</v>
       </c>
-      <c r="F33" s="23" t="s">
-        <v>341</v>
+      <c r="F33" s="24" t="s">
+        <v>338</v>
       </c>
       <c r="G33" s="23" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="H33" s="23" t="s">
         <v>146</v>
@@ -6630,42 +6672,42 @@
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" s="43" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="B34" s="40" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="C34" s="37"/>
       <c r="D34" s="41"/>
       <c r="E34" s="41"/>
-      <c r="F34" s="23"/>
+      <c r="F34" s="24"/>
       <c r="G34" s="23"/>
       <c r="H34" s="23"/>
       <c r="I34" s="23" t="s">
-        <v>515</v>
+        <v>505</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" s="43" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="B35" s="40" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="C35" s="37" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="D35" s="41" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="E35" s="41" t="s">
         <v>149</v>
       </c>
-      <c r="F35" s="23" t="s">
-        <v>342</v>
+      <c r="F35" s="24" t="s">
+        <v>339</v>
       </c>
       <c r="G35" s="23" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="H35" s="23" t="s">
         <v>146</v>
@@ -6674,25 +6716,25 @@
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" s="43" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="B36" s="40" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="C36" s="37" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="D36" s="41" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="E36" s="41" t="s">
         <v>149</v>
       </c>
-      <c r="F36" s="23" t="s">
-        <v>343</v>
+      <c r="F36" s="24" t="s">
+        <v>340</v>
       </c>
       <c r="G36" s="23" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="H36" s="23" t="s">
         <v>146</v>
@@ -6701,25 +6743,25 @@
     </row>
     <row r="37" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A37" s="43" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="B37" s="40" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="C37" s="37" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="D37" s="41" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="E37" s="41" t="s">
         <v>149</v>
       </c>
-      <c r="F37" s="23" t="s">
-        <v>344</v>
+      <c r="F37" s="24" t="s">
+        <v>341</v>
       </c>
       <c r="G37" s="23" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="H37" s="23" t="s">
         <v>146</v>
@@ -6728,25 +6770,25 @@
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" s="43" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="B38" s="40" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="C38" s="37" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="D38" s="41" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="E38" s="41" t="s">
         <v>149</v>
       </c>
-      <c r="F38" s="23" t="s">
-        <v>431</v>
+      <c r="F38" s="24" t="s">
+        <v>427</v>
       </c>
       <c r="G38" s="23" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="H38" s="23" t="s">
         <v>146</v>
@@ -6755,42 +6797,42 @@
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" s="46" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="B39" s="40" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="C39" s="37"/>
       <c r="D39" s="41"/>
       <c r="E39" s="41"/>
-      <c r="F39" s="23"/>
+      <c r="F39" s="24"/>
       <c r="G39" s="23"/>
       <c r="H39" s="23"/>
       <c r="I39" s="23" t="s">
-        <v>516</v>
+        <v>506</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" s="43" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="B40" s="40" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="C40" s="37" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="D40" s="41" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="E40" s="41" t="s">
         <v>149</v>
       </c>
-      <c r="F40" s="23" t="s">
-        <v>348</v>
+      <c r="F40" s="24" t="s">
+        <v>345</v>
       </c>
       <c r="G40" s="23" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="H40" s="23" t="s">
         <v>149</v>
@@ -6799,25 +6841,25 @@
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" s="43" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="B41" s="40" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="C41" s="37" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="D41" s="41" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="E41" s="41" t="s">
         <v>149</v>
       </c>
-      <c r="F41" s="23" t="s">
-        <v>349</v>
+      <c r="F41" s="24" t="s">
+        <v>346</v>
       </c>
       <c r="G41" s="23" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="H41" s="23" t="s">
         <v>149</v>
@@ -6826,25 +6868,25 @@
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" s="43" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="B42" s="40" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="C42" s="37" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="D42" s="41" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="E42" s="41" t="s">
         <v>149</v>
       </c>
-      <c r="F42" s="23" t="s">
-        <v>432</v>
+      <c r="F42" s="24" t="s">
+        <v>428</v>
       </c>
       <c r="G42" s="23" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="H42" s="23" t="s">
         <v>149</v>
@@ -6853,25 +6895,25 @@
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" s="46" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="B43" s="40" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="C43" s="37" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="D43" s="41" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="E43" s="41" t="s">
         <v>149</v>
       </c>
-      <c r="F43" s="23" t="s">
-        <v>433</v>
+      <c r="F43" s="24" t="s">
+        <v>429</v>
       </c>
       <c r="G43" s="23" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="H43" s="23" t="s">
         <v>149</v>
@@ -6880,59 +6922,59 @@
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" s="47" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="B44" s="40" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="C44" s="37"/>
       <c r="D44" s="41"/>
       <c r="E44" s="41"/>
-      <c r="F44" s="23"/>
+      <c r="F44" s="24"/>
       <c r="G44" s="23"/>
       <c r="H44" s="23"/>
       <c r="I44" s="23" t="s">
-        <v>517</v>
+        <v>507</v>
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" s="44" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="B45" s="40" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="C45" s="37"/>
       <c r="D45" s="41"/>
       <c r="E45" s="41"/>
-      <c r="F45" s="23"/>
+      <c r="F45" s="24"/>
       <c r="G45" s="23"/>
       <c r="H45" s="23"/>
       <c r="I45" s="23" t="s">
-        <v>518</v>
+        <v>508</v>
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" s="43" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="B46" s="40" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="C46" s="37" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="D46" s="41" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="E46" s="41" t="s">
         <v>149</v>
       </c>
-      <c r="F46" s="23" t="s">
-        <v>434</v>
+      <c r="F46" s="24" t="s">
+        <v>430</v>
       </c>
       <c r="G46" s="23" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="H46" s="23" t="s">
         <v>149</v>
@@ -6941,25 +6983,25 @@
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47" s="43" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="B47" s="40" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="C47" s="37" t="s">
-        <v>435</v>
+        <v>431</v>
       </c>
       <c r="D47" s="41" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="E47" s="41" t="s">
         <v>150</v>
       </c>
-      <c r="F47" s="23" t="s">
-        <v>435</v>
+      <c r="F47" s="24" t="s">
+        <v>431</v>
       </c>
       <c r="G47" s="23" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="H47" s="23" t="s">
         <v>150</v>
@@ -6968,25 +7010,25 @@
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48" s="45" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="B48" s="40" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="C48" s="37" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="D48" s="41" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="E48" s="41" t="s">
         <v>149</v>
       </c>
-      <c r="F48" s="23" t="s">
-        <v>436</v>
+      <c r="F48" s="24" t="s">
+        <v>432</v>
       </c>
       <c r="G48" s="23" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="H48" s="23" t="s">
         <v>149</v>
@@ -6995,25 +7037,25 @@
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" s="43" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="B49" s="40" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="C49" s="37" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="D49" s="41" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="E49" s="41" t="s">
         <v>149</v>
       </c>
-      <c r="F49" s="23" t="s">
-        <v>438</v>
+      <c r="F49" s="24" t="s">
+        <v>433</v>
       </c>
       <c r="G49" s="23" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="H49" s="23" t="s">
         <v>149</v>
@@ -7022,25 +7064,25 @@
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" s="43" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="B50" s="40" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="C50" s="37" t="s">
-        <v>437</v>
+        <v>771</v>
       </c>
       <c r="D50" s="41" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="E50" s="41" t="s">
         <v>149</v>
       </c>
-      <c r="F50" s="23" t="s">
-        <v>437</v>
+      <c r="F50" s="94" t="s">
+        <v>771</v>
       </c>
       <c r="G50" s="23" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="H50" s="23" t="s">
         <v>149</v>
@@ -7049,123 +7091,131 @@
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" s="43" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="B51" s="40" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="C51" s="37" t="s">
-        <v>439</v>
+        <v>770</v>
       </c>
       <c r="D51" s="41" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E51" s="41" t="s">
-        <v>149</v>
-      </c>
-      <c r="F51" s="23" t="s">
-        <v>439</v>
+        <v>150</v>
+      </c>
+      <c r="F51" s="94" t="s">
+        <v>770</v>
       </c>
       <c r="G51" s="23" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H51" s="23" t="s">
-        <v>149</v>
+        <v>502</v>
       </c>
       <c r="I51" s="23"/>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" s="43" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="B52" s="40" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="C52" s="37" t="s">
-        <v>440</v>
+        <v>774</v>
       </c>
       <c r="D52" s="41" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="E52" s="41" t="s">
         <v>149</v>
       </c>
-      <c r="F52" s="23" t="s">
-        <v>440</v>
+      <c r="F52" s="24" t="s">
+        <v>774</v>
       </c>
       <c r="G52" s="23" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="H52" s="23" t="s">
         <v>149</v>
       </c>
       <c r="I52" s="23"/>
     </row>
-    <row r="53" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A53" s="44" t="s">
-        <v>249</v>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A53" s="43" t="s">
+        <v>244</v>
       </c>
       <c r="B53" s="40" t="s">
-        <v>352</v>
+        <v>347</v>
       </c>
       <c r="C53" s="37" t="s">
-        <v>441</v>
+        <v>775</v>
       </c>
       <c r="D53" s="41" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E53" s="41" t="s">
-        <v>149</v>
-      </c>
-      <c r="F53" s="23" t="s">
-        <v>441</v>
+        <v>150</v>
+      </c>
+      <c r="F53" s="24" t="s">
+        <v>775</v>
       </c>
       <c r="G53" s="23" t="s">
-        <v>195</v>
-      </c>
-      <c r="H53" s="23" t="s">
-        <v>149</v>
-      </c>
+        <v>194</v>
+      </c>
+      <c r="H53" s="23"/>
       <c r="I53" s="23"/>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A54" s="44" t="s">
-        <v>250</v>
+      <c r="A54" s="43" t="s">
+        <v>245</v>
       </c>
       <c r="B54" s="40" t="s">
-        <v>353</v>
-      </c>
-      <c r="C54" s="37"/>
-      <c r="D54" s="41"/>
-      <c r="E54" s="41"/>
-      <c r="F54" s="23"/>
-      <c r="G54" s="23"/>
-      <c r="H54" s="23"/>
-      <c r="I54" s="23" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A55" s="43" t="s">
-        <v>237</v>
+        <v>348</v>
+      </c>
+      <c r="C54" s="37" t="s">
+        <v>434</v>
+      </c>
+      <c r="D54" s="41" t="s">
+        <v>200</v>
+      </c>
+      <c r="E54" s="41" t="s">
+        <v>149</v>
+      </c>
+      <c r="F54" s="24" t="s">
+        <v>434</v>
+      </c>
+      <c r="G54" s="23" t="s">
+        <v>193</v>
+      </c>
+      <c r="H54" s="23" t="s">
+        <v>149</v>
+      </c>
+      <c r="I54" s="23"/>
+    </row>
+    <row r="55" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A55" s="44" t="s">
+        <v>246</v>
       </c>
       <c r="B55" s="40" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="C55" s="37" t="s">
-        <v>442</v>
+        <v>435</v>
       </c>
       <c r="D55" s="41" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="E55" s="41" t="s">
         <v>149</v>
       </c>
-      <c r="F55" s="23" t="s">
-        <v>442</v>
+      <c r="F55" s="24" t="s">
+        <v>435</v>
       </c>
       <c r="G55" s="23" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="H55" s="23" t="s">
         <v>149</v>
@@ -7173,53 +7223,43 @@
       <c r="I55" s="23"/>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A56" s="43" t="s">
-        <v>237</v>
+      <c r="A56" s="44" t="s">
+        <v>247</v>
       </c>
       <c r="B56" s="40" t="s">
-        <v>354</v>
-      </c>
-      <c r="C56" s="37" t="s">
-        <v>443</v>
-      </c>
-      <c r="D56" s="41" t="s">
-        <v>203</v>
-      </c>
-      <c r="E56" s="41" t="s">
-        <v>150</v>
-      </c>
-      <c r="F56" s="23" t="s">
-        <v>443</v>
-      </c>
-      <c r="G56" s="23" t="s">
-        <v>196</v>
-      </c>
-      <c r="H56" s="23" t="s">
-        <v>150</v>
-      </c>
-      <c r="I56" s="23"/>
+        <v>350</v>
+      </c>
+      <c r="C56" s="37"/>
+      <c r="D56" s="41"/>
+      <c r="E56" s="41"/>
+      <c r="F56" s="24"/>
+      <c r="G56" s="23"/>
+      <c r="H56" s="23"/>
+      <c r="I56" s="23" t="s">
+        <v>509</v>
+      </c>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" s="43" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="B57" s="40" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="C57" s="37" t="s">
-        <v>445</v>
+        <v>436</v>
       </c>
       <c r="D57" s="41" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="E57" s="41" t="s">
         <v>149</v>
       </c>
-      <c r="F57" s="23" t="s">
-        <v>445</v>
+      <c r="F57" s="24" t="s">
+        <v>436</v>
       </c>
       <c r="G57" s="23" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="H57" s="23" t="s">
         <v>149</v>
@@ -7228,25 +7268,25 @@
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" s="43" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="B58" s="40" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="C58" s="37" t="s">
-        <v>444</v>
+        <v>437</v>
       </c>
       <c r="D58" s="41" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="E58" s="41" t="s">
         <v>150</v>
       </c>
-      <c r="F58" s="23" t="s">
-        <v>444</v>
+      <c r="F58" s="24" t="s">
+        <v>437</v>
       </c>
       <c r="G58" s="23" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="H58" s="23" t="s">
         <v>150</v>
@@ -7255,25 +7295,25 @@
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59" s="43" t="s">
-        <v>251</v>
+        <v>235</v>
       </c>
       <c r="B59" s="40" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="C59" s="37" t="s">
-        <v>446</v>
+        <v>438</v>
       </c>
       <c r="D59" s="41" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="E59" s="41" t="s">
         <v>149</v>
       </c>
-      <c r="F59" s="23" t="s">
-        <v>446</v>
+      <c r="F59" s="24" t="s">
+        <v>438</v>
       </c>
       <c r="G59" s="23" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="H59" s="23" t="s">
         <v>149</v>
@@ -7282,248 +7322,248 @@
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" s="43" t="s">
-        <v>251</v>
+        <v>235</v>
       </c>
       <c r="B60" s="40" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="C60" s="37" t="s">
-        <v>447</v>
+        <v>778</v>
       </c>
       <c r="D60" s="41" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="E60" s="41" t="s">
         <v>150</v>
       </c>
-      <c r="F60" s="23" t="s">
-        <v>447</v>
+      <c r="F60" s="24" t="s">
+        <v>778</v>
       </c>
       <c r="G60" s="23" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="H60" s="23" t="s">
         <v>150</v>
       </c>
       <c r="I60" s="23"/>
     </row>
-    <row r="61" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" s="43" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="B61" s="40" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="C61" s="37" t="s">
-        <v>669</v>
+        <v>439</v>
       </c>
       <c r="D61" s="41" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="E61" s="41" t="s">
         <v>149</v>
       </c>
-      <c r="F61" s="23" t="s">
-        <v>448</v>
+      <c r="F61" s="24" t="s">
+        <v>439</v>
       </c>
       <c r="G61" s="23" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="H61" s="23" t="s">
         <v>149</v>
       </c>
       <c r="I61" s="23"/>
     </row>
-    <row r="62" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" s="43" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="B62" s="40" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="C62" s="37" t="s">
-        <v>448</v>
+        <v>439</v>
       </c>
       <c r="D62" s="41" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="E62" s="41" t="s">
         <v>150</v>
       </c>
-      <c r="F62" s="92">
+      <c r="F62" s="24" t="s">
+        <v>439</v>
+      </c>
+      <c r="G62" s="23" t="s">
+        <v>194</v>
+      </c>
+      <c r="H62" s="23" t="s">
+        <v>150</v>
+      </c>
+      <c r="I62" s="23"/>
+    </row>
+    <row r="63" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A63" s="43" t="s">
+        <v>249</v>
+      </c>
+      <c r="B63" s="40" t="s">
+        <v>354</v>
+      </c>
+      <c r="C63" s="37" t="s">
+        <v>655</v>
+      </c>
+      <c r="D63" s="41" t="s">
+        <v>200</v>
+      </c>
+      <c r="E63" s="41" t="s">
+        <v>149</v>
+      </c>
+      <c r="F63" s="24" t="s">
+        <v>440</v>
+      </c>
+      <c r="G63" s="23" t="s">
+        <v>193</v>
+      </c>
+      <c r="H63" s="23" t="s">
+        <v>149</v>
+      </c>
+      <c r="I63" s="23"/>
+    </row>
+    <row r="64" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A64" s="43" t="s">
+        <v>249</v>
+      </c>
+      <c r="B64" s="40" t="s">
+        <v>354</v>
+      </c>
+      <c r="C64" s="37" t="s">
+        <v>440</v>
+      </c>
+      <c r="D64" s="41" t="s">
+        <v>201</v>
+      </c>
+      <c r="E64" s="41" t="s">
+        <v>150</v>
+      </c>
+      <c r="F64" s="94">
         <v>13</v>
       </c>
-      <c r="G62" s="23" t="s">
-        <v>196</v>
-      </c>
-      <c r="H62" s="23" t="s">
-        <v>512</v>
-      </c>
-      <c r="I62" s="23"/>
-    </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A63" s="43" t="s">
-        <v>253</v>
-      </c>
-      <c r="B63" s="40" t="s">
-        <v>358</v>
-      </c>
-      <c r="C63" s="37" t="s">
-        <v>449</v>
-      </c>
-      <c r="D63" s="41" t="s">
-        <v>202</v>
-      </c>
-      <c r="E63" s="41" t="s">
-        <v>149</v>
-      </c>
-      <c r="F63" s="23" t="s">
-        <v>449</v>
-      </c>
-      <c r="G63" s="23" t="s">
-        <v>195</v>
-      </c>
-      <c r="H63" s="23" t="s">
-        <v>149</v>
-      </c>
-      <c r="I63" s="23"/>
-    </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A64" s="48" t="s">
-        <v>254</v>
-      </c>
-      <c r="B64" s="40" t="s">
-        <v>359</v>
-      </c>
-      <c r="C64" s="37" t="s">
-        <v>450</v>
-      </c>
-      <c r="D64" s="41" t="s">
-        <v>202</v>
-      </c>
-      <c r="E64" s="41" t="s">
-        <v>149</v>
-      </c>
-      <c r="F64" s="23" t="s">
-        <v>450</v>
-      </c>
       <c r="G64" s="23" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H64" s="23" t="s">
-        <v>149</v>
+        <v>502</v>
       </c>
       <c r="I64" s="23"/>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A65" s="44" t="s">
-        <v>255</v>
+      <c r="A65" s="43" t="s">
+        <v>250</v>
       </c>
       <c r="B65" s="40" t="s">
-        <v>360</v>
-      </c>
-      <c r="C65" s="37"/>
-      <c r="D65" s="41"/>
-      <c r="E65" s="41"/>
-      <c r="F65" s="23"/>
-      <c r="G65" s="23"/>
-      <c r="H65" s="23"/>
-      <c r="I65" s="23" t="s">
-        <v>520</v>
-      </c>
+        <v>355</v>
+      </c>
+      <c r="C65" s="37" t="s">
+        <v>441</v>
+      </c>
+      <c r="D65" s="41" t="s">
+        <v>200</v>
+      </c>
+      <c r="E65" s="41" t="s">
+        <v>149</v>
+      </c>
+      <c r="F65" s="24" t="s">
+        <v>441</v>
+      </c>
+      <c r="G65" s="23" t="s">
+        <v>193</v>
+      </c>
+      <c r="H65" s="23" t="s">
+        <v>149</v>
+      </c>
+      <c r="I65" s="23"/>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A66" s="43" t="s">
-        <v>256</v>
+      <c r="A66" s="48" t="s">
+        <v>251</v>
       </c>
       <c r="B66" s="40" t="s">
-        <v>361</v>
-      </c>
-      <c r="C66" s="37"/>
-      <c r="D66" s="41"/>
-      <c r="E66" s="41"/>
-      <c r="F66" s="23"/>
-      <c r="G66" s="23"/>
-      <c r="H66" s="23"/>
-      <c r="I66" s="23" t="s">
-        <v>521</v>
-      </c>
+        <v>356</v>
+      </c>
+      <c r="C66" s="37" t="s">
+        <v>442</v>
+      </c>
+      <c r="D66" s="41" t="s">
+        <v>200</v>
+      </c>
+      <c r="E66" s="41" t="s">
+        <v>149</v>
+      </c>
+      <c r="F66" s="24" t="s">
+        <v>442</v>
+      </c>
+      <c r="G66" s="23" t="s">
+        <v>193</v>
+      </c>
+      <c r="H66" s="23" t="s">
+        <v>149</v>
+      </c>
+      <c r="I66" s="23"/>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A67" s="43" t="s">
-        <v>257</v>
+      <c r="A67" s="44" t="s">
+        <v>252</v>
       </c>
       <c r="B67" s="40" t="s">
-        <v>362</v>
-      </c>
-      <c r="C67" s="37" t="s">
-        <v>451</v>
-      </c>
-      <c r="D67" s="41" t="s">
-        <v>202</v>
-      </c>
-      <c r="E67" s="41" t="s">
-        <v>149</v>
-      </c>
-      <c r="F67" s="23" t="s">
-        <v>451</v>
-      </c>
-      <c r="G67" s="23" t="s">
-        <v>195</v>
-      </c>
-      <c r="H67" s="23" t="s">
-        <v>146</v>
-      </c>
-      <c r="I67" s="23"/>
+        <v>357</v>
+      </c>
+      <c r="C67" s="37"/>
+      <c r="D67" s="41"/>
+      <c r="E67" s="41"/>
+      <c r="F67" s="24"/>
+      <c r="G67" s="23"/>
+      <c r="H67" s="23"/>
+      <c r="I67" s="23" t="s">
+        <v>510</v>
+      </c>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68" s="43" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="B68" s="40" t="s">
-        <v>363</v>
-      </c>
-      <c r="C68" s="37" t="s">
-        <v>452</v>
-      </c>
-      <c r="D68" s="41" t="s">
-        <v>202</v>
-      </c>
-      <c r="E68" s="41" t="s">
-        <v>149</v>
-      </c>
-      <c r="F68" s="23" t="s">
-        <v>452</v>
-      </c>
-      <c r="G68" s="23" t="s">
-        <v>195</v>
-      </c>
-      <c r="H68" s="23" t="s">
-        <v>146</v>
-      </c>
-      <c r="I68" s="23"/>
+        <v>358</v>
+      </c>
+      <c r="C68" s="37"/>
+      <c r="D68" s="41"/>
+      <c r="E68" s="41"/>
+      <c r="F68" s="24"/>
+      <c r="G68" s="23"/>
+      <c r="H68" s="23"/>
+      <c r="I68" s="23" t="s">
+        <v>511</v>
+      </c>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A69" s="43" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="B69" s="40" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="C69" s="37" t="s">
-        <v>453</v>
+        <v>443</v>
       </c>
       <c r="D69" s="41" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="E69" s="41" t="s">
         <v>149</v>
       </c>
-      <c r="F69" s="23" t="s">
-        <v>453</v>
+      <c r="F69" s="24" t="s">
+        <v>443</v>
       </c>
       <c r="G69" s="23" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="H69" s="23" t="s">
         <v>146</v>
@@ -7532,25 +7572,25 @@
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70" s="43" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="B70" s="40" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="C70" s="37" t="s">
-        <v>454</v>
+        <v>444</v>
       </c>
       <c r="D70" s="41" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="E70" s="41" t="s">
         <v>149</v>
       </c>
-      <c r="F70" s="23" t="s">
-        <v>454</v>
+      <c r="F70" s="24" t="s">
+        <v>444</v>
       </c>
       <c r="G70" s="23" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="H70" s="23" t="s">
         <v>146</v>
@@ -7559,25 +7599,25 @@
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71" s="43" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="B71" s="40" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="C71" s="37" t="s">
-        <v>455</v>
+        <v>445</v>
       </c>
       <c r="D71" s="41" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="E71" s="41" t="s">
         <v>149</v>
       </c>
-      <c r="F71" s="23" t="s">
-        <v>455</v>
+      <c r="F71" s="24" t="s">
+        <v>445</v>
       </c>
       <c r="G71" s="23" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="H71" s="23" t="s">
         <v>146</v>
@@ -7585,266 +7625,266 @@
       <c r="I71" s="23"/>
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A72" s="44" t="s">
-        <v>262</v>
+      <c r="A72" s="43" t="s">
+        <v>257</v>
       </c>
       <c r="B72" s="40" t="s">
-        <v>367</v>
-      </c>
-      <c r="C72" s="37"/>
-      <c r="D72" s="41"/>
-      <c r="E72" s="41"/>
-      <c r="F72" s="23"/>
-      <c r="G72" s="23"/>
-      <c r="H72" s="23"/>
-      <c r="I72" s="23" t="s">
-        <v>522</v>
-      </c>
+        <v>362</v>
+      </c>
+      <c r="C72" s="37" t="s">
+        <v>446</v>
+      </c>
+      <c r="D72" s="41" t="s">
+        <v>200</v>
+      </c>
+      <c r="E72" s="41" t="s">
+        <v>149</v>
+      </c>
+      <c r="F72" s="24" t="s">
+        <v>446</v>
+      </c>
+      <c r="G72" s="23" t="s">
+        <v>193</v>
+      </c>
+      <c r="H72" s="23" t="s">
+        <v>146</v>
+      </c>
+      <c r="I72" s="23"/>
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A73" s="43" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="B73" s="40" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="C73" s="37" t="s">
-        <v>456</v>
+        <v>447</v>
       </c>
       <c r="D73" s="41" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="E73" s="41" t="s">
         <v>149</v>
       </c>
-      <c r="F73" s="23" t="s">
-        <v>456</v>
+      <c r="F73" s="24" t="s">
+        <v>447</v>
       </c>
       <c r="G73" s="23" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="H73" s="23" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="I73" s="23"/>
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A74" s="43" t="s">
-        <v>263</v>
+      <c r="A74" s="44" t="s">
+        <v>259</v>
       </c>
       <c r="B74" s="40" t="s">
-        <v>368</v>
-      </c>
-      <c r="C74" s="37" t="s">
-        <v>731</v>
-      </c>
-      <c r="D74" s="41" t="s">
-        <v>203</v>
-      </c>
-      <c r="E74" s="41" t="s">
-        <v>150</v>
-      </c>
-      <c r="F74" s="91">
-        <v>103100</v>
-      </c>
-      <c r="G74" s="23" t="s">
-        <v>196</v>
-      </c>
-      <c r="H74" s="23" t="s">
-        <v>150</v>
-      </c>
-      <c r="I74" s="23"/>
+        <v>364</v>
+      </c>
+      <c r="C74" s="37"/>
+      <c r="D74" s="41"/>
+      <c r="E74" s="41"/>
+      <c r="F74" s="24"/>
+      <c r="G74" s="23"/>
+      <c r="H74" s="23"/>
+      <c r="I74" s="23" t="s">
+        <v>512</v>
+      </c>
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A75" s="43" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="B75" s="40" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="C75" s="37" t="s">
-        <v>457</v>
+        <v>448</v>
       </c>
       <c r="D75" s="41" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="E75" s="41" t="s">
         <v>149</v>
       </c>
-      <c r="F75" s="23" t="s">
-        <v>457</v>
+      <c r="F75" s="24" t="s">
+        <v>448</v>
       </c>
       <c r="G75" s="23" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="H75" s="23" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="I75" s="23"/>
     </row>
-    <row r="76" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A76" s="46" t="s">
-        <v>265</v>
+    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A76" s="43" t="s">
+        <v>260</v>
       </c>
       <c r="B76" s="40" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="C76" s="37" t="s">
-        <v>458</v>
+        <v>717</v>
       </c>
       <c r="D76" s="41" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E76" s="41" t="s">
-        <v>149</v>
-      </c>
-      <c r="F76" s="23" t="s">
-        <v>458</v>
+        <v>150</v>
+      </c>
+      <c r="F76" s="94" t="s">
+        <v>768</v>
       </c>
       <c r="G76" s="23" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H76" s="23" t="s">
-        <v>149</v>
+        <v>502</v>
       </c>
       <c r="I76" s="23"/>
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A77" s="49" t="s">
-        <v>266</v>
+      <c r="A77" s="43" t="s">
+        <v>261</v>
       </c>
       <c r="B77" s="40" t="s">
-        <v>371</v>
-      </c>
-      <c r="C77" s="37"/>
-      <c r="D77" s="41"/>
-      <c r="E77" s="41"/>
-      <c r="F77" s="23"/>
-      <c r="G77" s="23"/>
-      <c r="H77" s="23"/>
-      <c r="I77" s="23" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A78" s="44" t="s">
-        <v>267</v>
+        <v>366</v>
+      </c>
+      <c r="C77" s="37" t="s">
+        <v>449</v>
+      </c>
+      <c r="D77" s="41" t="s">
+        <v>200</v>
+      </c>
+      <c r="E77" s="41" t="s">
+        <v>149</v>
+      </c>
+      <c r="F77" s="24" t="s">
+        <v>449</v>
+      </c>
+      <c r="G77" s="23" t="s">
+        <v>193</v>
+      </c>
+      <c r="H77" s="23" t="s">
+        <v>149</v>
+      </c>
+      <c r="I77" s="23"/>
+    </row>
+    <row r="78" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A78" s="46" t="s">
+        <v>262</v>
       </c>
       <c r="B78" s="40" t="s">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="C78" s="37" t="s">
-        <v>459</v>
+        <v>450</v>
       </c>
       <c r="D78" s="41" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="E78" s="41" t="s">
         <v>149</v>
       </c>
-      <c r="F78" s="23" t="s">
-        <v>459</v>
+      <c r="F78" s="24" t="s">
+        <v>450</v>
       </c>
       <c r="G78" s="23" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="H78" s="23" t="s">
         <v>149</v>
       </c>
       <c r="I78" s="23"/>
     </row>
-    <row r="79" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A79" s="46" t="s">
-        <v>268</v>
+    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A79" s="49" t="s">
+        <v>263</v>
       </c>
       <c r="B79" s="40" t="s">
-        <v>373</v>
+        <v>368</v>
       </c>
       <c r="C79" s="37"/>
       <c r="D79" s="41"/>
       <c r="E79" s="41"/>
-      <c r="F79" s="23"/>
+      <c r="F79" s="24"/>
       <c r="G79" s="23"/>
       <c r="H79" s="23"/>
       <c r="I79" s="23" t="s">
-        <v>524</v>
+        <v>513</v>
       </c>
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A80" s="50" t="s">
-        <v>269</v>
+      <c r="A80" s="44" t="s">
+        <v>264</v>
       </c>
       <c r="B80" s="40" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="C80" s="37" t="s">
-        <v>460</v>
+        <v>451</v>
       </c>
       <c r="D80" s="41" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="E80" s="41" t="s">
         <v>149</v>
       </c>
-      <c r="F80" s="23" t="s">
-        <v>460</v>
+      <c r="F80" s="24" t="s">
+        <v>451</v>
       </c>
       <c r="G80" s="23" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="H80" s="23" t="s">
         <v>149</v>
       </c>
       <c r="I80" s="23"/>
     </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A81" s="44" t="s">
-        <v>270</v>
+    <row r="81" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A81" s="46" t="s">
+        <v>265</v>
       </c>
       <c r="B81" s="40" t="s">
-        <v>375</v>
-      </c>
-      <c r="C81" s="37" t="s">
-        <v>461</v>
-      </c>
-      <c r="D81" s="41" t="s">
-        <v>203</v>
-      </c>
-      <c r="E81" s="41" t="s">
-        <v>149</v>
-      </c>
-      <c r="F81" s="23" t="s">
-        <v>461</v>
-      </c>
-      <c r="G81" s="23" t="s">
-        <v>196</v>
-      </c>
-      <c r="H81" s="23" t="s">
-        <v>149</v>
-      </c>
-      <c r="I81" s="23"/>
+        <v>370</v>
+      </c>
+      <c r="C81" s="37"/>
+      <c r="D81" s="41"/>
+      <c r="E81" s="41"/>
+      <c r="F81" s="24"/>
+      <c r="G81" s="23"/>
+      <c r="H81" s="23"/>
+      <c r="I81" s="23" t="s">
+        <v>514</v>
+      </c>
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A82" s="44" t="s">
-        <v>271</v>
+      <c r="A82" s="50" t="s">
+        <v>266</v>
       </c>
       <c r="B82" s="40" t="s">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="C82" s="37" t="s">
-        <v>462</v>
+        <v>452</v>
       </c>
       <c r="D82" s="41" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="E82" s="41" t="s">
         <v>149</v>
       </c>
-      <c r="F82" s="23" t="s">
-        <v>462</v>
+      <c r="F82" s="24" t="s">
+        <v>452</v>
       </c>
       <c r="G82" s="23" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="H82" s="23" t="s">
         <v>149</v>
@@ -7853,52 +7893,52 @@
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A83" s="44" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="B83" s="40" t="s">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="C83" s="37" t="s">
-        <v>463</v>
+        <v>453</v>
       </c>
       <c r="D83" s="41" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="E83" s="41" t="s">
         <v>149</v>
       </c>
-      <c r="F83" s="23" t="s">
-        <v>463</v>
+      <c r="F83" s="24" t="s">
+        <v>453</v>
       </c>
       <c r="G83" s="23" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="H83" s="23" t="s">
         <v>149</v>
       </c>
       <c r="I83" s="23"/>
     </row>
-    <row r="84" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A84" s="46" t="s">
-        <v>273</v>
+    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A84" s="44" t="s">
+        <v>268</v>
       </c>
       <c r="B84" s="40" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="C84" s="37" t="s">
-        <v>464</v>
+        <v>454</v>
       </c>
       <c r="D84" s="41" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="E84" s="41" t="s">
         <v>149</v>
       </c>
-      <c r="F84" s="23" t="s">
-        <v>464</v>
+      <c r="F84" s="24" t="s">
+        <v>454</v>
       </c>
       <c r="G84" s="23" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="H84" s="23" t="s">
         <v>149</v>
@@ -7907,42 +7947,52 @@
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A85" s="44" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="B85" s="40" t="s">
-        <v>379</v>
-      </c>
-      <c r="C85" s="37"/>
-      <c r="D85" s="41"/>
-      <c r="E85" s="41"/>
-      <c r="F85" s="23"/>
-      <c r="G85" s="23"/>
-      <c r="H85" s="23"/>
-      <c r="I85" s="23" t="s">
-        <v>525</v>
-      </c>
-    </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A86" s="48" t="s">
-        <v>275</v>
+        <v>374</v>
+      </c>
+      <c r="C85" s="37" t="s">
+        <v>455</v>
+      </c>
+      <c r="D85" s="41" t="s">
+        <v>201</v>
+      </c>
+      <c r="E85" s="41" t="s">
+        <v>149</v>
+      </c>
+      <c r="F85" s="24" t="s">
+        <v>455</v>
+      </c>
+      <c r="G85" s="23" t="s">
+        <v>194</v>
+      </c>
+      <c r="H85" s="23" t="s">
+        <v>149</v>
+      </c>
+      <c r="I85" s="23"/>
+    </row>
+    <row r="86" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A86" s="46" t="s">
+        <v>270</v>
       </c>
       <c r="B86" s="40" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="C86" s="37" t="s">
-        <v>465</v>
+        <v>456</v>
       </c>
       <c r="D86" s="41" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="E86" s="41" t="s">
         <v>149</v>
       </c>
-      <c r="F86" s="23" t="s">
-        <v>465</v>
+      <c r="F86" s="24" t="s">
+        <v>456</v>
       </c>
       <c r="G86" s="23" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="H86" s="23" t="s">
         <v>149</v>
@@ -7950,53 +8000,43 @@
       <c r="I86" s="23"/>
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A87" s="48" t="s">
-        <v>276</v>
+      <c r="A87" s="44" t="s">
+        <v>271</v>
       </c>
       <c r="B87" s="40" t="s">
-        <v>381</v>
-      </c>
-      <c r="C87" s="37" t="s">
-        <v>466</v>
-      </c>
-      <c r="D87" s="41" t="s">
-        <v>203</v>
-      </c>
-      <c r="E87" s="41" t="s">
-        <v>149</v>
-      </c>
-      <c r="F87" s="23" t="s">
-        <v>466</v>
-      </c>
-      <c r="G87" s="23" t="s">
-        <v>196</v>
-      </c>
-      <c r="H87" s="23" t="s">
-        <v>149</v>
-      </c>
-      <c r="I87" s="23"/>
+        <v>376</v>
+      </c>
+      <c r="C87" s="37"/>
+      <c r="D87" s="41"/>
+      <c r="E87" s="41"/>
+      <c r="F87" s="24"/>
+      <c r="G87" s="23"/>
+      <c r="H87" s="23"/>
+      <c r="I87" s="23" t="s">
+        <v>515</v>
+      </c>
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A88" s="48" t="s">
-        <v>277</v>
-      </c>
-      <c r="B88" s="51" t="s">
-        <v>382</v>
+        <v>272</v>
+      </c>
+      <c r="B88" s="40" t="s">
+        <v>377</v>
       </c>
       <c r="C88" s="37" t="s">
-        <v>467</v>
+        <v>457</v>
       </c>
       <c r="D88" s="41" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="E88" s="41" t="s">
         <v>149</v>
       </c>
-      <c r="F88" s="23" t="s">
-        <v>467</v>
+      <c r="F88" s="24" t="s">
+        <v>457</v>
       </c>
       <c r="G88" s="23" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="H88" s="23" t="s">
         <v>149</v>
@@ -8004,26 +8044,26 @@
       <c r="I88" s="23"/>
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A89" s="44" t="s">
-        <v>278</v>
-      </c>
-      <c r="B89" s="51" t="s">
-        <v>383</v>
+      <c r="A89" s="48" t="s">
+        <v>273</v>
+      </c>
+      <c r="B89" s="40" t="s">
+        <v>378</v>
       </c>
       <c r="C89" s="37" t="s">
-        <v>468</v>
+        <v>458</v>
       </c>
       <c r="D89" s="41" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="E89" s="41" t="s">
         <v>149</v>
       </c>
-      <c r="F89" s="23" t="s">
-        <v>468</v>
+      <c r="F89" s="24" t="s">
+        <v>458</v>
       </c>
       <c r="G89" s="23" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="H89" s="23" t="s">
         <v>149</v>
@@ -8031,26 +8071,26 @@
       <c r="I89" s="23"/>
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A90" s="44" t="s">
-        <v>279</v>
+      <c r="A90" s="48" t="s">
+        <v>274</v>
       </c>
       <c r="B90" s="51" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="C90" s="37" t="s">
-        <v>469</v>
+        <v>459</v>
       </c>
       <c r="D90" s="41" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E90" s="41" t="s">
         <v>149</v>
       </c>
-      <c r="F90" s="23" t="s">
-        <v>469</v>
+      <c r="F90" s="24" t="s">
+        <v>459</v>
       </c>
       <c r="G90" s="23" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H90" s="23" t="s">
         <v>149</v>
@@ -8059,25 +8099,25 @@
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A91" s="44" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="B91" s="51" t="s">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="C91" s="37" t="s">
-        <v>470</v>
+        <v>460</v>
       </c>
       <c r="D91" s="41" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E91" s="41" t="s">
         <v>149</v>
       </c>
-      <c r="F91" s="23" t="s">
-        <v>470</v>
+      <c r="F91" s="24" t="s">
+        <v>460</v>
       </c>
       <c r="G91" s="23" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H91" s="23" t="s">
         <v>149</v>
@@ -8086,187 +8126,197 @@
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A92" s="44" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="B92" s="51" t="s">
-        <v>386</v>
-      </c>
-      <c r="C92" s="37"/>
-      <c r="D92" s="41"/>
-      <c r="E92" s="41"/>
-      <c r="F92" s="23"/>
-      <c r="G92" s="23"/>
-      <c r="H92" s="23"/>
+        <v>381</v>
+      </c>
+      <c r="C92" s="37" t="s">
+        <v>461</v>
+      </c>
+      <c r="D92" s="41" t="s">
+        <v>200</v>
+      </c>
+      <c r="E92" s="41" t="s">
+        <v>149</v>
+      </c>
+      <c r="F92" s="24" t="s">
+        <v>461</v>
+      </c>
+      <c r="G92" s="23" t="s">
+        <v>193</v>
+      </c>
+      <c r="H92" s="23" t="s">
+        <v>149</v>
+      </c>
       <c r="I92" s="23"/>
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A93" s="52" t="s">
-        <v>282</v>
+      <c r="A93" s="44" t="s">
+        <v>277</v>
       </c>
       <c r="B93" s="51" t="s">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="C93" s="37" t="s">
-        <v>471</v>
-      </c>
-      <c r="D93" s="41" t="s">
-        <v>203</v>
-      </c>
-      <c r="E93" s="41" t="s">
-        <v>149</v>
-      </c>
-      <c r="F93" s="23" t="s">
-        <v>471</v>
+        <v>765</v>
+      </c>
+      <c r="D93" s="41"/>
+      <c r="E93" s="41"/>
+      <c r="F93" s="24">
+        <v>951</v>
       </c>
       <c r="G93" s="23" t="s">
-        <v>196</v>
-      </c>
-      <c r="H93" s="23" t="s">
-        <v>149</v>
-      </c>
+        <v>193</v>
+      </c>
+      <c r="H93" s="23"/>
       <c r="I93" s="23"/>
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A94" s="53" t="s">
-        <v>283</v>
+      <c r="A94" s="44" t="s">
+        <v>278</v>
       </c>
       <c r="B94" s="51" t="s">
-        <v>388</v>
-      </c>
-      <c r="C94" s="37"/>
+        <v>383</v>
+      </c>
+      <c r="C94" s="37" t="s">
+        <v>766</v>
+      </c>
       <c r="D94" s="41"/>
       <c r="E94" s="41"/>
-      <c r="F94" s="23"/>
-      <c r="G94" s="23"/>
+      <c r="F94" s="24">
+        <v>961</v>
+      </c>
+      <c r="G94" s="23" t="s">
+        <v>194</v>
+      </c>
       <c r="H94" s="23"/>
       <c r="I94" s="23"/>
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A95" s="53" t="s">
-        <v>284</v>
+      <c r="A95" s="52" t="s">
+        <v>279</v>
       </c>
       <c r="B95" s="51" t="s">
-        <v>389</v>
-      </c>
-      <c r="C95" s="37"/>
-      <c r="D95" s="41"/>
-      <c r="E95" s="41"/>
-      <c r="F95" s="23"/>
-      <c r="G95" s="23"/>
-      <c r="H95" s="23"/>
-      <c r="I95" s="23" t="s">
-        <v>526</v>
-      </c>
+        <v>384</v>
+      </c>
+      <c r="C95" s="37" t="s">
+        <v>462</v>
+      </c>
+      <c r="D95" s="41" t="s">
+        <v>201</v>
+      </c>
+      <c r="E95" s="41" t="s">
+        <v>149</v>
+      </c>
+      <c r="F95" s="24" t="s">
+        <v>462</v>
+      </c>
+      <c r="G95" s="23" t="s">
+        <v>194</v>
+      </c>
+      <c r="H95" s="23" t="s">
+        <v>149</v>
+      </c>
+      <c r="I95" s="23"/>
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A96" s="44" t="s">
-        <v>285</v>
+      <c r="A96" s="53" t="s">
+        <v>280</v>
       </c>
       <c r="B96" s="51" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="C96" s="37"/>
       <c r="D96" s="41"/>
       <c r="E96" s="41"/>
-      <c r="F96" s="23"/>
+      <c r="F96" s="24"/>
       <c r="G96" s="23"/>
       <c r="H96" s="23"/>
-      <c r="I96" s="23" t="s">
-        <v>527</v>
-      </c>
+      <c r="I96" s="23"/>
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A97" s="48" t="s">
-        <v>286</v>
+      <c r="A97" s="53" t="s">
+        <v>281</v>
       </c>
       <c r="B97" s="51" t="s">
-        <v>391</v>
-      </c>
-      <c r="C97" s="37" t="s">
-        <v>472</v>
-      </c>
-      <c r="D97" s="41" t="s">
-        <v>203</v>
-      </c>
-      <c r="E97" s="41" t="s">
-        <v>149</v>
-      </c>
-      <c r="F97" s="23" t="s">
-        <v>472</v>
-      </c>
-      <c r="G97" s="23" t="s">
-        <v>196</v>
-      </c>
-      <c r="H97" s="23" t="s">
-        <v>149</v>
-      </c>
-      <c r="I97" s="23"/>
+        <v>386</v>
+      </c>
+      <c r="C97" s="37"/>
+      <c r="D97" s="41"/>
+      <c r="E97" s="41"/>
+      <c r="F97" s="24"/>
+      <c r="G97" s="23"/>
+      <c r="H97" s="23"/>
+      <c r="I97" s="23" t="s">
+        <v>516</v>
+      </c>
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A98" s="54" t="s">
-        <v>287</v>
+      <c r="A98" s="44" t="s">
+        <v>282</v>
       </c>
       <c r="B98" s="51" t="s">
-        <v>392</v>
-      </c>
-      <c r="C98" s="37" t="s">
-        <v>473</v>
-      </c>
-      <c r="D98" s="41" t="s">
-        <v>203</v>
-      </c>
-      <c r="E98" s="41" t="s">
-        <v>149</v>
-      </c>
-      <c r="F98" s="23" t="s">
-        <v>473</v>
-      </c>
-      <c r="G98" s="23" t="s">
-        <v>196</v>
-      </c>
-      <c r="H98" s="23" t="s">
-        <v>149</v>
-      </c>
-      <c r="I98" s="23"/>
+        <v>387</v>
+      </c>
+      <c r="C98" s="37"/>
+      <c r="D98" s="41"/>
+      <c r="E98" s="41"/>
+      <c r="F98" s="24"/>
+      <c r="G98" s="23"/>
+      <c r="H98" s="23"/>
+      <c r="I98" s="23" t="s">
+        <v>517</v>
+      </c>
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A99" s="39" t="s">
-        <v>288</v>
+      <c r="A99" s="48" t="s">
+        <v>283</v>
       </c>
       <c r="B99" s="51" t="s">
-        <v>393</v>
-      </c>
-      <c r="C99" s="37"/>
-      <c r="D99" s="41"/>
-      <c r="E99" s="41"/>
-      <c r="F99" s="23"/>
-      <c r="G99" s="23"/>
-      <c r="H99" s="23"/>
-      <c r="I99" s="23" t="s">
-        <v>528</v>
-      </c>
+        <v>388</v>
+      </c>
+      <c r="C99" s="37" t="s">
+        <v>463</v>
+      </c>
+      <c r="D99" s="41" t="s">
+        <v>201</v>
+      </c>
+      <c r="E99" s="41" t="s">
+        <v>149</v>
+      </c>
+      <c r="F99" s="24" t="s">
+        <v>463</v>
+      </c>
+      <c r="G99" s="23" t="s">
+        <v>194</v>
+      </c>
+      <c r="H99" s="23" t="s">
+        <v>149</v>
+      </c>
+      <c r="I99" s="23"/>
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A100" s="42" t="s">
-        <v>289</v>
+      <c r="A100" s="54" t="s">
+        <v>284</v>
       </c>
       <c r="B100" s="51" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="C100" s="37" t="s">
-        <v>474</v>
+        <v>464</v>
       </c>
       <c r="D100" s="41" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="E100" s="41" t="s">
         <v>149</v>
       </c>
-      <c r="F100" s="23" t="s">
-        <v>474</v>
+      <c r="F100" s="24" t="s">
+        <v>464</v>
       </c>
       <c r="G100" s="23" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="H100" s="23" t="s">
         <v>149</v>
@@ -8274,53 +8324,43 @@
       <c r="I100" s="23"/>
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A101" s="42" t="s">
-        <v>290</v>
+      <c r="A101" s="39" t="s">
+        <v>285</v>
       </c>
       <c r="B101" s="51" t="s">
-        <v>395</v>
-      </c>
-      <c r="C101" s="37" t="s">
-        <v>475</v>
-      </c>
-      <c r="D101" s="41" t="s">
-        <v>203</v>
-      </c>
-      <c r="E101" s="41" t="s">
-        <v>149</v>
-      </c>
-      <c r="F101" s="23" t="s">
-        <v>475</v>
-      </c>
-      <c r="G101" s="23" t="s">
-        <v>196</v>
-      </c>
-      <c r="H101" s="23" t="s">
-        <v>149</v>
-      </c>
-      <c r="I101" s="23"/>
+        <v>390</v>
+      </c>
+      <c r="C101" s="37"/>
+      <c r="D101" s="41"/>
+      <c r="E101" s="41"/>
+      <c r="F101" s="24"/>
+      <c r="G101" s="23"/>
+      <c r="H101" s="23"/>
+      <c r="I101" s="23" t="s">
+        <v>518</v>
+      </c>
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A102" s="42" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="B102" s="51" t="s">
-        <v>396</v>
+        <v>391</v>
       </c>
       <c r="C102" s="37" t="s">
-        <v>476</v>
+        <v>465</v>
       </c>
       <c r="D102" s="41" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="E102" s="41" t="s">
         <v>149</v>
       </c>
-      <c r="F102" s="23" t="s">
-        <v>476</v>
+      <c r="F102" s="24" t="s">
+        <v>465</v>
       </c>
       <c r="G102" s="23" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="H102" s="23" t="s">
         <v>149</v>
@@ -8329,25 +8369,25 @@
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A103" s="42" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="B103" s="51" t="s">
-        <v>397</v>
+        <v>392</v>
       </c>
       <c r="C103" s="37" t="s">
-        <v>477</v>
+        <v>466</v>
       </c>
       <c r="D103" s="41" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="E103" s="41" t="s">
         <v>149</v>
       </c>
-      <c r="F103" s="23" t="s">
-        <v>477</v>
+      <c r="F103" s="24" t="s">
+        <v>466</v>
       </c>
       <c r="G103" s="23" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="H103" s="23" t="s">
         <v>149</v>
@@ -8356,25 +8396,25 @@
     </row>
     <row r="104" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A104" s="42" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="B104" s="51" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="C104" s="37" t="s">
-        <v>478</v>
+        <v>467</v>
       </c>
       <c r="D104" s="41" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="E104" s="41" t="s">
         <v>149</v>
       </c>
-      <c r="F104" s="23" t="s">
-        <v>478</v>
+      <c r="F104" s="24" t="s">
+        <v>467</v>
       </c>
       <c r="G104" s="23" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="H104" s="23" t="s">
         <v>149</v>
@@ -8383,25 +8423,25 @@
     </row>
     <row r="105" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A105" s="42" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="B105" s="51" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="C105" s="37" t="s">
-        <v>479</v>
+        <v>468</v>
       </c>
       <c r="D105" s="41" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="E105" s="41" t="s">
         <v>149</v>
       </c>
-      <c r="F105" s="23" t="s">
-        <v>479</v>
+      <c r="F105" s="24" t="s">
+        <v>468</v>
       </c>
       <c r="G105" s="23" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="H105" s="23" t="s">
         <v>149</v>
@@ -8410,25 +8450,25 @@
     </row>
     <row r="106" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A106" s="42" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="B106" s="51" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="C106" s="37" t="s">
-        <v>480</v>
+        <v>469</v>
       </c>
       <c r="D106" s="41" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="E106" s="41" t="s">
         <v>149</v>
       </c>
-      <c r="F106" s="23" t="s">
-        <v>480</v>
+      <c r="F106" s="24" t="s">
+        <v>469</v>
       </c>
       <c r="G106" s="23" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="H106" s="23" t="s">
         <v>149</v>
@@ -8437,40 +8477,52 @@
     </row>
     <row r="107" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A107" s="42" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="B107" s="51" t="s">
-        <v>401</v>
-      </c>
-      <c r="C107" s="37"/>
-      <c r="D107" s="41"/>
-      <c r="E107" s="41"/>
-      <c r="F107" s="23"/>
-      <c r="G107" s="23"/>
-      <c r="H107" s="23"/>
+        <v>396</v>
+      </c>
+      <c r="C107" s="37" t="s">
+        <v>470</v>
+      </c>
+      <c r="D107" s="41" t="s">
+        <v>201</v>
+      </c>
+      <c r="E107" s="41" t="s">
+        <v>149</v>
+      </c>
+      <c r="F107" s="24" t="s">
+        <v>470</v>
+      </c>
+      <c r="G107" s="23" t="s">
+        <v>194</v>
+      </c>
+      <c r="H107" s="23" t="s">
+        <v>149</v>
+      </c>
       <c r="I107" s="23"/>
     </row>
     <row r="108" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A108" s="39" t="s">
-        <v>297</v>
+      <c r="A108" s="42" t="s">
+        <v>292</v>
       </c>
       <c r="B108" s="51" t="s">
-        <v>402</v>
+        <v>397</v>
       </c>
       <c r="C108" s="37" t="s">
-        <v>481</v>
+        <v>471</v>
       </c>
       <c r="D108" s="41" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="E108" s="41" t="s">
         <v>149</v>
       </c>
-      <c r="F108" s="23" t="s">
-        <v>481</v>
+      <c r="F108" s="24" t="s">
+        <v>471</v>
       </c>
       <c r="G108" s="23" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="H108" s="23" t="s">
         <v>149</v>
@@ -8478,43 +8530,41 @@
       <c r="I108" s="23"/>
     </row>
     <row r="109" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A109" s="39" t="s">
-        <v>298</v>
+      <c r="A109" s="42" t="s">
+        <v>293</v>
       </c>
       <c r="B109" s="51" t="s">
-        <v>403</v>
+        <v>398</v>
       </c>
       <c r="C109" s="37"/>
       <c r="D109" s="41"/>
       <c r="E109" s="41"/>
-      <c r="F109" s="23"/>
+      <c r="F109" s="24"/>
       <c r="G109" s="23"/>
       <c r="H109" s="23"/>
-      <c r="I109" s="23" t="s">
-        <v>529</v>
-      </c>
+      <c r="I109" s="23"/>
     </row>
     <row r="110" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A110" s="42" t="s">
-        <v>289</v>
+      <c r="A110" s="39" t="s">
+        <v>294</v>
       </c>
       <c r="B110" s="51" t="s">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="C110" s="37" t="s">
-        <v>482</v>
+        <v>472</v>
       </c>
       <c r="D110" s="41" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="E110" s="41" t="s">
         <v>149</v>
       </c>
-      <c r="F110" s="23" t="s">
-        <v>482</v>
+      <c r="F110" s="24" t="s">
+        <v>472</v>
       </c>
       <c r="G110" s="23" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="H110" s="23" t="s">
         <v>149</v>
@@ -8522,80 +8572,70 @@
       <c r="I110" s="23"/>
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A111" s="42" t="s">
-        <v>290</v>
+      <c r="A111" s="39" t="s">
+        <v>295</v>
       </c>
       <c r="B111" s="51" t="s">
-        <v>405</v>
-      </c>
-      <c r="C111" s="37" t="s">
-        <v>635</v>
-      </c>
-      <c r="D111" s="41" t="s">
-        <v>203</v>
-      </c>
-      <c r="E111" s="41" t="s">
-        <v>149</v>
-      </c>
-      <c r="F111" s="24" t="s">
-        <v>635</v>
-      </c>
-      <c r="G111" s="23" t="s">
-        <v>196</v>
-      </c>
-      <c r="H111" s="23" t="s">
-        <v>149</v>
-      </c>
-      <c r="I111" s="23"/>
+        <v>400</v>
+      </c>
+      <c r="C111" s="37"/>
+      <c r="D111" s="41"/>
+      <c r="E111" s="41"/>
+      <c r="F111" s="24"/>
+      <c r="G111" s="23"/>
+      <c r="H111" s="23"/>
+      <c r="I111" s="23" t="s">
+        <v>519</v>
+      </c>
     </row>
     <row r="112" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A112" s="42" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="B112" s="51" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="C112" s="37" t="s">
-        <v>636</v>
+        <v>473</v>
       </c>
       <c r="D112" s="41" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E112" s="41" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F112" s="24" t="s">
-        <v>636</v>
+        <v>473</v>
       </c>
       <c r="G112" s="23" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H112" s="23" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="I112" s="23"/>
     </row>
     <row r="113" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A113" s="42" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="B113" s="51" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="C113" s="37" t="s">
-        <v>483</v>
+        <v>622</v>
       </c>
       <c r="D113" s="41" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="E113" s="41" t="s">
         <v>149</v>
       </c>
       <c r="F113" s="24" t="s">
-        <v>483</v>
+        <v>622</v>
       </c>
       <c r="G113" s="23" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="H113" s="23" t="s">
         <v>149</v>
@@ -8604,25 +8644,25 @@
     </row>
     <row r="114" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A114" s="42" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="B114" s="51" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="C114" s="37" t="s">
-        <v>484</v>
+        <v>779</v>
       </c>
       <c r="D114" s="41" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="E114" s="41" t="s">
         <v>150</v>
       </c>
       <c r="F114" s="24" t="s">
-        <v>484</v>
+        <v>779</v>
       </c>
       <c r="G114" s="23" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="H114" s="23" t="s">
         <v>150</v>
@@ -8630,26 +8670,26 @@
       <c r="I114" s="23"/>
     </row>
     <row r="115" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A115" s="30" t="s">
-        <v>299</v>
+      <c r="A115" s="42" t="s">
+        <v>288</v>
       </c>
       <c r="B115" s="51" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="C115" s="37" t="s">
-        <v>485</v>
+        <v>474</v>
       </c>
       <c r="D115" s="41" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="E115" s="41" t="s">
         <v>149</v>
       </c>
       <c r="F115" s="24" t="s">
-        <v>485</v>
+        <v>474</v>
       </c>
       <c r="G115" s="23" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="H115" s="23" t="s">
         <v>149</v>
@@ -8658,52 +8698,52 @@
     </row>
     <row r="116" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A116" s="42" t="s">
-        <v>300</v>
+        <v>288</v>
       </c>
       <c r="B116" s="51" t="s">
-        <v>408</v>
+        <v>403</v>
       </c>
       <c r="C116" s="37" t="s">
-        <v>486</v>
+        <v>474</v>
       </c>
       <c r="D116" s="41" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="E116" s="41" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F116" s="24" t="s">
-        <v>486</v>
+        <v>474</v>
       </c>
       <c r="G116" s="23" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="H116" s="23" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I116" s="23"/>
     </row>
     <row r="117" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A117" s="42" t="s">
-        <v>301</v>
+      <c r="A117" s="30" t="s">
+        <v>296</v>
       </c>
       <c r="B117" s="51" t="s">
-        <v>409</v>
+        <v>404</v>
       </c>
       <c r="C117" s="37" t="s">
-        <v>487</v>
+        <v>475</v>
       </c>
       <c r="D117" s="41" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="E117" s="41" t="s">
         <v>149</v>
       </c>
       <c r="F117" s="24" t="s">
-        <v>487</v>
+        <v>475</v>
       </c>
       <c r="G117" s="23" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="H117" s="23" t="s">
         <v>149</v>
@@ -8712,25 +8752,25 @@
     </row>
     <row r="118" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A118" s="42" t="s">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="B118" s="51" t="s">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="C118" s="37" t="s">
-        <v>488</v>
+        <v>476</v>
       </c>
       <c r="D118" s="41" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="E118" s="41" t="s">
         <v>149</v>
       </c>
       <c r="F118" s="24" t="s">
-        <v>488</v>
+        <v>476</v>
       </c>
       <c r="G118" s="23" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="H118" s="23" t="s">
         <v>149</v>
@@ -8739,25 +8779,25 @@
     </row>
     <row r="119" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A119" s="42" t="s">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="B119" s="51" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="C119" s="37" t="s">
-        <v>489</v>
+        <v>477</v>
       </c>
       <c r="D119" s="41" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="E119" s="41" t="s">
         <v>149</v>
       </c>
       <c r="F119" s="24" t="s">
-        <v>489</v>
+        <v>477</v>
       </c>
       <c r="G119" s="23" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="H119" s="23" t="s">
         <v>149</v>
@@ -8766,25 +8806,25 @@
     </row>
     <row r="120" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A120" s="42" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="B120" s="51" t="s">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="C120" s="37" t="s">
-        <v>490</v>
+        <v>478</v>
       </c>
       <c r="D120" s="41" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="E120" s="41" t="s">
         <v>149</v>
       </c>
       <c r="F120" s="24" t="s">
-        <v>490</v>
+        <v>478</v>
       </c>
       <c r="G120" s="23" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="H120" s="23" t="s">
         <v>149</v>
@@ -8793,25 +8833,25 @@
     </row>
     <row r="121" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A121" s="42" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="B121" s="51" t="s">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="C121" s="37" t="s">
-        <v>491</v>
+        <v>479</v>
       </c>
       <c r="D121" s="41" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="E121" s="41" t="s">
         <v>149</v>
       </c>
       <c r="F121" s="24" t="s">
-        <v>491</v>
+        <v>479</v>
       </c>
       <c r="G121" s="23" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="H121" s="23" t="s">
         <v>149</v>
@@ -8820,25 +8860,25 @@
     </row>
     <row r="122" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A122" s="42" t="s">
-        <v>303</v>
+        <v>290</v>
       </c>
       <c r="B122" s="51" t="s">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="C122" s="37" t="s">
-        <v>492</v>
+        <v>480</v>
       </c>
       <c r="D122" s="41" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="E122" s="41" t="s">
         <v>149</v>
       </c>
       <c r="F122" s="24" t="s">
-        <v>492</v>
+        <v>480</v>
       </c>
       <c r="G122" s="23" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="H122" s="23" t="s">
         <v>149</v>
@@ -8847,25 +8887,25 @@
     </row>
     <row r="123" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A123" s="42" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="B123" s="51" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="C123" s="37" t="s">
-        <v>493</v>
+        <v>481</v>
       </c>
       <c r="D123" s="41" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="E123" s="41" t="s">
         <v>149</v>
       </c>
       <c r="F123" s="24" t="s">
-        <v>493</v>
+        <v>481</v>
       </c>
       <c r="G123" s="23" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="H123" s="23" t="s">
         <v>149</v>
@@ -8874,175 +8914,227 @@
     </row>
     <row r="124" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A124" s="42" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="B124" s="51" t="s">
+        <v>411</v>
+      </c>
+      <c r="C124" s="37" t="s">
+        <v>482</v>
+      </c>
+      <c r="D124" s="41" t="s">
+        <v>201</v>
+      </c>
+      <c r="E124" s="41" t="s">
+        <v>149</v>
+      </c>
+      <c r="F124" s="24" t="s">
+        <v>482</v>
+      </c>
+      <c r="G124" s="23" t="s">
+        <v>194</v>
+      </c>
+      <c r="H124" s="23" t="s">
+        <v>149</v>
+      </c>
+      <c r="I124" s="23"/>
+    </row>
+    <row r="125" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A125" s="42" t="s">
+        <v>292</v>
+      </c>
+      <c r="B125" s="51" t="s">
+        <v>412</v>
+      </c>
+      <c r="C125" s="37" t="s">
+        <v>483</v>
+      </c>
+      <c r="D125" s="41" t="s">
+        <v>201</v>
+      </c>
+      <c r="E125" s="41" t="s">
+        <v>149</v>
+      </c>
+      <c r="F125" s="24" t="s">
+        <v>483</v>
+      </c>
+      <c r="G125" s="23" t="s">
+        <v>194</v>
+      </c>
+      <c r="H125" s="23" t="s">
+        <v>149</v>
+      </c>
+      <c r="I125" s="23"/>
+    </row>
+    <row r="126" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A126" s="42" t="s">
+        <v>293</v>
+      </c>
+      <c r="B126" s="51" t="s">
+        <v>413</v>
+      </c>
+      <c r="C126" s="37" t="s">
+        <v>484</v>
+      </c>
+      <c r="D126" s="41" t="s">
+        <v>201</v>
+      </c>
+      <c r="E126" s="41" t="s">
+        <v>149</v>
+      </c>
+      <c r="F126" s="24" t="s">
+        <v>484</v>
+      </c>
+      <c r="G126" s="23" t="s">
+        <v>194</v>
+      </c>
+      <c r="H126" s="23" t="s">
+        <v>149</v>
+      </c>
+      <c r="I126" s="23"/>
+    </row>
+    <row r="127" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A127" s="44" t="s">
+        <v>301</v>
+      </c>
+      <c r="B127" s="51" t="s">
+        <v>414</v>
+      </c>
+      <c r="C127" s="37" t="s">
+        <v>485</v>
+      </c>
+      <c r="D127" s="41" t="s">
+        <v>201</v>
+      </c>
+      <c r="E127" s="41" t="s">
+        <v>149</v>
+      </c>
+      <c r="F127" s="24" t="s">
+        <v>485</v>
+      </c>
+      <c r="G127" s="23" t="s">
+        <v>194</v>
+      </c>
+      <c r="H127" s="23" t="s">
+        <v>149</v>
+      </c>
+      <c r="I127" s="23"/>
+    </row>
+    <row r="128" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A128" s="39" t="s">
+        <v>302</v>
+      </c>
+      <c r="B128" s="51" t="s">
+        <v>415</v>
+      </c>
+      <c r="C128" s="37" t="s">
+        <v>486</v>
+      </c>
+      <c r="D128" s="41" t="s">
+        <v>201</v>
+      </c>
+      <c r="E128" s="41" t="s">
+        <v>149</v>
+      </c>
+      <c r="F128" s="24" t="s">
+        <v>486</v>
+      </c>
+      <c r="G128" s="23" t="s">
+        <v>194</v>
+      </c>
+      <c r="H128" s="23" t="s">
+        <v>149</v>
+      </c>
+      <c r="I128" s="23"/>
+    </row>
+    <row r="129" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A129" s="39" t="s">
+        <v>303</v>
+      </c>
+      <c r="B129" s="51" t="s">
         <v>416</v>
       </c>
-      <c r="C124" s="37" t="s">
-        <v>494</v>
-      </c>
-      <c r="D124" s="41" t="s">
-        <v>203</v>
-      </c>
-      <c r="E124" s="41" t="s">
-        <v>149</v>
-      </c>
-      <c r="F124" s="24" t="s">
-        <v>494</v>
-      </c>
-      <c r="G124" s="23" t="s">
-        <v>196</v>
-      </c>
-      <c r="H124" s="23" t="s">
-        <v>149</v>
-      </c>
-      <c r="I124" s="23"/>
-    </row>
-    <row r="125" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A125" s="44" t="s">
+      <c r="C129" s="37"/>
+      <c r="D129" s="41"/>
+      <c r="E129" s="41"/>
+      <c r="F129" s="24"/>
+      <c r="G129" s="23"/>
+      <c r="H129" s="23"/>
+      <c r="I129" s="23" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="130" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A130" s="44" t="s">
         <v>304</v>
       </c>
-      <c r="B125" s="51" t="s">
+      <c r="B130" s="51" t="s">
         <v>417</v>
       </c>
-      <c r="C125" s="37" t="s">
-        <v>495</v>
-      </c>
-      <c r="D125" s="41" t="s">
-        <v>203</v>
-      </c>
-      <c r="E125" s="41" t="s">
-        <v>149</v>
-      </c>
-      <c r="F125" s="23" t="s">
-        <v>495</v>
-      </c>
-      <c r="G125" s="23" t="s">
-        <v>196</v>
-      </c>
-      <c r="H125" s="23" t="s">
-        <v>149</v>
-      </c>
-      <c r="I125" s="23"/>
-    </row>
-    <row r="126" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A126" s="39" t="s">
-        <v>305</v>
-      </c>
-      <c r="B126" s="51" t="s">
-        <v>418</v>
-      </c>
-      <c r="C126" s="37" t="s">
-        <v>496</v>
-      </c>
-      <c r="D126" s="41" t="s">
-        <v>203</v>
-      </c>
-      <c r="E126" s="41" t="s">
-        <v>149</v>
-      </c>
-      <c r="F126" s="23" t="s">
-        <v>496</v>
-      </c>
-      <c r="G126" s="23" t="s">
-        <v>196</v>
-      </c>
-      <c r="H126" s="23" t="s">
-        <v>149</v>
-      </c>
-      <c r="I126" s="23"/>
-    </row>
-    <row r="127" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A127" s="39" t="s">
-        <v>306</v>
-      </c>
-      <c r="B127" s="51" t="s">
-        <v>419</v>
-      </c>
-      <c r="C127" s="37"/>
-      <c r="D127" s="41"/>
-      <c r="E127" s="41"/>
-      <c r="F127" s="23"/>
-      <c r="G127" s="23"/>
-      <c r="H127" s="23"/>
-      <c r="I127" s="23" t="s">
-        <v>530</v>
-      </c>
-    </row>
-    <row r="128" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A128" s="44" t="s">
-        <v>307</v>
-      </c>
-      <c r="B128" s="51" t="s">
-        <v>420</v>
-      </c>
-      <c r="C128" s="37" t="s">
-        <v>497</v>
-      </c>
-      <c r="D128" s="41" t="s">
-        <v>203</v>
-      </c>
-      <c r="E128" s="41" t="s">
-        <v>149</v>
-      </c>
-      <c r="F128" s="23" t="s">
-        <v>497</v>
-      </c>
-      <c r="G128" s="23" t="s">
-        <v>196</v>
-      </c>
-      <c r="H128" s="23" t="s">
-        <v>149</v>
-      </c>
-      <c r="I128" s="23"/>
-    </row>
-    <row r="129" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C129" s="16"/>
-    </row>
-    <row r="130" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C130" s="16"/>
-    </row>
-    <row r="131" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C130" s="37" t="s">
+        <v>487</v>
+      </c>
+      <c r="D130" s="41" t="s">
+        <v>201</v>
+      </c>
+      <c r="E130" s="41" t="s">
+        <v>149</v>
+      </c>
+      <c r="F130" s="24" t="s">
+        <v>487</v>
+      </c>
+      <c r="G130" s="23" t="s">
+        <v>194</v>
+      </c>
+      <c r="H130" s="23" t="s">
+        <v>149</v>
+      </c>
+      <c r="I130" s="23"/>
+    </row>
+    <row r="131" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C131" s="16"/>
-    </row>
-    <row r="132" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="F131" s="16"/>
+    </row>
+    <row r="132" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C132" s="16"/>
-    </row>
-    <row r="133" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="F132" s="16"/>
+    </row>
+    <row r="133" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C133" s="16"/>
-    </row>
-    <row r="134" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="F133" s="16"/>
+    </row>
+    <row r="134" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C134" s="16"/>
-    </row>
-    <row r="135" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="F134" s="16"/>
+    </row>
+    <row r="135" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C135" s="16"/>
     </row>
-    <row r="136" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C136" s="16"/>
     </row>
-    <row r="137" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C137" s="16"/>
     </row>
-    <row r="138" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C138" s="16"/>
     </row>
-    <row r="139" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C139" s="16"/>
     </row>
-    <row r="140" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C140" s="16"/>
     </row>
-    <row r="141" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C141" s="16"/>
     </row>
-    <row r="142" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C142" s="16"/>
     </row>
-    <row r="143" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C143" s="16"/>
     </row>
-    <row r="144" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C144" s="16"/>
     </row>
     <row r="145" spans="3:3" x14ac:dyDescent="0.25">
@@ -9468,34 +9560,41 @@
     <row r="285" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C285" s="16"/>
     </row>
+    <row r="286" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C286" s="16"/>
+    </row>
+    <row r="287" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C287" s="16"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I128" xr:uid="{B82CF358-6F31-4D7F-93EC-0C8D1049DBC2}"/>
+  <autoFilter ref="A1:I130" xr:uid="{B82CF358-6F31-4D7F-93EC-0C8D1049DBC2}"/>
   <mergeCells count="3">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="C2:E2"/>
     <mergeCell ref="F2:H2"/>
   </mergeCells>
+  <phoneticPr fontId="14" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="3">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" disablePrompts="1" count="3">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{A3A06F99-31BF-4A5B-9EAE-8CFAC715D117}">
           <x14:formula1>
             <xm:f>konta!$A$2:$A$19</xm:f>
           </x14:formula1>
-          <xm:sqref>D4:D215</xm:sqref>
+          <xm:sqref>D4:D217</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{6EAF70CE-009F-4A5D-8C05-5D472733BCFB}">
           <x14:formula1>
             <xm:f>konta!$B$2:$B$12</xm:f>
           </x14:formula1>
-          <xm:sqref>E4:E180</xm:sqref>
+          <xm:sqref>E4:E182</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{53D34262-83A1-4432-9E7C-4EBDCF8A37C7}">
           <x14:formula1>
             <xm:f>konta!$A$2:$A$11</xm:f>
           </x14:formula1>
-          <xm:sqref>G4:G252</xm:sqref>
+          <xm:sqref>G4:G254</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -9514,93 +9613,93 @@
   <sheetData>
     <row r="1" spans="1:5" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B1" s="76" t="s">
-        <v>670</v>
+        <v>656</v>
       </c>
       <c r="C1" s="77"/>
     </row>
     <row r="2" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="89" t="s">
-        <v>688</v>
+        <v>674</v>
       </c>
       <c r="B2" s="90" t="s">
-        <v>614</v>
+        <v>601</v>
       </c>
       <c r="C2" s="90" t="s">
-        <v>499</v>
+        <v>489</v>
       </c>
       <c r="D2" s="89" t="s">
-        <v>628</v>
+        <v>615</v>
       </c>
       <c r="E2" s="89" t="s">
-        <v>689</v>
+        <v>675</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="23" t="s">
-        <v>692</v>
+        <v>678</v>
       </c>
       <c r="B3" s="79" t="s">
         <v>6</v>
       </c>
       <c r="C3" s="84" t="s">
-        <v>690</v>
+        <v>676</v>
       </c>
       <c r="D3" s="23" t="s">
-        <v>632</v>
+        <v>619</v>
       </c>
       <c r="E3" s="23" t="s">
-        <v>725</v>
+        <v>711</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" s="23" t="s">
-        <v>693</v>
+        <v>679</v>
       </c>
       <c r="B4" s="78" t="s">
-        <v>671</v>
+        <v>657</v>
       </c>
       <c r="C4" s="85" t="s">
-        <v>730</v>
+        <v>716</v>
       </c>
       <c r="D4" s="23" t="s">
-        <v>632</v>
+        <v>619</v>
       </c>
       <c r="E4" s="23" t="s">
-        <v>725</v>
+        <v>711</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="23" t="s">
-        <v>694</v>
+        <v>680</v>
       </c>
       <c r="B5" s="80" t="s">
-        <v>672</v>
+        <v>658</v>
       </c>
       <c r="C5" s="86" t="s">
-        <v>691</v>
+        <v>677</v>
       </c>
       <c r="D5" s="23" t="s">
-        <v>632</v>
+        <v>619</v>
       </c>
       <c r="E5" s="23" t="s">
-        <v>725</v>
+        <v>711</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" s="23" t="s">
-        <v>695</v>
+        <v>681</v>
       </c>
       <c r="B6" s="81" t="s">
-        <v>673</v>
+        <v>659</v>
       </c>
       <c r="C6" s="87" t="s">
-        <v>732</v>
+        <v>718</v>
       </c>
       <c r="D6" s="23" t="s">
-        <v>632</v>
+        <v>619</v>
       </c>
       <c r="E6" s="23" t="s">
-        <v>726</v>
+        <v>712</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
@@ -9619,155 +9718,155 @@
     </row>
     <row r="9" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" s="23" t="s">
-        <v>704</v>
+        <v>690</v>
       </c>
       <c r="B9" s="80" t="s">
-        <v>674</v>
+        <v>660</v>
       </c>
       <c r="C9" s="86" t="s">
-        <v>696</v>
+        <v>682</v>
       </c>
       <c r="D9" s="23" t="s">
-        <v>632</v>
+        <v>619</v>
       </c>
       <c r="E9" s="23" t="s">
-        <v>725</v>
+        <v>711</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" s="23" t="s">
-        <v>705</v>
+        <v>691</v>
       </c>
       <c r="B10" s="78" t="s">
-        <v>675</v>
+        <v>661</v>
       </c>
       <c r="C10" s="88" t="s">
-        <v>697</v>
+        <v>683</v>
       </c>
       <c r="D10" s="23" t="s">
-        <v>632</v>
+        <v>619</v>
       </c>
       <c r="E10" s="23" t="s">
-        <v>725</v>
+        <v>711</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" s="23" t="s">
-        <v>706</v>
+        <v>692</v>
       </c>
       <c r="B11" s="80" t="s">
         <v>26</v>
       </c>
       <c r="C11" s="86" t="s">
-        <v>698</v>
+        <v>684</v>
       </c>
       <c r="D11" s="23" t="s">
-        <v>632</v>
+        <v>619</v>
       </c>
       <c r="E11" s="23" t="s">
-        <v>725</v>
+        <v>711</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12" s="23" t="s">
-        <v>707</v>
+        <v>693</v>
       </c>
       <c r="B12" s="78" t="s">
-        <v>676</v>
+        <v>662</v>
       </c>
       <c r="C12" s="88" t="s">
-        <v>699</v>
+        <v>685</v>
       </c>
       <c r="D12" s="23" t="s">
-        <v>632</v>
+        <v>619</v>
       </c>
       <c r="E12" s="23" t="s">
-        <v>725</v>
+        <v>711</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13" s="23" t="s">
-        <v>708</v>
+        <v>694</v>
       </c>
       <c r="B13" s="80" t="s">
-        <v>677</v>
+        <v>663</v>
       </c>
       <c r="C13" s="86" t="s">
-        <v>700</v>
+        <v>686</v>
       </c>
       <c r="D13" s="23" t="s">
-        <v>632</v>
+        <v>619</v>
       </c>
       <c r="E13" s="23" t="s">
-        <v>725</v>
+        <v>711</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14" s="23" t="s">
-        <v>709</v>
+        <v>695</v>
       </c>
       <c r="B14" s="78" t="s">
-        <v>678</v>
+        <v>664</v>
       </c>
       <c r="C14" s="88" t="s">
-        <v>701</v>
+        <v>687</v>
       </c>
       <c r="D14" s="23" t="s">
-        <v>632</v>
+        <v>619</v>
       </c>
       <c r="E14" s="23" t="s">
-        <v>725</v>
+        <v>711</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15" s="23" t="s">
-        <v>710</v>
+        <v>696</v>
       </c>
       <c r="B15" s="80" t="s">
-        <v>679</v>
+        <v>665</v>
       </c>
       <c r="C15" s="86" t="s">
-        <v>702</v>
+        <v>688</v>
       </c>
       <c r="D15" s="23" t="s">
-        <v>632</v>
+        <v>619</v>
       </c>
       <c r="E15" s="23" t="s">
-        <v>725</v>
+        <v>711</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" s="23" t="s">
+        <v>697</v>
+      </c>
+      <c r="B16" s="78" t="s">
+        <v>666</v>
+      </c>
+      <c r="C16" s="88" t="s">
+        <v>689</v>
+      </c>
+      <c r="D16" s="23" t="s">
+        <v>619</v>
+      </c>
+      <c r="E16" s="23" t="s">
         <v>711</v>
-      </c>
-      <c r="B16" s="78" t="s">
-        <v>680</v>
-      </c>
-      <c r="C16" s="88" t="s">
-        <v>703</v>
-      </c>
-      <c r="D16" s="23" t="s">
-        <v>632</v>
-      </c>
-      <c r="E16" s="23" t="s">
-        <v>725</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17" s="23" t="s">
-        <v>712</v>
+        <v>698</v>
       </c>
       <c r="B17" s="81" t="s">
-        <v>681</v>
+        <v>667</v>
       </c>
       <c r="C17" s="87" t="s">
+        <v>699</v>
+      </c>
+      <c r="D17" s="23" t="s">
+        <v>619</v>
+      </c>
+      <c r="E17" s="23" t="s">
         <v>713</v>
-      </c>
-      <c r="D17" s="23" t="s">
-        <v>632</v>
-      </c>
-      <c r="E17" s="23" t="s">
-        <v>727</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
@@ -9779,19 +9878,19 @@
     </row>
     <row r="19" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19" s="23" t="s">
-        <v>715</v>
+        <v>701</v>
       </c>
       <c r="B19" s="81" t="s">
-        <v>682</v>
+        <v>668</v>
       </c>
       <c r="C19" s="87" t="s">
-        <v>714</v>
+        <v>700</v>
       </c>
       <c r="D19" s="23" t="s">
-        <v>632</v>
+        <v>619</v>
       </c>
       <c r="E19" s="23" t="s">
-        <v>727</v>
+        <v>713</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
@@ -9803,47 +9902,47 @@
     </row>
     <row r="21" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21" s="23" t="s">
-        <v>716</v>
+        <v>702</v>
       </c>
       <c r="B21" s="80" t="s">
-        <v>683</v>
+        <v>669</v>
       </c>
       <c r="C21" s="86" t="s">
-        <v>595</v>
+        <v>582</v>
       </c>
       <c r="D21" s="23" t="s">
-        <v>632</v>
+        <v>619</v>
       </c>
       <c r="E21" s="23" t="s">
-        <v>725</v>
+        <v>711</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" s="23" t="s">
-        <v>717</v>
+        <v>703</v>
       </c>
       <c r="B22" s="78" t="s">
-        <v>684</v>
+        <v>670</v>
       </c>
       <c r="C22" s="88" t="s">
-        <v>596</v>
+        <v>583</v>
       </c>
       <c r="D22" s="23" t="s">
-        <v>632</v>
+        <v>619</v>
       </c>
       <c r="E22" s="23" t="s">
-        <v>725</v>
+        <v>711</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23" s="23" t="s">
-        <v>718</v>
+        <v>704</v>
       </c>
       <c r="B23" s="81" t="s">
-        <v>685</v>
+        <v>671</v>
       </c>
       <c r="C23" s="87" t="s">
-        <v>719</v>
+        <v>705</v>
       </c>
       <c r="D23" s="23"/>
       <c r="E23" s="23"/>
@@ -9864,53 +9963,53 @@
     </row>
     <row r="26" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26" s="23" t="s">
-        <v>720</v>
+        <v>706</v>
       </c>
       <c r="B26" s="78" t="s">
-        <v>724</v>
+        <v>710</v>
       </c>
       <c r="C26" s="88" t="s">
-        <v>733</v>
+        <v>719</v>
       </c>
       <c r="D26" s="23" t="s">
-        <v>632</v>
+        <v>619</v>
       </c>
       <c r="E26" s="23" t="s">
-        <v>728</v>
+        <v>714</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27" s="23" t="s">
-        <v>721</v>
+        <v>707</v>
       </c>
       <c r="B27" s="80" t="s">
-        <v>686</v>
+        <v>672</v>
       </c>
       <c r="C27" s="86" t="s">
-        <v>598</v>
+        <v>585</v>
       </c>
       <c r="D27" s="23" t="s">
-        <v>729</v>
+        <v>715</v>
       </c>
       <c r="E27" s="23" t="s">
-        <v>725</v>
+        <v>711</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A28" s="23" t="s">
-        <v>722</v>
+        <v>708</v>
       </c>
       <c r="B28" s="81" t="s">
-        <v>687</v>
+        <v>673</v>
       </c>
       <c r="C28" s="87" t="s">
-        <v>723</v>
+        <v>709</v>
       </c>
       <c r="D28" s="23" t="s">
-        <v>729</v>
+        <v>715</v>
       </c>
       <c r="E28" s="23" t="s">
-        <v>728</v>
+        <v>714</v>
       </c>
     </row>
   </sheetData>
@@ -9931,140 +10030,140 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="23" t="s">
-        <v>573</v>
+        <v>561</v>
       </c>
       <c r="B1" s="23" t="s">
-        <v>748</v>
+        <v>734</v>
       </c>
       <c r="C1" s="23" t="s">
-        <v>535</v>
+        <v>525</v>
       </c>
       <c r="D1" s="23" t="s">
-        <v>615</v>
+        <v>602</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="23" t="s">
-        <v>749</v>
+        <v>735</v>
       </c>
       <c r="B2" s="23" t="s">
-        <v>757</v>
+        <v>743</v>
       </c>
       <c r="C2" s="23" t="s">
-        <v>758</v>
+        <v>744</v>
       </c>
       <c r="D2" s="23" t="s">
-        <v>767</v>
+        <v>753</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="23" t="s">
-        <v>774</v>
+        <v>760</v>
       </c>
       <c r="B3" s="23" t="s">
-        <v>757</v>
+        <v>743</v>
       </c>
       <c r="C3" s="23" t="s">
-        <v>759</v>
+        <v>745</v>
       </c>
       <c r="D3" s="23" t="s">
-        <v>775</v>
+        <v>761</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="23" t="s">
-        <v>750</v>
+        <v>736</v>
       </c>
       <c r="B4" s="23" t="s">
-        <v>757</v>
+        <v>743</v>
       </c>
       <c r="C4" s="23" t="s">
-        <v>776</v>
+        <v>762</v>
       </c>
       <c r="D4" s="23" t="s">
-        <v>777</v>
+        <v>763</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="23" t="s">
-        <v>751</v>
+        <v>737</v>
       </c>
       <c r="B5" s="23" t="s">
-        <v>757</v>
+        <v>743</v>
       </c>
       <c r="C5" s="23" t="s">
-        <v>760</v>
+        <v>746</v>
       </c>
       <c r="D5" s="23" t="s">
-        <v>768</v>
+        <v>754</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="23" t="s">
-        <v>752</v>
+        <v>738</v>
       </c>
       <c r="B6" s="23" t="s">
-        <v>757</v>
+        <v>743</v>
       </c>
       <c r="C6" s="23" t="s">
-        <v>761</v>
+        <v>747</v>
       </c>
       <c r="D6" s="23" t="s">
-        <v>769</v>
+        <v>755</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="23" t="s">
-        <v>753</v>
+        <v>739</v>
       </c>
       <c r="B7" s="23" t="s">
-        <v>762</v>
+        <v>748</v>
       </c>
       <c r="C7" s="23" t="s">
-        <v>763</v>
+        <v>749</v>
       </c>
       <c r="D7" s="23" t="s">
-        <v>770</v>
+        <v>756</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="23" t="s">
-        <v>754</v>
+        <v>740</v>
       </c>
       <c r="B8" s="23" t="s">
-        <v>762</v>
-      </c>
-      <c r="C8" s="92">
+        <v>748</v>
+      </c>
+      <c r="C8" s="91">
         <v>218</v>
       </c>
       <c r="D8" s="23" t="s">
-        <v>771</v>
+        <v>757</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="23" t="s">
-        <v>755</v>
+        <v>741</v>
       </c>
       <c r="B9" s="23" t="s">
-        <v>764</v>
+        <v>750</v>
       </c>
       <c r="C9" s="23" t="s">
-        <v>765</v>
+        <v>751</v>
       </c>
       <c r="D9" s="23" t="s">
-        <v>773</v>
+        <v>759</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="23" t="s">
-        <v>756</v>
+        <v>742</v>
       </c>
       <c r="B10" s="23" t="s">
-        <v>766</v>
+        <v>752</v>
       </c>
       <c r="C10" s="23"/>
       <c r="D10" s="23" t="s">
-        <v>772</v>
+        <v>758</v>
       </c>
     </row>
   </sheetData>
@@ -10074,7 +10173,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{880F8430-BA4F-490D-BC3E-D695AFB7258C}">
-  <dimension ref="A1:E71"/>
+  <dimension ref="A1:E73"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="77" bestFit="1" customWidth="1"/>
@@ -10084,35 +10183,35 @@
   <sheetData>
     <row r="1" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B1" s="61" t="s">
-        <v>537</v>
+        <v>527</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B2" s="61" t="s">
-        <v>538</v>
+        <v>528</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="68" t="s">
-        <v>535</v>
+        <v>525</v>
       </c>
       <c r="B3" s="69" t="s">
-        <v>573</v>
+        <v>561</v>
       </c>
       <c r="C3" s="68" t="s">
-        <v>583</v>
+        <v>570</v>
       </c>
       <c r="D3" s="68" t="s">
         <v>144</v>
       </c>
       <c r="E3" s="68" t="s">
-        <v>536</v>
+        <v>526</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" s="23"/>
       <c r="B4" s="58" t="s">
-        <v>539</v>
+        <v>529</v>
       </c>
       <c r="C4" s="23"/>
       <c r="D4" s="23"/>
@@ -10120,13 +10219,13 @@
     </row>
     <row r="5" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="63" t="s">
-        <v>559</v>
+        <v>548</v>
       </c>
       <c r="B5" s="59" t="s">
-        <v>540</v>
+        <v>530</v>
       </c>
       <c r="C5" s="24" t="s">
-        <v>584</v>
+        <v>571</v>
       </c>
       <c r="D5" s="24" t="s">
         <v>149</v>
@@ -10135,13 +10234,13 @@
     </row>
     <row r="6" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" s="63" t="s">
-        <v>559</v>
+        <v>548</v>
       </c>
       <c r="B6" s="59" t="s">
-        <v>540</v>
+        <v>530</v>
       </c>
       <c r="C6" s="24" t="s">
-        <v>585</v>
+        <v>572</v>
       </c>
       <c r="D6" s="24" t="s">
         <v>150</v>
@@ -10150,13 +10249,13 @@
     </row>
     <row r="7" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" s="63" t="s">
-        <v>559</v>
+        <v>548</v>
       </c>
       <c r="B7" s="59" t="s">
-        <v>540</v>
+        <v>530</v>
       </c>
       <c r="C7" s="24" t="s">
-        <v>638</v>
+        <v>624</v>
       </c>
       <c r="D7" s="24" t="s">
         <v>150</v>
@@ -10165,13 +10264,13 @@
     </row>
     <row r="8" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="62" t="s">
-        <v>560</v>
+        <v>549</v>
       </c>
       <c r="B8" s="59" t="s">
-        <v>541</v>
+        <v>531</v>
       </c>
       <c r="C8" s="24" t="s">
-        <v>586</v>
+        <v>573</v>
       </c>
       <c r="D8" s="24" t="s">
         <v>150</v>
@@ -10180,13 +10279,13 @@
     </row>
     <row r="9" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" s="62" t="s">
-        <v>560</v>
+        <v>549</v>
       </c>
       <c r="B9" s="59" t="s">
-        <v>541</v>
+        <v>531</v>
       </c>
       <c r="C9" s="24" t="s">
-        <v>587</v>
+        <v>574</v>
       </c>
       <c r="D9" s="24" t="s">
         <v>149</v>
@@ -10195,13 +10294,13 @@
     </row>
     <row r="10" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" s="62" t="s">
-        <v>560</v>
+        <v>549</v>
       </c>
       <c r="B10" s="59" t="s">
-        <v>541</v>
+        <v>531</v>
       </c>
       <c r="C10" s="24" t="s">
-        <v>588</v>
+        <v>575</v>
       </c>
       <c r="D10" s="24" t="s">
         <v>150</v>
@@ -10210,13 +10309,13 @@
     </row>
     <row r="11" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" s="62" t="s">
-        <v>560</v>
+        <v>549</v>
       </c>
       <c r="B11" s="59" t="s">
-        <v>541</v>
+        <v>531</v>
       </c>
       <c r="C11" s="24" t="s">
-        <v>589</v>
+        <v>576</v>
       </c>
       <c r="D11" s="24" t="s">
         <v>149</v>
@@ -10225,13 +10324,13 @@
     </row>
     <row r="12" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12" s="62" t="s">
-        <v>560</v>
+        <v>549</v>
       </c>
       <c r="B12" s="59" t="s">
-        <v>541</v>
+        <v>531</v>
       </c>
       <c r="C12" s="24" t="s">
-        <v>590</v>
+        <v>577</v>
       </c>
       <c r="D12" s="24" t="s">
         <v>149</v>
@@ -10240,13 +10339,13 @@
     </row>
     <row r="13" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13" s="62" t="s">
-        <v>560</v>
+        <v>549</v>
       </c>
       <c r="B13" s="59" t="s">
-        <v>541</v>
+        <v>531</v>
       </c>
       <c r="C13" s="24" t="s">
-        <v>591</v>
+        <v>777</v>
       </c>
       <c r="D13" s="24" t="s">
         <v>150</v>
@@ -10254,29 +10353,29 @@
       <c r="E13" s="24"/>
     </row>
     <row r="14" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A14" s="64" t="s">
-        <v>561</v>
+      <c r="A14" s="62" t="s">
+        <v>549</v>
       </c>
       <c r="B14" s="59" t="s">
-        <v>542</v>
+        <v>531</v>
       </c>
       <c r="C14" s="24" t="s">
-        <v>592</v>
+        <v>578</v>
       </c>
       <c r="D14" s="24" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E14" s="24"/>
     </row>
     <row r="15" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15" s="64" t="s">
-        <v>561</v>
+        <v>550</v>
       </c>
       <c r="B15" s="59" t="s">
-        <v>542</v>
+        <v>532</v>
       </c>
       <c r="C15" s="24" t="s">
-        <v>593</v>
+        <v>579</v>
       </c>
       <c r="D15" s="24" t="s">
         <v>149</v>
@@ -10284,40 +10383,44 @@
       <c r="E15" s="24"/>
     </row>
     <row r="16" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A16" s="65" t="s">
-        <v>562</v>
+      <c r="A16" s="64" t="s">
+        <v>550</v>
       </c>
       <c r="B16" s="59" t="s">
-        <v>543</v>
-      </c>
-      <c r="C16" s="24"/>
-      <c r="D16" s="24"/>
+        <v>532</v>
+      </c>
+      <c r="C16" s="24" t="s">
+        <v>580</v>
+      </c>
+      <c r="D16" s="24" t="s">
+        <v>149</v>
+      </c>
       <c r="E16" s="24"/>
     </row>
     <row r="17" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A17" s="66" t="s">
-        <v>563</v>
+      <c r="A17" s="65" t="s">
+        <v>551</v>
       </c>
       <c r="B17" s="59" t="s">
-        <v>544</v>
+        <v>533</v>
       </c>
       <c r="C17" s="24" t="s">
-        <v>594</v>
+        <v>767</v>
       </c>
       <c r="D17" s="24" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E17" s="24"/>
     </row>
     <row r="18" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A18" s="67" t="s">
-        <v>564</v>
+      <c r="A18" s="66" t="s">
+        <v>551</v>
       </c>
       <c r="B18" s="59" t="s">
-        <v>545</v>
+        <v>534</v>
       </c>
       <c r="C18" s="24" t="s">
-        <v>595</v>
+        <v>581</v>
       </c>
       <c r="D18" s="24" t="s">
         <v>150</v>
@@ -10326,110 +10429,110 @@
     </row>
     <row r="19" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19" s="67" t="s">
-        <v>564</v>
+        <v>552</v>
       </c>
       <c r="B19" s="59" t="s">
-        <v>545</v>
+        <v>535</v>
       </c>
       <c r="C19" s="24" t="s">
-        <v>596</v>
+        <v>582</v>
       </c>
       <c r="D19" s="24" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E19" s="24"/>
     </row>
     <row r="20" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20" s="67" t="s">
-        <v>564</v>
+        <v>552</v>
       </c>
       <c r="B20" s="59" t="s">
-        <v>545</v>
+        <v>535</v>
       </c>
       <c r="C20" s="24" t="s">
-        <v>597</v>
+        <v>583</v>
       </c>
       <c r="D20" s="24" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E20" s="24"/>
     </row>
     <row r="21" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A21" s="66" t="s">
-        <v>565</v>
+      <c r="A21" s="67" t="s">
+        <v>552</v>
       </c>
       <c r="B21" s="59" t="s">
-        <v>546</v>
+        <v>535</v>
       </c>
       <c r="C21" s="24" t="s">
-        <v>598</v>
+        <v>584</v>
       </c>
       <c r="D21" s="24" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E21" s="24"/>
     </row>
     <row r="22" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" s="66" t="s">
-        <v>565</v>
+        <v>553</v>
       </c>
       <c r="B22" s="59" t="s">
-        <v>546</v>
+        <v>536</v>
       </c>
       <c r="C22" s="24" t="s">
-        <v>599</v>
+        <v>585</v>
       </c>
       <c r="D22" s="24" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E22" s="24"/>
     </row>
     <row r="23" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A23" s="23" t="s">
-        <v>610</v>
-      </c>
-      <c r="B23" s="58" t="s">
-        <v>547</v>
-      </c>
-      <c r="C23" s="24"/>
-      <c r="D23" s="24"/>
-      <c r="E23" s="24" t="s">
-        <v>607</v>
-      </c>
+      <c r="A23" s="66" t="s">
+        <v>553</v>
+      </c>
+      <c r="B23" s="59" t="s">
+        <v>536</v>
+      </c>
+      <c r="C23" s="24" t="s">
+        <v>586</v>
+      </c>
+      <c r="D23" s="24" t="s">
+        <v>149</v>
+      </c>
+      <c r="E23" s="24"/>
     </row>
     <row r="24" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A24" s="23"/>
+      <c r="A24" s="23" t="s">
+        <v>597</v>
+      </c>
       <c r="B24" s="58" t="s">
-        <v>548</v>
+        <v>537</v>
       </c>
       <c r="C24" s="24"/>
       <c r="D24" s="24"/>
-      <c r="E24" s="24"/>
+      <c r="E24" s="24" t="s">
+        <v>594</v>
+      </c>
     </row>
     <row r="25" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A25" s="23" t="s">
-        <v>566</v>
-      </c>
-      <c r="B25" s="59" t="s">
-        <v>549</v>
-      </c>
-      <c r="C25" s="24" t="s">
-        <v>600</v>
-      </c>
-      <c r="D25" s="24" t="s">
-        <v>150</v>
-      </c>
+      <c r="A25" s="23"/>
+      <c r="B25" s="58" t="s">
+        <v>538</v>
+      </c>
+      <c r="C25" s="24"/>
+      <c r="D25" s="24"/>
       <c r="E25" s="24"/>
     </row>
     <row r="26" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26" s="23" t="s">
-        <v>567</v>
+        <v>554</v>
       </c>
       <c r="B26" s="59" t="s">
-        <v>550</v>
+        <v>539</v>
       </c>
       <c r="C26" s="24" t="s">
-        <v>601</v>
+        <v>587</v>
       </c>
       <c r="D26" s="24" t="s">
         <v>150</v>
@@ -10438,13 +10541,13 @@
     </row>
     <row r="27" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27" s="23" t="s">
-        <v>567</v>
+        <v>555</v>
       </c>
       <c r="B27" s="59" t="s">
-        <v>550</v>
+        <v>540</v>
       </c>
       <c r="C27" s="24" t="s">
-        <v>602</v>
+        <v>588</v>
       </c>
       <c r="D27" s="24" t="s">
         <v>150</v>
@@ -10453,13 +10556,13 @@
     </row>
     <row r="28" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A28" s="23" t="s">
-        <v>567</v>
+        <v>555</v>
       </c>
       <c r="B28" s="59" t="s">
-        <v>550</v>
+        <v>540</v>
       </c>
       <c r="C28" s="24" t="s">
-        <v>603</v>
+        <v>589</v>
       </c>
       <c r="D28" s="24" t="s">
         <v>150</v>
@@ -10468,13 +10571,13 @@
     </row>
     <row r="29" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29" s="23" t="s">
-        <v>567</v>
+        <v>555</v>
       </c>
       <c r="B29" s="59" t="s">
-        <v>550</v>
+        <v>540</v>
       </c>
       <c r="C29" s="24" t="s">
-        <v>604</v>
+        <v>590</v>
       </c>
       <c r="D29" s="24" t="s">
         <v>150</v>
@@ -10483,13 +10586,13 @@
     </row>
     <row r="30" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30" s="23" t="s">
-        <v>567</v>
+        <v>555</v>
       </c>
       <c r="B30" s="59" t="s">
-        <v>550</v>
+        <v>540</v>
       </c>
       <c r="C30" s="24" t="s">
-        <v>605</v>
+        <v>591</v>
       </c>
       <c r="D30" s="24" t="s">
         <v>150</v>
@@ -10498,13 +10601,13 @@
     </row>
     <row r="31" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A31" s="23" t="s">
-        <v>567</v>
+        <v>555</v>
       </c>
       <c r="B31" s="59" t="s">
-        <v>550</v>
+        <v>540</v>
       </c>
       <c r="C31" s="24" t="s">
-        <v>606</v>
+        <v>592</v>
       </c>
       <c r="D31" s="24" t="s">
         <v>150</v>
@@ -10513,28 +10616,28 @@
     </row>
     <row r="32" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32" s="23" t="s">
-        <v>567</v>
+        <v>555</v>
       </c>
       <c r="B32" s="59" t="s">
-        <v>550</v>
+        <v>540</v>
       </c>
       <c r="C32" s="24" t="s">
-        <v>613</v>
+        <v>593</v>
       </c>
       <c r="D32" s="24" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E32" s="24"/>
     </row>
     <row r="33" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33" s="23" t="s">
-        <v>567</v>
+        <v>555</v>
       </c>
       <c r="B33" s="59" t="s">
-        <v>550</v>
+        <v>540</v>
       </c>
       <c r="C33" s="24" t="s">
-        <v>637</v>
+        <v>600</v>
       </c>
       <c r="D33" s="24" t="s">
         <v>150</v>
@@ -10543,140 +10646,160 @@
     </row>
     <row r="34" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A34" s="23" t="s">
-        <v>581</v>
-      </c>
-      <c r="B34" s="58" t="s">
-        <v>551</v>
-      </c>
-      <c r="C34" s="24"/>
-      <c r="D34" s="24"/>
-      <c r="E34" s="24" t="s">
-        <v>574</v>
-      </c>
+        <v>555</v>
+      </c>
+      <c r="B34" s="59" t="s">
+        <v>540</v>
+      </c>
+      <c r="C34" s="24" t="s">
+        <v>776</v>
+      </c>
+      <c r="D34" s="24" t="s">
+        <v>150</v>
+      </c>
+      <c r="E34" s="24"/>
     </row>
     <row r="35" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A35" s="23" t="s">
-        <v>582</v>
-      </c>
-      <c r="B35" s="58" t="s">
-        <v>552</v>
-      </c>
-      <c r="C35" s="24"/>
-      <c r="D35" s="24"/>
+        <v>555</v>
+      </c>
+      <c r="B35" s="59" t="s">
+        <v>540</v>
+      </c>
+      <c r="C35" s="24" t="s">
+        <v>623</v>
+      </c>
+      <c r="D35" s="24" t="s">
+        <v>150</v>
+      </c>
       <c r="E35" s="24"/>
     </row>
     <row r="36" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A36" s="23" t="s">
         <v>568</v>
       </c>
-      <c r="B36" s="59" t="s">
-        <v>553</v>
-      </c>
-      <c r="C36" s="24" t="s">
-        <v>608</v>
-      </c>
-      <c r="D36" s="24" t="s">
-        <v>149</v>
-      </c>
+      <c r="B36" s="58" t="s">
+        <v>541</v>
+      </c>
+      <c r="C36" s="24"/>
+      <c r="D36" s="24"/>
       <c r="E36" s="24" t="s">
-        <v>412</v>
+        <v>562</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A37" s="23" t="s">
         <v>569</v>
       </c>
-      <c r="B37" s="59" t="s">
-        <v>554</v>
-      </c>
-      <c r="C37" s="24" t="s">
-        <v>609</v>
-      </c>
-      <c r="D37" s="24" t="s">
-        <v>149</v>
-      </c>
-      <c r="E37" s="24" t="s">
-        <v>374</v>
-      </c>
+      <c r="B37" s="58" t="s">
+        <v>542</v>
+      </c>
+      <c r="C37" s="24"/>
+      <c r="D37" s="24"/>
+      <c r="E37" s="24"/>
     </row>
     <row r="38" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A38" s="23" t="s">
-        <v>580</v>
-      </c>
-      <c r="B38" s="60" t="s">
-        <v>555</v>
-      </c>
-      <c r="C38" s="24"/>
-      <c r="D38" s="24"/>
+        <v>556</v>
+      </c>
+      <c r="B38" s="59" t="s">
+        <v>543</v>
+      </c>
+      <c r="C38" s="24" t="s">
+        <v>595</v>
+      </c>
+      <c r="D38" s="24" t="s">
+        <v>149</v>
+      </c>
       <c r="E38" s="24" t="s">
-        <v>575</v>
+        <v>409</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A39" s="23" t="s">
-        <v>570</v>
-      </c>
-      <c r="B39" s="60" t="s">
-        <v>556</v>
-      </c>
-      <c r="C39" s="24"/>
-      <c r="D39" s="24"/>
+        <v>557</v>
+      </c>
+      <c r="B39" s="59" t="s">
+        <v>544</v>
+      </c>
+      <c r="C39" s="24" t="s">
+        <v>596</v>
+      </c>
+      <c r="D39" s="24" t="s">
+        <v>149</v>
+      </c>
       <c r="E39" s="24" t="s">
-        <v>576</v>
+        <v>371</v>
       </c>
     </row>
     <row r="40" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A40" s="23" t="s">
-        <v>571</v>
-      </c>
-      <c r="B40" s="59" t="s">
-        <v>557</v>
-      </c>
-      <c r="C40" s="24" t="s">
-        <v>611</v>
-      </c>
-      <c r="D40" s="24" t="s">
-        <v>149</v>
-      </c>
-      <c r="E40" s="24"/>
+        <v>567</v>
+      </c>
+      <c r="B40" s="60" t="s">
+        <v>545</v>
+      </c>
+      <c r="C40" s="24"/>
+      <c r="D40" s="24"/>
+      <c r="E40" s="24" t="s">
+        <v>563</v>
+      </c>
     </row>
     <row r="41" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A41" s="23" t="s">
-        <v>572</v>
-      </c>
-      <c r="B41" s="59" t="s">
         <v>558</v>
       </c>
-      <c r="C41" s="24" t="s">
-        <v>612</v>
-      </c>
-      <c r="D41" s="24" t="s">
-        <v>149</v>
-      </c>
-      <c r="E41" s="24"/>
+      <c r="B41" s="60" t="s">
+        <v>772</v>
+      </c>
+      <c r="C41" s="24"/>
+      <c r="D41" s="24"/>
+      <c r="E41" s="24" t="s">
+        <v>564</v>
+      </c>
     </row>
     <row r="42" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A42" s="23" t="s">
-        <v>578</v>
+        <v>559</v>
       </c>
       <c r="B42" s="59" t="s">
-        <v>577</v>
-      </c>
-      <c r="C42" s="24"/>
-      <c r="D42" s="24"/>
-      <c r="E42" s="24" t="s">
-        <v>579</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C43" s="16"/>
-      <c r="D43" s="16"/>
-      <c r="E43" s="16"/>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C44" s="16"/>
-      <c r="D44" s="16"/>
-      <c r="E44" s="16"/>
+        <v>546</v>
+      </c>
+      <c r="C42" s="24" t="s">
+        <v>598</v>
+      </c>
+      <c r="D42" s="24" t="s">
+        <v>149</v>
+      </c>
+      <c r="E42" s="24"/>
+    </row>
+    <row r="43" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A43" s="23" t="s">
+        <v>560</v>
+      </c>
+      <c r="B43" s="59" t="s">
+        <v>547</v>
+      </c>
+      <c r="C43" s="24" t="s">
+        <v>599</v>
+      </c>
+      <c r="D43" s="24" t="s">
+        <v>149</v>
+      </c>
+      <c r="E43" s="24"/>
+    </row>
+    <row r="44" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="23" t="s">
+        <v>565</v>
+      </c>
+      <c r="B44" s="95" t="s">
+        <v>773</v>
+      </c>
+      <c r="C44" s="24"/>
+      <c r="D44" s="24"/>
+      <c r="E44" s="24" t="s">
+        <v>566</v>
+      </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C45" s="16"/>
@@ -10689,10 +10812,12 @@
       <c r="E46" s="16"/>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C47" s="16"/>
       <c r="D47" s="16"/>
       <c r="E47" s="16"/>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C48" s="16"/>
       <c r="D48" s="16"/>
       <c r="E48" s="16"/>
     </row>
@@ -10781,10 +10906,18 @@
       <c r="E69" s="16"/>
     </row>
     <row r="70" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D70" s="16"/>
       <c r="E70" s="16"/>
     </row>
     <row r="71" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D71" s="16"/>
       <c r="E71" s="16"/>
+    </row>
+    <row r="72" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="E72" s="16"/>
+    </row>
+    <row r="73" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="E73" s="16"/>
     </row>
   </sheetData>
   <phoneticPr fontId="14" type="noConversion"/>
@@ -10796,7 +10929,7 @@
           <x14:formula1>
             <xm:f>konta!$B$2:$B$3</xm:f>
           </x14:formula1>
-          <xm:sqref>D5:D52</xm:sqref>
+          <xm:sqref>D5:D54</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -10820,51 +10953,51 @@
   <sheetData>
     <row r="1" spans="1:9" s="18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>535</v>
+        <v>525</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>614</v>
+        <v>601</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>499</v>
+        <v>489</v>
       </c>
       <c r="D1" s="2" t="s">
+        <v>602</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>615</v>
       </c>
-      <c r="E1" s="2" t="s">
-        <v>628</v>
-      </c>
       <c r="F1" s="2" t="s">
-        <v>658</v>
+        <v>644</v>
       </c>
       <c r="G1" s="18" t="s">
-        <v>664</v>
+        <v>650</v>
       </c>
       <c r="H1" s="18" t="s">
-        <v>668</v>
+        <v>654</v>
       </c>
       <c r="I1" s="18" t="s">
-        <v>665</v>
+        <v>651</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A2" s="33" t="s">
-        <v>616</v>
+        <v>603</v>
       </c>
       <c r="B2" s="73" t="s">
+        <v>607</v>
+      </c>
+      <c r="C2" s="33" t="s">
+        <v>613</v>
+      </c>
+      <c r="D2" s="70" t="s">
+        <v>610</v>
+      </c>
+      <c r="E2" s="33" t="s">
         <v>620</v>
       </c>
-      <c r="C2" s="33" t="s">
-        <v>626</v>
-      </c>
-      <c r="D2" s="70" t="s">
-        <v>623</v>
-      </c>
-      <c r="E2" s="33" t="s">
-        <v>633</v>
-      </c>
       <c r="F2" s="33" t="s">
-        <v>663</v>
+        <v>649</v>
       </c>
       <c r="G2">
         <v>1.75</v>
@@ -10873,27 +11006,27 @@
         <v>1.5</v>
       </c>
       <c r="I2" s="75" t="s">
-        <v>666</v>
+        <v>652</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="135" x14ac:dyDescent="0.25">
       <c r="A3" s="33" t="s">
-        <v>617</v>
+        <v>604</v>
       </c>
       <c r="B3" s="73" t="s">
-        <v>621</v>
+        <v>608</v>
       </c>
       <c r="C3" s="33" t="s">
-        <v>627</v>
+        <v>614</v>
       </c>
       <c r="D3" s="71" t="s">
-        <v>622</v>
+        <v>609</v>
       </c>
       <c r="E3" s="33" t="s">
-        <v>633</v>
+        <v>620</v>
       </c>
       <c r="F3" s="33" t="s">
-        <v>663</v>
+        <v>649</v>
       </c>
       <c r="G3">
         <v>1</v>
@@ -10902,220 +11035,220 @@
         <v>1</v>
       </c>
       <c r="I3" s="75" t="s">
-        <v>667</v>
+        <v>653</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="40.5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>618</v>
+        <v>605</v>
       </c>
       <c r="B4" s="74" t="s">
-        <v>624</v>
+        <v>611</v>
       </c>
       <c r="C4" t="s">
-        <v>634</v>
+        <v>621</v>
       </c>
       <c r="D4" s="72" t="s">
-        <v>625</v>
+        <v>612</v>
       </c>
       <c r="E4" t="s">
-        <v>632</v>
+        <v>619</v>
       </c>
       <c r="F4" t="s">
-        <v>663</v>
+        <v>649</v>
       </c>
       <c r="I4" s="75"/>
     </row>
     <row r="5" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>619</v>
+        <v>606</v>
       </c>
       <c r="B5" s="74" t="s">
-        <v>629</v>
+        <v>616</v>
       </c>
       <c r="C5" t="s">
-        <v>630</v>
+        <v>617</v>
       </c>
       <c r="D5" s="70" t="s">
-        <v>631</v>
+        <v>618</v>
       </c>
       <c r="E5" t="s">
-        <v>633</v>
+        <v>620</v>
       </c>
       <c r="F5" t="s">
-        <v>663</v>
+        <v>649</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="40.5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>643</v>
+        <v>629</v>
       </c>
       <c r="B6" s="74" t="s">
-        <v>639</v>
+        <v>625</v>
       </c>
       <c r="C6" t="s">
-        <v>640</v>
-      </c>
-      <c r="D6" s="93" t="s">
-        <v>641</v>
+        <v>626</v>
+      </c>
+      <c r="D6" s="92" t="s">
+        <v>627</v>
       </c>
       <c r="E6" t="s">
-        <v>642</v>
+        <v>628</v>
       </c>
       <c r="F6" t="s">
-        <v>661</v>
+        <v>647</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="81" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>633</v>
+      </c>
+      <c r="B7" t="s">
+        <v>630</v>
+      </c>
+      <c r="C7" t="s">
+        <v>631</v>
+      </c>
+      <c r="D7" s="72" t="s">
+        <v>632</v>
+      </c>
+      <c r="E7" t="s">
+        <v>628</v>
+      </c>
+      <c r="F7" t="s">
         <v>647</v>
-      </c>
-      <c r="B7" t="s">
-        <v>644</v>
-      </c>
-      <c r="C7" t="s">
-        <v>645</v>
-      </c>
-      <c r="D7" s="72" t="s">
-        <v>646</v>
-      </c>
-      <c r="E7" t="s">
-        <v>642</v>
-      </c>
-      <c r="F7" t="s">
-        <v>661</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="121.5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>648</v>
+        <v>634</v>
       </c>
       <c r="B8" s="74" t="s">
-        <v>649</v>
+        <v>635</v>
       </c>
       <c r="C8" t="s">
-        <v>654</v>
+        <v>640</v>
       </c>
       <c r="D8" s="72" t="s">
-        <v>650</v>
+        <v>636</v>
       </c>
       <c r="E8" t="s">
-        <v>633</v>
+        <v>620</v>
       </c>
       <c r="F8" s="74" t="s">
-        <v>661</v>
+        <v>647</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="54" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>651</v>
+        <v>637</v>
       </c>
       <c r="B9" s="74" t="s">
-        <v>652</v>
+        <v>638</v>
       </c>
       <c r="C9" t="s">
-        <v>655</v>
+        <v>641</v>
       </c>
       <c r="D9" s="72" t="s">
-        <v>653</v>
+        <v>639</v>
       </c>
       <c r="E9" t="s">
-        <v>633</v>
+        <v>620</v>
       </c>
       <c r="F9" t="s">
-        <v>661</v>
+        <v>647</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>659</v>
+        <v>645</v>
       </c>
       <c r="B10" t="s">
-        <v>746</v>
+        <v>732</v>
       </c>
       <c r="C10" t="s">
-        <v>660</v>
-      </c>
-      <c r="D10" s="94"/>
+        <v>646</v>
+      </c>
+      <c r="D10" s="93"/>
       <c r="E10" t="s">
-        <v>642</v>
+        <v>628</v>
       </c>
       <c r="F10" t="s">
-        <v>662</v>
+        <v>648</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>734</v>
+        <v>720</v>
       </c>
       <c r="B11" t="s">
-        <v>747</v>
+        <v>733</v>
       </c>
       <c r="C11" t="s">
-        <v>745</v>
-      </c>
-      <c r="D11" s="94"/>
+        <v>731</v>
+      </c>
+      <c r="D11" s="93"/>
       <c r="E11" t="s">
-        <v>642</v>
+        <v>628</v>
       </c>
       <c r="F11" t="s">
-        <v>662</v>
+        <v>648</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>735</v>
+        <v>721</v>
       </c>
       <c r="B12" t="s">
-        <v>736</v>
+        <v>722</v>
       </c>
       <c r="C12" t="s">
-        <v>737</v>
+        <v>723</v>
       </c>
       <c r="D12" s="70" t="s">
-        <v>738</v>
+        <v>724</v>
       </c>
       <c r="E12" t="s">
-        <v>642</v>
+        <v>628</v>
       </c>
       <c r="F12" t="s">
-        <v>739</v>
+        <v>725</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>740</v>
+        <v>726</v>
       </c>
       <c r="B13" t="s">
-        <v>741</v>
+        <v>727</v>
       </c>
       <c r="C13" t="s">
-        <v>742</v>
-      </c>
-      <c r="D13" s="94"/>
+        <v>728</v>
+      </c>
+      <c r="D13" s="93"/>
       <c r="E13" t="s">
-        <v>632</v>
+        <v>619</v>
       </c>
       <c r="F13" t="s">
-        <v>739</v>
+        <v>725</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>743</v>
+        <v>729</v>
       </c>
       <c r="B14" t="s">
-        <v>744</v>
+        <v>730</v>
       </c>
       <c r="C14" t="s">
-        <v>778</v>
-      </c>
-      <c r="D14" s="94"/>
+        <v>764</v>
+      </c>
+      <c r="D14" s="93"/>
       <c r="E14" t="s">
-        <v>642</v>
+        <v>628</v>
       </c>
       <c r="F14" t="s">
-        <v>662</v>
+        <v>648</v>
       </c>
     </row>
   </sheetData>
@@ -11142,7 +11275,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="34" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="B2" s="18" t="s">
         <v>149</v>
@@ -11150,7 +11283,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="34" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B3" s="19" t="s">
         <v>150</v>
@@ -11158,40 +11291,40 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="34" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B4" s="17"/>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="34" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B5" s="17"/>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="34" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B6" s="17"/>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="34" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="34" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="35" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="34" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">

--- a/pravila bilansi.xlsx
+++ b/pravila bilansi.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pc1\OneDrive\Desktop\goce proekt\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{275E9ACC-A850-4637-A815-BF382BD5B252}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD337BBA-A173-4511-A591-E9B5A270BF45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{093C95D7-6491-4473-A653-F40FC2BC4264}"/>
   </bookViews>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1616" uniqueCount="780">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1610" uniqueCount="780">
   <si>
     <r>
       <t xml:space="preserve">Биланс на успехот     </t>
@@ -3065,6 +3065,9 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment shrinkToFit="1"/>
     </xf>
@@ -3082,9 +3085,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3815,12 +3815,12 @@
       <c r="B1" s="2"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B2" s="96" t="s">
+      <c r="B2" s="97" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B3" s="97"/>
+      <c r="B3" s="98"/>
     </row>
     <row r="4" spans="1:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
@@ -5861,7 +5861,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="98" t="s">
+      <c r="A1" s="99" t="s">
         <v>305</v>
       </c>
       <c r="B1" s="38"/>
@@ -5870,18 +5870,18 @@
       <c r="E1" s="38"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="99"/>
+      <c r="A2" s="100"/>
       <c r="B2" s="38"/>
-      <c r="C2" s="100" t="s">
+      <c r="C2" s="101" t="s">
         <v>418</v>
       </c>
-      <c r="D2" s="100"/>
-      <c r="E2" s="100"/>
-      <c r="F2" s="101" t="s">
+      <c r="D2" s="101"/>
+      <c r="E2" s="101"/>
+      <c r="F2" s="102" t="s">
         <v>419</v>
       </c>
-      <c r="G2" s="101"/>
-      <c r="H2" s="101"/>
+      <c r="G2" s="102"/>
+      <c r="H2" s="102"/>
     </row>
     <row r="3" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A3" s="55" t="s">
@@ -6365,24 +6365,12 @@
       <c r="B22" s="40" t="s">
         <v>320</v>
       </c>
-      <c r="C22" s="102" t="s">
-        <v>324</v>
-      </c>
-      <c r="D22" s="41" t="s">
-        <v>201</v>
-      </c>
-      <c r="E22" s="41" t="s">
-        <v>150</v>
-      </c>
-      <c r="F22" s="24" t="s">
-        <v>324</v>
-      </c>
-      <c r="G22" s="23" t="s">
-        <v>194</v>
-      </c>
-      <c r="H22" s="23" t="s">
-        <v>502</v>
-      </c>
+      <c r="C22" s="96"/>
+      <c r="D22" s="41"/>
+      <c r="E22" s="41"/>
+      <c r="F22" s="24"/>
+      <c r="G22" s="23"/>
+      <c r="H22" s="23"/>
       <c r="I22" s="23"/>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
@@ -9577,7 +9565,7 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" disablePrompts="1" count="3">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="3">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{A3A06F99-31BF-4A5B-9EAE-8CFAC715D117}">
           <x14:formula1>
             <xm:f>konta!$A$2:$A$19</xm:f>
